--- a/portfolio/zach-adams/kml-data-by-person.xlsx
+++ b/portfolio/zach-adams/kml-data-by-person.xlsx
@@ -4,6 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kml-data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phone Directory" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'kml-data'!$A$1:$G$1000</definedName>
@@ -37,7 +38,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +81,48 @@
         <bgColor rgb="FF0D1B2A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00333333"/>
+        <bgColor rgb="00333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD699"/>
+        <bgColor rgb="00FFD699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0099CCFF"/>
+        <bgColor rgb="0099CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0099FF99"/>
+        <bgColor rgb="0099FF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF99"/>
+        <bgColor rgb="00FFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCCCCC"/>
+        <bgColor rgb="00CCCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
+        <bgColor rgb="00FF9999"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -87,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -116,6 +159,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,7 +749,7 @@
           <t>Major Event: Remains recovery location Date: September 7, 2014 Discovered by: Ernest "Larry" Stone (ginseng hunter) Details: Skull found under upside-down bucket near cell tower</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
@@ -748,7 +798,7 @@
           <t>Major Event: Remains recovery location Date: September 7, 2014 Discovered by: Ernest "Larry" Stone (ginseng hunter) Details: Skull found under upside-down bucket near cell tower</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
@@ -793,7 +843,7 @@
         <v>-88.1279471</v>
       </c>
       <c r="F8" s="3" t="n"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
@@ -838,7 +888,7 @@
         <v>-88.1279021</v>
       </c>
       <c r="F9" s="3" t="n"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
@@ -1413,7 +1463,7 @@
           <t>Testimony: Jason Autry searched his late grandmother's barn on Yellow Springs Road for evidence. [cite: 376] Witness: Brian Vitt lived across from the barn. [cite: 415] Status: Reported destroyed in late 2012 or early 2013. [cite: 752] Source: 2022 appellate opinion (State v. Zachary Rye Adams), line refs above</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>Juanita Hickerson</t>
         </is>
@@ -1572,7 +1622,7 @@
           <t>Testimony: Brenda O'Bryant's parents lived across from "Kelly Ridge". [cite: 423] Testimony: A man (identified as Autry) asked to fish in their ponds. [cite: 425] Statement: Defendant told Autry "we throwed her out near Kelly Ridge." [cite: 356] Source: 2022 appellate opinion (State v. Zachary Rye Adams), line refs above</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>Brenda O'Bryant</t>
         </is>
@@ -1678,7 +1728,7 @@
           <t>Testimony: The men drove to Dottie Cooley's home to meet Victor Dinsmore. [cite: 345] Location detail: About two miles from the Defendant's home. [cite: 345] Witness: Cleaner Debbie Dorris reported seeing three men there between ~2:30 and 3:30 p.m. [cite: 521] Source: 2022 appellate opinion (State v. Zachary Rye Adams), line refs above</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>Dottie Cooley</t>
         </is>
@@ -1731,7 +1781,7 @@
           <t>Location: Yellow Springs Road in the Holladay community. [cite: 436] Proximity: The victim's remains were found less than two miles from this location. [cite: 470] Source: 2022 appellate opinion (State v. Zachary Rye Adams), line refs above</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>Victor Dinsmore</t>
         </is>
@@ -1784,7 +1834,7 @@
           <t>Testimony: Defendant hid his white truck in Dinsmore's shop. [cite: 452] Notes: Coordinate represents a mapped shop location near Dinsmore's residence. Source: 2022 appellate opinion (State v. Zachary Rye Adams), line refs above</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>Victor Dinsmore</t>
         </is>
@@ -1837,7 +1887,7 @@
           <t>Identity: Late grandmother of Shayne Austin and Jason Autry. [cite: 415] Evidence: Money and a receipt with the victim's name were found on her property. [cite: 488] Location detail: Located about one mile from Austin's home. [cite: 725] Source: 2022 appellate opinion (State v. Zachary Rye Adams), line refs above</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>Juanita Hickerson</t>
         </is>
@@ -2049,7 +2099,7 @@
           <t>Location detail: In the Yellow Springs community across from Hickerson property. [cite: 415] Testimony: Vitt reported mowing his yard here on the morning of 2011-04-13. [cite: 417] Source: 2022 appellate opinion (State v. Zachary Rye Adams), line refs above</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>Brian Vitt</t>
         </is>
@@ -2098,7 +2148,7 @@
         <v>-87.94491499999999</v>
       </c>
       <c r="F33" s="3" t="n"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" s="0" t="inlineStr"/>
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
@@ -2143,7 +2193,7 @@
         <v>-88.1304504</v>
       </c>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" s="0" t="inlineStr"/>
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
@@ -2245,7 +2295,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 180°–300°</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" s="0" t="inlineStr"/>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
@@ -2290,7 +2340,7 @@
         <v>-88.0894732</v>
       </c>
       <c r="F37" s="3" t="n"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" s="0" t="inlineStr"/>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
@@ -2339,7 +2389,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" s="0" t="inlineStr"/>
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
@@ -2384,7 +2434,7 @@
         <v>-88.0894732</v>
       </c>
       <c r="F39" s="3" t="n"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" s="0" t="inlineStr"/>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
@@ -2433,7 +2483,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" s="0" t="inlineStr"/>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
@@ -2482,7 +2532,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 300°–60°</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" s="0" t="inlineStr"/>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
@@ -2527,7 +2577,7 @@
         <v>-88.0894732</v>
       </c>
       <c r="F42" s="3" t="n"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" s="0" t="inlineStr"/>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
@@ -2576,7 +2626,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" s="0" t="inlineStr"/>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
@@ -2621,7 +2671,7 @@
         <v>-88.0894732</v>
       </c>
       <c r="F44" s="3" t="n"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" s="0" t="inlineStr"/>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
@@ -2670,7 +2720,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" s="0" t="inlineStr"/>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
@@ -2719,7 +2769,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 60°–180°</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" s="0" t="inlineStr"/>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
@@ -2764,7 +2814,7 @@
         <v>-88.0894732</v>
       </c>
       <c r="F47" s="3" t="n"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" s="0" t="inlineStr"/>
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
@@ -2813,7 +2863,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" s="0" t="inlineStr"/>
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
@@ -2858,7 +2908,7 @@
         <v>-88.0894732</v>
       </c>
       <c r="F49" s="3" t="n"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" s="0" t="inlineStr"/>
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
@@ -2907,7 +2957,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" s="0" t="inlineStr"/>
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
@@ -2956,7 +3006,7 @@
           <t>Notes: Cell tower location included for mapping tower geography referenced in case materials. Source: Tower location data (as compiled in this file)</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" s="0" t="inlineStr"/>
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
@@ -3005,7 +3055,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 0°–120°</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" s="0" t="inlineStr"/>
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
@@ -3050,7 +3100,7 @@
         <v>-88.2741621</v>
       </c>
       <c r="F53" s="3" t="n"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" s="0" t="inlineStr"/>
       <c r="H53" s="3" t="n"/>
       <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n"/>
@@ -3099,7 +3149,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" s="0" t="inlineStr"/>
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
@@ -3144,7 +3194,7 @@
         <v>-88.2741621</v>
       </c>
       <c r="F55" s="3" t="n"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" s="0" t="inlineStr"/>
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
@@ -3193,7 +3243,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" s="0" t="inlineStr"/>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
@@ -3242,7 +3292,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 120°–240°</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" s="0" t="inlineStr"/>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
@@ -3287,7 +3337,7 @@
         <v>-88.2741621</v>
       </c>
       <c r="F58" s="3" t="n"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" s="0" t="inlineStr"/>
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
@@ -3336,7 +3386,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" s="0" t="inlineStr"/>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
@@ -3381,7 +3431,7 @@
         <v>-88.2741621</v>
       </c>
       <c r="F60" s="3" t="n"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" s="0" t="inlineStr"/>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
       <c r="J60" s="3" t="n"/>
@@ -3430,7 +3480,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" s="0" t="inlineStr"/>
       <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
       <c r="J61" s="3" t="n"/>
@@ -3479,7 +3529,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 240°–360°</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" s="0" t="inlineStr"/>
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
       <c r="J62" s="3" t="n"/>
@@ -3524,7 +3574,7 @@
         <v>-88.2741621</v>
       </c>
       <c r="F63" s="3" t="n"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" s="0" t="inlineStr"/>
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
       <c r="J63" s="3" t="n"/>
@@ -3573,7 +3623,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" s="0" t="inlineStr"/>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
       <c r="J64" s="3" t="n"/>
@@ -3618,7 +3668,7 @@
         <v>-88.2741621</v>
       </c>
       <c r="F65" s="3" t="n"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" s="0" t="inlineStr"/>
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
       <c r="J65" s="3" t="n"/>
@@ -3667,7 +3717,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" s="0" t="inlineStr"/>
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
       <c r="J66" s="3" t="n"/>
@@ -3769,7 +3819,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 0°–120°</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" s="0" t="inlineStr"/>
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
       <c r="J68" s="3" t="n"/>
@@ -3814,7 +3864,7 @@
         <v>-88.121126</v>
       </c>
       <c r="F69" s="3" t="n"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" s="0" t="inlineStr"/>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
       <c r="J69" s="3" t="n"/>
@@ -3863,7 +3913,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" s="0" t="inlineStr"/>
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
       <c r="J70" s="3" t="n"/>
@@ -3908,7 +3958,7 @@
         <v>-88.121126</v>
       </c>
       <c r="F71" s="3" t="n"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" s="0" t="inlineStr"/>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
       <c r="J71" s="3" t="n"/>
@@ -3957,7 +4007,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" s="0" t="inlineStr"/>
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
       <c r="J72" s="3" t="n"/>
@@ -4006,7 +4056,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 120°–240°</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" s="0" t="inlineStr"/>
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="3" t="n"/>
       <c r="J73" s="3" t="n"/>
@@ -4051,7 +4101,7 @@
         <v>-88.121126</v>
       </c>
       <c r="F74" s="3" t="n"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" s="0" t="inlineStr"/>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
       <c r="J74" s="3" t="n"/>
@@ -4100,7 +4150,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" s="0" t="inlineStr"/>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
       <c r="J75" s="3" t="n"/>
@@ -4145,7 +4195,7 @@
         <v>-88.121126</v>
       </c>
       <c r="F76" s="3" t="n"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" s="0" t="inlineStr"/>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
       <c r="J76" s="3" t="n"/>
@@ -4194,7 +4244,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" s="0" t="inlineStr"/>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
       <c r="J77" s="3" t="n"/>
@@ -4243,7 +4293,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 240°–360°</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" s="0" t="inlineStr"/>
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
       <c r="J78" s="3" t="n"/>
@@ -4288,7 +4338,7 @@
         <v>-88.121126</v>
       </c>
       <c r="F79" s="3" t="n"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" s="0" t="inlineStr"/>
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
       <c r="J79" s="3" t="n"/>
@@ -4337,7 +4387,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" s="0" t="inlineStr"/>
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="n"/>
@@ -4382,7 +4432,7 @@
         <v>-88.121126</v>
       </c>
       <c r="F81" s="3" t="n"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" s="0" t="inlineStr"/>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
       <c r="J81" s="3" t="n"/>
@@ -4431,7 +4481,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" s="0" t="inlineStr"/>
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="n"/>
       <c r="J82" s="3" t="n"/>
@@ -4533,7 +4583,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 0°–120°</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" s="0" t="inlineStr"/>
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="n"/>
       <c r="J84" s="3" t="n"/>
@@ -4578,7 +4628,7 @@
         <v>-88.2058356</v>
       </c>
       <c r="F85" s="3" t="n"/>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" s="0" t="inlineStr"/>
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="n"/>
       <c r="J85" s="3" t="n"/>
@@ -4627,7 +4677,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" s="0" t="inlineStr"/>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="n"/>
       <c r="J86" s="3" t="n"/>
@@ -4672,7 +4722,7 @@
         <v>-88.2058356</v>
       </c>
       <c r="F87" s="3" t="n"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" s="0" t="inlineStr"/>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
       <c r="J87" s="3" t="n"/>
@@ -4721,7 +4771,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" s="0" t="inlineStr"/>
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="n"/>
       <c r="J88" s="3" t="n"/>
@@ -4770,7 +4820,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 120°–240°</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" s="0" t="inlineStr"/>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
       <c r="J89" s="3" t="n"/>
@@ -4815,7 +4865,7 @@
         <v>-88.2058356</v>
       </c>
       <c r="F90" s="3" t="n"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" s="0" t="inlineStr"/>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
       <c r="J90" s="3" t="n"/>
@@ -4864,7 +4914,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" s="0" t="inlineStr"/>
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="n"/>
       <c r="J91" s="3" t="n"/>
@@ -4909,7 +4959,7 @@
         <v>-88.2058356</v>
       </c>
       <c r="F92" s="3" t="n"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" s="0" t="inlineStr"/>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
       <c r="J92" s="3" t="n"/>
@@ -4958,7 +5008,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" s="0" t="inlineStr"/>
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
       <c r="J93" s="3" t="n"/>
@@ -5007,7 +5057,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 240°–360°</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" s="0" t="inlineStr"/>
       <c r="H94" s="3" t="n"/>
       <c r="I94" s="3" t="n"/>
       <c r="J94" s="3" t="n"/>
@@ -5052,7 +5102,7 @@
         <v>-88.2058356</v>
       </c>
       <c r="F95" s="3" t="n"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" s="0" t="inlineStr"/>
       <c r="H95" s="3" t="n"/>
       <c r="I95" s="3" t="n"/>
       <c r="J95" s="3" t="n"/>
@@ -5101,7 +5151,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" s="0" t="inlineStr"/>
       <c r="H96" s="3" t="n"/>
       <c r="I96" s="3" t="n"/>
       <c r="J96" s="3" t="n"/>
@@ -5146,7 +5196,7 @@
         <v>-88.2058356</v>
       </c>
       <c r="F97" s="3" t="n"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" s="0" t="inlineStr"/>
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
       <c r="J97" s="3" t="n"/>
@@ -5195,7 +5245,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" s="0" t="inlineStr"/>
       <c r="H98" s="3" t="n"/>
       <c r="I98" s="3" t="n"/>
       <c r="J98" s="3" t="n"/>
@@ -5297,7 +5347,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 0°–120°</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" s="0" t="inlineStr"/>
       <c r="H100" s="3" t="n"/>
       <c r="I100" s="3" t="n"/>
       <c r="J100" s="3" t="n"/>
@@ -5342,7 +5392,7 @@
         <v>-88.0379963</v>
       </c>
       <c r="F101" s="3" t="n"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" s="0" t="inlineStr"/>
       <c r="H101" s="3" t="n"/>
       <c r="I101" s="3" t="n"/>
       <c r="J101" s="3" t="n"/>
@@ -5391,7 +5441,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" s="0" t="inlineStr"/>
       <c r="H102" s="3" t="n"/>
       <c r="I102" s="3" t="n"/>
       <c r="J102" s="3" t="n"/>
@@ -5436,7 +5486,7 @@
         <v>-88.0379963</v>
       </c>
       <c r="F103" s="3" t="n"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" s="0" t="inlineStr"/>
       <c r="H103" s="3" t="n"/>
       <c r="I103" s="3" t="n"/>
       <c r="J103" s="3" t="n"/>
@@ -5485,7 +5535,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" s="0" t="inlineStr"/>
       <c r="H104" s="3" t="n"/>
       <c r="I104" s="3" t="n"/>
       <c r="J104" s="3" t="n"/>
@@ -5534,7 +5584,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 120°–240°</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" s="0" t="inlineStr"/>
       <c r="H105" s="3" t="n"/>
       <c r="I105" s="3" t="n"/>
       <c r="J105" s="3" t="n"/>
@@ -5579,7 +5629,7 @@
         <v>-88.0379963</v>
       </c>
       <c r="F106" s="3" t="n"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" s="0" t="inlineStr"/>
       <c r="H106" s="3" t="n"/>
       <c r="I106" s="3" t="n"/>
       <c r="J106" s="3" t="n"/>
@@ -5628,7 +5678,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" s="0" t="inlineStr"/>
       <c r="H107" s="3" t="n"/>
       <c r="I107" s="3" t="n"/>
       <c r="J107" s="3" t="n"/>
@@ -5673,7 +5723,7 @@
         <v>-88.0379963</v>
       </c>
       <c r="F108" s="3" t="n"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" s="0" t="inlineStr"/>
       <c r="H108" s="3" t="n"/>
       <c r="I108" s="3" t="n"/>
       <c r="J108" s="3" t="n"/>
@@ -5722,7 +5772,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" s="0" t="inlineStr"/>
       <c r="H109" s="3" t="n"/>
       <c r="I109" s="3" t="n"/>
       <c r="J109" s="3" t="n"/>
@@ -5771,7 +5821,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 240°–360°</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" s="0" t="inlineStr"/>
       <c r="H110" s="3" t="n"/>
       <c r="I110" s="3" t="n"/>
       <c r="J110" s="3" t="n"/>
@@ -5816,7 +5866,7 @@
         <v>-88.0379963</v>
       </c>
       <c r="F111" s="3" t="n"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" s="0" t="inlineStr"/>
       <c r="H111" s="3" t="n"/>
       <c r="I111" s="3" t="n"/>
       <c r="J111" s="3" t="n"/>
@@ -5865,7 +5915,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" s="0" t="inlineStr"/>
       <c r="H112" s="3" t="n"/>
       <c r="I112" s="3" t="n"/>
       <c r="J112" s="3" t="n"/>
@@ -5910,7 +5960,7 @@
         <v>-88.0379963</v>
       </c>
       <c r="F113" s="3" t="n"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" s="0" t="inlineStr"/>
       <c r="H113" s="3" t="n"/>
       <c r="I113" s="3" t="n"/>
       <c r="J113" s="3" t="n"/>
@@ -5959,7 +6009,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" s="0" t="inlineStr"/>
       <c r="H114" s="3" t="n"/>
       <c r="I114" s="3" t="n"/>
       <c r="J114" s="3" t="n"/>
@@ -6008,7 +6058,7 @@
           <t>Notes: Cell tower location included for mapping tower geography referenced in case materials. Source: Tower location data (as compiled in this file)</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" s="0" t="inlineStr"/>
       <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="n"/>
       <c r="J115" s="3" t="n"/>
@@ -6057,7 +6107,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 0°–120°</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" s="0" t="inlineStr"/>
       <c r="H116" s="3" t="n"/>
       <c r="I116" s="3" t="n"/>
       <c r="J116" s="3" t="n"/>
@@ -6102,7 +6152,7 @@
         <v>-88.10396249999999</v>
       </c>
       <c r="F117" s="3" t="n"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" s="0" t="inlineStr"/>
       <c r="H117" s="3" t="n"/>
       <c r="I117" s="3" t="n"/>
       <c r="J117" s="3" t="n"/>
@@ -6151,7 +6201,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" s="0" t="inlineStr"/>
       <c r="H118" s="3" t="n"/>
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="3" t="n"/>
@@ -6196,7 +6246,7 @@
         <v>-88.10396249999999</v>
       </c>
       <c r="F119" s="3" t="n"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" s="0" t="inlineStr"/>
       <c r="H119" s="3" t="n"/>
       <c r="I119" s="3" t="n"/>
       <c r="J119" s="3" t="n"/>
@@ -6245,7 +6295,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" s="0" t="inlineStr"/>
       <c r="H120" s="3" t="n"/>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="3" t="n"/>
@@ -6294,7 +6344,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 120°–240°</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" s="0" t="inlineStr"/>
       <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="n"/>
       <c r="J121" s="3" t="n"/>
@@ -6339,7 +6389,7 @@
         <v>-88.10396249999999</v>
       </c>
       <c r="F122" s="3" t="n"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" s="0" t="inlineStr"/>
       <c r="H122" s="3" t="n"/>
       <c r="I122" s="3" t="n"/>
       <c r="J122" s="3" t="n"/>
@@ -6388,7 +6438,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" s="0" t="inlineStr"/>
       <c r="H123" s="3" t="n"/>
       <c r="I123" s="3" t="n"/>
       <c r="J123" s="3" t="n"/>
@@ -6433,7 +6483,7 @@
         <v>-88.10396249999999</v>
       </c>
       <c r="F124" s="3" t="n"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" s="0" t="inlineStr"/>
       <c r="H124" s="3" t="n"/>
       <c r="I124" s="3" t="n"/>
       <c r="J124" s="3" t="n"/>
@@ -6482,7 +6532,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" s="0" t="inlineStr"/>
       <c r="H125" s="3" t="n"/>
       <c r="I125" s="3" t="n"/>
       <c r="J125" s="3" t="n"/>
@@ -6531,7 +6581,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 240°–360°</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" s="0" t="inlineStr"/>
       <c r="H126" s="3" t="n"/>
       <c r="I126" s="3" t="n"/>
       <c r="J126" s="3" t="n"/>
@@ -6576,7 +6626,7 @@
         <v>-88.10396249999999</v>
       </c>
       <c r="F127" s="3" t="n"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" s="0" t="inlineStr"/>
       <c r="H127" s="3" t="n"/>
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="3" t="n"/>
@@ -6625,7 +6675,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" s="0" t="inlineStr"/>
       <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="n"/>
       <c r="J128" s="3" t="n"/>
@@ -6670,7 +6720,7 @@
         <v>-88.10396249999999</v>
       </c>
       <c r="F129" s="3" t="n"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" s="0" t="inlineStr"/>
       <c r="H129" s="3" t="n"/>
       <c r="I129" s="3" t="n"/>
       <c r="J129" s="3" t="n"/>
@@ -6719,7 +6769,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" s="0" t="inlineStr"/>
       <c r="H130" s="3" t="n"/>
       <c r="I130" s="3" t="n"/>
       <c r="J130" s="3" t="n"/>
@@ -6821,7 +6871,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 0°–120°</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" s="0" t="inlineStr"/>
       <c r="H132" s="3" t="n"/>
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="n"/>
@@ -6866,7 +6916,7 @@
         <v>-87.9716572</v>
       </c>
       <c r="F133" s="3" t="n"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" s="0" t="inlineStr"/>
       <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="3" t="n"/>
@@ -6915,7 +6965,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" s="0" t="inlineStr"/>
       <c r="H134" s="3" t="n"/>
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="3" t="n"/>
@@ -6960,7 +7010,7 @@
         <v>-87.9716572</v>
       </c>
       <c r="F135" s="3" t="n"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" s="0" t="inlineStr"/>
       <c r="H135" s="3" t="n"/>
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="3" t="n"/>
@@ -7009,7 +7059,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" s="0" t="inlineStr"/>
       <c r="H136" s="3" t="n"/>
       <c r="I136" s="3" t="n"/>
       <c r="J136" s="3" t="n"/>
@@ -7058,7 +7108,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 120°–240°</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" s="0" t="inlineStr"/>
       <c r="H137" s="3" t="n"/>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="3" t="n"/>
@@ -7103,7 +7153,7 @@
         <v>-87.9716572</v>
       </c>
       <c r="F138" s="3" t="n"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" s="0" t="inlineStr"/>
       <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="3" t="n"/>
@@ -7152,7 +7202,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" s="0" t="inlineStr"/>
       <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="3" t="n"/>
@@ -7197,7 +7247,7 @@
         <v>-87.9716572</v>
       </c>
       <c r="F140" s="3" t="n"/>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" s="0" t="inlineStr"/>
       <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n"/>
@@ -7246,7 +7296,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" s="0" t="inlineStr"/>
       <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n"/>
@@ -7295,7 +7345,7 @@
           <t>Type: Approx sector wedge Radius: 2.0 km Bearing range: 240°–360°</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" s="0" t="inlineStr"/>
       <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="3" t="n"/>
@@ -7340,7 +7390,7 @@
         <v>-87.9716572</v>
       </c>
       <c r="F143" s="3" t="n"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" s="0" t="inlineStr"/>
       <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="3" t="n"/>
@@ -7389,7 +7439,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" s="0" t="inlineStr"/>
       <c r="H144" s="3" t="n"/>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="n"/>
@@ -7434,7 +7484,7 @@
         <v>-87.9716572</v>
       </c>
       <c r="F145" s="3" t="n"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" s="0" t="inlineStr"/>
       <c r="H145" s="3" t="n"/>
       <c r="I145" s="3" t="n"/>
       <c r="J145" s="3" t="n"/>
@@ -7483,7 +7533,7 @@
           <t>2 points</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" s="0" t="inlineStr"/>
       <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="n"/>
       <c r="J146" s="3" t="n"/>
@@ -7532,7 +7582,7 @@
           <t>TowerType: ATT Time: 9:10am Date: 1302652800000</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" s="0" t="inlineStr"/>
       <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="n"/>
       <c r="J147" s="3" t="n"/>
@@ -7581,7 +7631,7 @@
           <t>FID: 1 TowerType: ATT Time: 9:02am Date: 1302652800000</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" s="0" t="inlineStr"/>
       <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="n"/>
       <c r="J148" s="3" t="n"/>
@@ -7630,7 +7680,7 @@
           <t>FID: 2 TowerType: ATT Time: 8:57am Date: 1302652800000</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" s="0" t="inlineStr"/>
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="n"/>
       <c r="J149" s="3" t="n"/>
@@ -7679,7 +7729,7 @@
           <t>Category: Private business/person Date: -88.1758007! Source: Designated context points (as compiled in this file)</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" s="0" t="inlineStr"/>
       <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="n"/>
       <c r="J150" s="3" t="n"/>
@@ -7728,7 +7778,7 @@
           <t>Label: Phone GPS Trail Notes: Data from social media/independent investigation Type: GPS Comment: Not from court proceedings</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" s="0" t="inlineStr"/>
       <c r="H151" s="3" t="n"/>
       <c r="I151" s="3" t="n"/>
       <c r="J151" s="3" t="n"/>
@@ -7777,7 +7827,7 @@
           <t>153 points</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
+      <c r="G152" s="0" t="inlineStr"/>
       <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="n"/>
       <c r="J152" s="3" t="n"/>
@@ -7826,7 +7876,7 @@
           <t>Label: Phone GPS Trail Notes: Data from social media/independent investigation Type: GPS Comment: Not from court proceedings</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" s="0" t="inlineStr"/>
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="n"/>
@@ -7875,7 +7925,7 @@
           <t>138 points</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" s="0" t="inlineStr"/>
       <c r="H154" s="3" t="n"/>
       <c r="I154" s="3" t="n"/>
       <c r="J154" s="3" t="n"/>
@@ -7924,7 +7974,7 @@
           <t>BOBO RESIDENCE Cell phone departs near 8:00 AM</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
+      <c r="G155" s="0" t="inlineStr"/>
       <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="n"/>
       <c r="J155" s="3" t="n"/>
@@ -7973,7 +8023,7 @@
           <t>Near Hickory Forks (along route from Bobo Residence)</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
+      <c r="G156" s="0" t="inlineStr"/>
       <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="n"/>
       <c r="J156" s="3" t="n"/>
@@ -8022,7 +8072,7 @@
           <t>Near Bible Hill (along route)</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
+      <c r="G157" s="0" t="inlineStr"/>
       <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="n"/>
       <c r="J157" s="3" t="n"/>
@@ -8071,7 +8121,7 @@
           <t>Along route heading north</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
+      <c r="G158" s="0" t="inlineStr"/>
       <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="n"/>
       <c r="J158" s="3" t="n"/>
@@ -8120,7 +8170,7 @@
           <t>Along route in Henderson County area</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
+      <c r="G159" s="0" t="inlineStr"/>
       <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="n"/>
       <c r="J159" s="3" t="n"/>
@@ -8169,7 +8219,7 @@
           <t>Cell phone 8:11 AM Approximate location of telephone at 8:11 AM reading CR 1253 Section 1</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
+      <c r="G160" s="0" t="inlineStr"/>
       <c r="H160" s="3" t="n"/>
       <c r="I160" s="3" t="n"/>
       <c r="J160" s="3" t="n"/>
@@ -8218,7 +8268,7 @@
           <t>Near marker 6 (along route)</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
+      <c r="G161" s="0" t="inlineStr"/>
       <c r="H161" s="3" t="n"/>
       <c r="I161" s="3" t="n"/>
       <c r="J161" s="3" t="n"/>
@@ -8267,7 +8317,7 @@
           <t>Creek Gooch Road Location of cell phone at 9:25 AM Reading CR 1257 Section 3. Creek location of Lunch Box and Notebook</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
+      <c r="G162" s="0" t="inlineStr"/>
       <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="n"/>
       <c r="J162" s="3" t="n"/>
@@ -8316,7 +8366,7 @@
           <t>Natchez Trace State area In Area for 30 minutes. Reading CR 1096 Section 1. Direction of travel, in area of CR 1096 Section 1</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
+      <c r="G163" s="0" t="inlineStr"/>
       <c r="H163" s="3" t="n"/>
       <c r="I163" s="3" t="n"/>
       <c r="J163" s="3" t="n"/>
@@ -8418,7 +8468,7 @@
           <t>Cell phone at 9:06 AM Approximate location of cell phone at 9:06 AM reading CR 3152 Section 3</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
+      <c r="G165" s="0" t="inlineStr"/>
       <c r="H165" s="3" t="n"/>
       <c r="I165" s="3" t="n"/>
       <c r="J165" s="3" t="n"/>
@@ -8520,7 +8570,7 @@
           <t>In Benton County/Tennessee area (along route)</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
+      <c r="G167" s="0" t="inlineStr"/>
       <c r="H167" s="3" t="n"/>
       <c r="I167" s="3" t="n"/>
       <c r="J167" s="3" t="n"/>
@@ -8569,7 +8619,7 @@
           <t>Cell phone at 9:02 AM Approximate location of cell telephone at 9:02 AM reading CR 3152 Section 3</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" s="0" t="inlineStr"/>
       <c r="H168" s="3" t="n"/>
       <c r="I168" s="3" t="n"/>
       <c r="J168" s="3" t="n"/>
@@ -8618,7 +8668,7 @@
           <t>Cell phone at 9:10 AM Approximate location of cell phone at 9:10 AM reading CR 3152 Section 2</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" s="0" t="inlineStr"/>
       <c r="H169" s="3" t="n"/>
       <c r="I169" s="3" t="n"/>
       <c r="J169" s="3" t="n"/>
@@ -8667,7 +8717,7 @@
           <t>Along route near marker 17</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" s="0" t="inlineStr"/>
       <c r="H170" s="3" t="n"/>
       <c r="I170" s="3" t="n"/>
       <c r="J170" s="3" t="n"/>
@@ -8716,7 +8766,7 @@
           <t>Near Jeannette (along route)</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
+      <c r="G171" s="0" t="inlineStr"/>
       <c r="H171" s="3" t="n"/>
       <c r="I171" s="3" t="n"/>
       <c r="J171" s="3" t="n"/>
@@ -9858,7 +9908,7 @@
       <c r="D193" s="4" t="n"/>
       <c r="E193" s="4" t="n"/>
       <c r="F193" s="3" t="n"/>
-      <c r="G193" t="inlineStr"/>
+      <c r="G193" s="0" t="inlineStr"/>
       <c r="H193" s="3" t="n"/>
       <c r="I193" s="3" t="n"/>
       <c r="J193" s="3" t="n"/>
@@ -9887,7 +9937,7 @@
       <c r="D194" s="4" t="n"/>
       <c r="E194" s="4" t="n"/>
       <c r="F194" s="3" t="n"/>
-      <c r="G194" t="inlineStr"/>
+      <c r="G194" s="0" t="inlineStr"/>
       <c r="H194" s="3" t="n"/>
       <c r="I194" s="3" t="n"/>
       <c r="J194" s="3" t="n"/>
@@ -9916,7 +9966,7 @@
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="4" t="n"/>
       <c r="F195" s="3" t="n"/>
-      <c r="G195" t="inlineStr"/>
+      <c r="G195" s="0" t="inlineStr"/>
       <c r="H195" s="3" t="n"/>
       <c r="I195" s="3" t="n"/>
       <c r="J195" s="3" t="n"/>
@@ -9945,7 +9995,7 @@
       <c r="D196" s="4" t="n"/>
       <c r="E196" s="4" t="n"/>
       <c r="F196" s="3" t="n"/>
-      <c r="G196" t="inlineStr"/>
+      <c r="G196" s="0" t="inlineStr"/>
       <c r="H196" s="3" t="n"/>
       <c r="I196" s="3" t="n"/>
       <c r="J196" s="3" t="n"/>
@@ -9974,7 +10024,7 @@
       <c r="D197" s="4" t="n"/>
       <c r="E197" s="4" t="n"/>
       <c r="F197" s="3" t="n"/>
-      <c r="G197" t="inlineStr"/>
+      <c r="G197" s="0" t="inlineStr"/>
       <c r="H197" s="3" t="n"/>
       <c r="I197" s="3" t="n"/>
       <c r="J197" s="3" t="n"/>
@@ -10003,7 +10053,7 @@
       <c r="D198" s="4" t="n"/>
       <c r="E198" s="4" t="n"/>
       <c r="F198" s="3" t="n"/>
-      <c r="G198" t="inlineStr"/>
+      <c r="G198" s="0" t="inlineStr"/>
       <c r="H198" s="3" t="n"/>
       <c r="I198" s="3" t="n"/>
       <c r="J198" s="3" t="n"/>
@@ -10032,7 +10082,7 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="4" t="n"/>
       <c r="F199" s="3" t="n"/>
-      <c r="G199" t="inlineStr"/>
+      <c r="G199" s="0" t="inlineStr"/>
       <c r="H199" s="3" t="n"/>
       <c r="I199" s="3" t="n"/>
       <c r="J199" s="3" t="n"/>
@@ -10061,7 +10111,7 @@
       <c r="D200" s="4" t="n"/>
       <c r="E200" s="4" t="n"/>
       <c r="F200" s="3" t="n"/>
-      <c r="G200" t="inlineStr"/>
+      <c r="G200" s="0" t="inlineStr"/>
       <c r="H200" s="3" t="n"/>
       <c r="I200" s="3" t="n"/>
       <c r="J200" s="3" t="n"/>
@@ -10090,7 +10140,7 @@
       <c r="D201" s="4" t="n"/>
       <c r="E201" s="4" t="n"/>
       <c r="F201" s="3" t="n"/>
-      <c r="G201" t="inlineStr"/>
+      <c r="G201" s="0" t="inlineStr"/>
       <c r="H201" s="3" t="n"/>
       <c r="I201" s="3" t="n"/>
       <c r="J201" s="3" t="n"/>
@@ -10119,7 +10169,7 @@
       <c r="D202" s="4" t="n"/>
       <c r="E202" s="4" t="n"/>
       <c r="F202" s="3" t="n"/>
-      <c r="G202" t="inlineStr"/>
+      <c r="G202" s="0" t="inlineStr"/>
       <c r="H202" s="3" t="n"/>
       <c r="I202" s="3" t="n"/>
       <c r="J202" s="3" t="n"/>
@@ -10148,7 +10198,7 @@
       <c r="D203" s="4" t="n"/>
       <c r="E203" s="4" t="n"/>
       <c r="F203" s="3" t="n"/>
-      <c r="G203" t="inlineStr"/>
+      <c r="G203" s="0" t="inlineStr"/>
       <c r="H203" s="3" t="n"/>
       <c r="I203" s="3" t="n"/>
       <c r="J203" s="3" t="n"/>
@@ -10177,7 +10227,7 @@
       <c r="D204" s="4" t="n"/>
       <c r="E204" s="4" t="n"/>
       <c r="F204" s="3" t="n"/>
-      <c r="G204" t="inlineStr"/>
+      <c r="G204" s="0" t="inlineStr"/>
       <c r="H204" s="3" t="n"/>
       <c r="I204" s="3" t="n"/>
       <c r="J204" s="3" t="n"/>
@@ -10206,7 +10256,7 @@
       <c r="D205" s="4" t="n"/>
       <c r="E205" s="4" t="n"/>
       <c r="F205" s="3" t="n"/>
-      <c r="G205" t="inlineStr"/>
+      <c r="G205" s="0" t="inlineStr"/>
       <c r="H205" s="3" t="n"/>
       <c r="I205" s="3" t="n"/>
       <c r="J205" s="3" t="n"/>
@@ -10235,7 +10285,7 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="4" t="n"/>
       <c r="F206" s="3" t="n"/>
-      <c r="G206" t="inlineStr"/>
+      <c r="G206" s="0" t="inlineStr"/>
       <c r="H206" s="3" t="n"/>
       <c r="I206" s="3" t="n"/>
       <c r="J206" s="3" t="n"/>
@@ -10264,7 +10314,7 @@
       <c r="D207" s="4" t="n"/>
       <c r="E207" s="4" t="n"/>
       <c r="F207" s="3" t="n"/>
-      <c r="G207" t="inlineStr"/>
+      <c r="G207" s="0" t="inlineStr"/>
       <c r="H207" s="3" t="n"/>
       <c r="I207" s="3" t="n"/>
       <c r="J207" s="3" t="n"/>
@@ -10293,7 +10343,7 @@
       <c r="D208" s="4" t="n"/>
       <c r="E208" s="4" t="n"/>
       <c r="F208" s="3" t="n"/>
-      <c r="G208" t="inlineStr"/>
+      <c r="G208" s="0" t="inlineStr"/>
       <c r="H208" s="3" t="n"/>
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="3" t="n"/>
@@ -10322,7 +10372,7 @@
       <c r="D209" s="4" t="n"/>
       <c r="E209" s="4" t="n"/>
       <c r="F209" s="3" t="n"/>
-      <c r="G209" t="inlineStr"/>
+      <c r="G209" s="0" t="inlineStr"/>
       <c r="H209" s="3" t="n"/>
       <c r="I209" s="3" t="n"/>
       <c r="J209" s="3" t="n"/>
@@ -10351,7 +10401,7 @@
       <c r="D210" s="4" t="n"/>
       <c r="E210" s="4" t="n"/>
       <c r="F210" s="3" t="n"/>
-      <c r="G210" t="inlineStr"/>
+      <c r="G210" s="0" t="inlineStr"/>
       <c r="H210" s="3" t="n"/>
       <c r="I210" s="3" t="n"/>
       <c r="J210" s="3" t="n"/>
@@ -10380,7 +10430,7 @@
       <c r="D211" s="4" t="n"/>
       <c r="E211" s="4" t="n"/>
       <c r="F211" s="3" t="n"/>
-      <c r="G211" t="inlineStr"/>
+      <c r="G211" s="0" t="inlineStr"/>
       <c r="H211" s="3" t="n"/>
       <c r="I211" s="3" t="n"/>
       <c r="J211" s="3" t="n"/>
@@ -10409,7 +10459,7 @@
       <c r="D212" s="4" t="n"/>
       <c r="E212" s="4" t="n"/>
       <c r="F212" s="3" t="n"/>
-      <c r="G212" t="inlineStr"/>
+      <c r="G212" s="0" t="inlineStr"/>
       <c r="H212" s="3" t="n"/>
       <c r="I212" s="3" t="n"/>
       <c r="J212" s="3" t="n"/>
@@ -10438,7 +10488,7 @@
       <c r="D213" s="4" t="n"/>
       <c r="E213" s="4" t="n"/>
       <c r="F213" s="3" t="n"/>
-      <c r="G213" t="inlineStr"/>
+      <c r="G213" s="0" t="inlineStr"/>
       <c r="H213" s="3" t="n"/>
       <c r="I213" s="3" t="n"/>
       <c r="J213" s="3" t="n"/>
@@ -10467,7 +10517,7 @@
       <c r="D214" s="4" t="n"/>
       <c r="E214" s="4" t="n"/>
       <c r="F214" s="3" t="n"/>
-      <c r="G214" t="inlineStr"/>
+      <c r="G214" s="0" t="inlineStr"/>
       <c r="H214" s="3" t="n"/>
       <c r="I214" s="3" t="n"/>
       <c r="J214" s="3" t="n"/>
@@ -10496,7 +10546,7 @@
       <c r="D215" s="4" t="n"/>
       <c r="E215" s="4" t="n"/>
       <c r="F215" s="3" t="n"/>
-      <c r="G215" t="inlineStr"/>
+      <c r="G215" s="0" t="inlineStr"/>
       <c r="H215" s="3" t="n"/>
       <c r="I215" s="3" t="n"/>
       <c r="J215" s="3" t="n"/>
@@ -10525,7 +10575,7 @@
       <c r="D216" s="4" t="n"/>
       <c r="E216" s="4" t="n"/>
       <c r="F216" s="3" t="n"/>
-      <c r="G216" t="inlineStr"/>
+      <c r="G216" s="0" t="inlineStr"/>
       <c r="H216" s="3" t="n"/>
       <c r="I216" s="3" t="n"/>
       <c r="J216" s="3" t="n"/>
@@ -10554,7 +10604,7 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="4" t="n"/>
       <c r="F217" s="3" t="n"/>
-      <c r="G217" t="inlineStr"/>
+      <c r="G217" s="0" t="inlineStr"/>
       <c r="H217" s="3" t="n"/>
       <c r="I217" s="3" t="n"/>
       <c r="J217" s="3" t="n"/>
@@ -10583,7 +10633,7 @@
       <c r="D218" s="4" t="n"/>
       <c r="E218" s="4" t="n"/>
       <c r="F218" s="3" t="n"/>
-      <c r="G218" t="inlineStr"/>
+      <c r="G218" s="0" t="inlineStr"/>
       <c r="H218" s="3" t="n"/>
       <c r="I218" s="3" t="n"/>
       <c r="J218" s="3" t="n"/>
@@ -10612,7 +10662,7 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="4" t="n"/>
       <c r="F219" s="3" t="n"/>
-      <c r="G219" t="inlineStr"/>
+      <c r="G219" s="0" t="inlineStr"/>
       <c r="H219" s="3" t="n"/>
       <c r="I219" s="3" t="n"/>
       <c r="J219" s="3" t="n"/>
@@ -10641,7 +10691,7 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="4" t="n"/>
       <c r="F220" s="3" t="n"/>
-      <c r="G220" t="inlineStr"/>
+      <c r="G220" s="0" t="inlineStr"/>
       <c r="H220" s="3" t="n"/>
       <c r="I220" s="3" t="n"/>
       <c r="J220" s="3" t="n"/>
@@ -10670,7 +10720,7 @@
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="4" t="n"/>
       <c r="F221" s="3" t="n"/>
-      <c r="G221" t="inlineStr"/>
+      <c r="G221" s="0" t="inlineStr"/>
       <c r="H221" s="3" t="n"/>
       <c r="I221" s="3" t="n"/>
       <c r="J221" s="3" t="n"/>
@@ -10699,7 +10749,7 @@
       <c r="D222" s="4" t="n"/>
       <c r="E222" s="4" t="n"/>
       <c r="F222" s="3" t="n"/>
-      <c r="G222" t="inlineStr"/>
+      <c r="G222" s="0" t="inlineStr"/>
       <c r="H222" s="3" t="n"/>
       <c r="I222" s="3" t="n"/>
       <c r="J222" s="3" t="n"/>
@@ -10728,7 +10778,7 @@
       <c r="D223" s="4" t="n"/>
       <c r="E223" s="4" t="n"/>
       <c r="F223" s="3" t="n"/>
-      <c r="G223" t="inlineStr"/>
+      <c r="G223" s="0" t="inlineStr"/>
       <c r="H223" s="3" t="n"/>
       <c r="I223" s="3" t="n"/>
       <c r="J223" s="3" t="n"/>
@@ -10757,7 +10807,7 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="4" t="n"/>
       <c r="F224" s="3" t="n"/>
-      <c r="G224" t="inlineStr"/>
+      <c r="G224" s="0" t="inlineStr"/>
       <c r="H224" s="3" t="n"/>
       <c r="I224" s="3" t="n"/>
       <c r="J224" s="3" t="n"/>
@@ -10786,7 +10836,7 @@
       <c r="D225" s="4" t="n"/>
       <c r="E225" s="4" t="n"/>
       <c r="F225" s="3" t="n"/>
-      <c r="G225" t="inlineStr"/>
+      <c r="G225" s="0" t="inlineStr"/>
       <c r="H225" s="3" t="n"/>
       <c r="I225" s="3" t="n"/>
       <c r="J225" s="3" t="n"/>
@@ -10815,7 +10865,7 @@
       <c r="D226" s="4" t="n"/>
       <c r="E226" s="4" t="n"/>
       <c r="F226" s="3" t="n"/>
-      <c r="G226" t="inlineStr"/>
+      <c r="G226" s="0" t="inlineStr"/>
       <c r="H226" s="3" t="n"/>
       <c r="I226" s="3" t="n"/>
       <c r="J226" s="3" t="n"/>
@@ -10844,7 +10894,7 @@
       <c r="D227" s="4" t="n"/>
       <c r="E227" s="4" t="n"/>
       <c r="F227" s="3" t="n"/>
-      <c r="G227" t="inlineStr"/>
+      <c r="G227" s="0" t="inlineStr"/>
       <c r="H227" s="3" t="n"/>
       <c r="I227" s="3" t="n"/>
       <c r="J227" s="3" t="n"/>
@@ -10873,7 +10923,7 @@
       <c r="D228" s="4" t="n"/>
       <c r="E228" s="4" t="n"/>
       <c r="F228" s="3" t="n"/>
-      <c r="G228" t="inlineStr"/>
+      <c r="G228" s="0" t="inlineStr"/>
       <c r="H228" s="3" t="n"/>
       <c r="I228" s="3" t="n"/>
       <c r="J228" s="3" t="n"/>
@@ -10902,7 +10952,7 @@
       <c r="D229" s="4" t="n"/>
       <c r="E229" s="4" t="n"/>
       <c r="F229" s="3" t="n"/>
-      <c r="G229" t="inlineStr"/>
+      <c r="G229" s="0" t="inlineStr"/>
       <c r="H229" s="3" t="n"/>
       <c r="I229" s="3" t="n"/>
       <c r="J229" s="3" t="n"/>
@@ -10931,7 +10981,7 @@
       <c r="D230" s="4" t="n"/>
       <c r="E230" s="4" t="n"/>
       <c r="F230" s="3" t="n"/>
-      <c r="G230" t="inlineStr"/>
+      <c r="G230" s="0" t="inlineStr"/>
       <c r="H230" s="3" t="n"/>
       <c r="I230" s="3" t="n"/>
       <c r="J230" s="3" t="n"/>
@@ -10960,7 +11010,7 @@
       <c r="D231" s="4" t="n"/>
       <c r="E231" s="4" t="n"/>
       <c r="F231" s="3" t="n"/>
-      <c r="G231" t="inlineStr"/>
+      <c r="G231" s="0" t="inlineStr"/>
       <c r="H231" s="3" t="n"/>
       <c r="I231" s="3" t="n"/>
       <c r="J231" s="3" t="n"/>
@@ -10989,7 +11039,7 @@
       <c r="D232" s="4" t="n"/>
       <c r="E232" s="4" t="n"/>
       <c r="F232" s="3" t="n"/>
-      <c r="G232" t="inlineStr"/>
+      <c r="G232" s="0" t="inlineStr"/>
       <c r="H232" s="3" t="n"/>
       <c r="I232" s="3" t="n"/>
       <c r="J232" s="3" t="n"/>
@@ -11018,7 +11068,7 @@
       <c r="D233" s="4" t="n"/>
       <c r="E233" s="4" t="n"/>
       <c r="F233" s="3" t="n"/>
-      <c r="G233" t="inlineStr"/>
+      <c r="G233" s="0" t="inlineStr"/>
       <c r="H233" s="3" t="n"/>
       <c r="I233" s="3" t="n"/>
       <c r="J233" s="3" t="n"/>
@@ -11047,7 +11097,7 @@
       <c r="D234" s="4" t="n"/>
       <c r="E234" s="4" t="n"/>
       <c r="F234" s="3" t="n"/>
-      <c r="G234" t="inlineStr"/>
+      <c r="G234" s="0" t="inlineStr"/>
       <c r="H234" s="3" t="n"/>
       <c r="I234" s="3" t="n"/>
       <c r="J234" s="3" t="n"/>
@@ -11076,7 +11126,7 @@
       <c r="D235" s="4" t="n"/>
       <c r="E235" s="4" t="n"/>
       <c r="F235" s="3" t="n"/>
-      <c r="G235" t="inlineStr"/>
+      <c r="G235" s="0" t="inlineStr"/>
       <c r="H235" s="3" t="n"/>
       <c r="I235" s="3" t="n"/>
       <c r="J235" s="3" t="n"/>
@@ -11105,7 +11155,7 @@
       <c r="D236" s="4" t="n"/>
       <c r="E236" s="4" t="n"/>
       <c r="F236" s="3" t="n"/>
-      <c r="G236" t="inlineStr"/>
+      <c r="G236" s="0" t="inlineStr"/>
       <c r="H236" s="3" t="n"/>
       <c r="I236" s="3" t="n"/>
       <c r="J236" s="3" t="n"/>
@@ -11134,7 +11184,7 @@
       <c r="D237" s="4" t="n"/>
       <c r="E237" s="4" t="n"/>
       <c r="F237" s="3" t="n"/>
-      <c r="G237" t="inlineStr"/>
+      <c r="G237" s="0" t="inlineStr"/>
       <c r="H237" s="3" t="n"/>
       <c r="I237" s="3" t="n"/>
       <c r="J237" s="3" t="n"/>
@@ -11163,7 +11213,7 @@
       <c r="D238" s="4" t="n"/>
       <c r="E238" s="4" t="n"/>
       <c r="F238" s="3" t="n"/>
-      <c r="G238" t="inlineStr"/>
+      <c r="G238" s="0" t="inlineStr"/>
       <c r="H238" s="3" t="n"/>
       <c r="I238" s="3" t="n"/>
       <c r="J238" s="3" t="n"/>
@@ -11192,7 +11242,7 @@
       <c r="D239" s="4" t="n"/>
       <c r="E239" s="4" t="n"/>
       <c r="F239" s="3" t="n"/>
-      <c r="G239" t="inlineStr"/>
+      <c r="G239" s="0" t="inlineStr"/>
       <c r="H239" s="3" t="n"/>
       <c r="I239" s="3" t="n"/>
       <c r="J239" s="3" t="n"/>
@@ -11221,7 +11271,7 @@
       <c r="D240" s="4" t="n"/>
       <c r="E240" s="4" t="n"/>
       <c r="F240" s="3" t="n"/>
-      <c r="G240" t="inlineStr"/>
+      <c r="G240" s="0" t="inlineStr"/>
       <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="n"/>
       <c r="J240" s="3" t="n"/>
@@ -11250,7 +11300,7 @@
       <c r="D241" s="4" t="n"/>
       <c r="E241" s="4" t="n"/>
       <c r="F241" s="3" t="n"/>
-      <c r="G241" t="inlineStr"/>
+      <c r="G241" s="0" t="inlineStr"/>
       <c r="H241" s="3" t="n"/>
       <c r="I241" s="3" t="n"/>
       <c r="J241" s="3" t="n"/>
@@ -11279,7 +11329,7 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="4" t="n"/>
       <c r="F242" s="3" t="n"/>
-      <c r="G242" t="inlineStr"/>
+      <c r="G242" s="0" t="inlineStr"/>
       <c r="H242" s="3" t="n"/>
       <c r="I242" s="3" t="n"/>
       <c r="J242" s="3" t="n"/>
@@ -11308,7 +11358,7 @@
       <c r="D243" s="4" t="n"/>
       <c r="E243" s="4" t="n"/>
       <c r="F243" s="3" t="n"/>
-      <c r="G243" t="inlineStr"/>
+      <c r="G243" s="0" t="inlineStr"/>
       <c r="H243" s="3" t="n"/>
       <c r="I243" s="3" t="n"/>
       <c r="J243" s="3" t="n"/>
@@ -11337,7 +11387,7 @@
       <c r="D244" s="4" t="n"/>
       <c r="E244" s="4" t="n"/>
       <c r="F244" s="3" t="n"/>
-      <c r="G244" t="inlineStr"/>
+      <c r="G244" s="0" t="inlineStr"/>
       <c r="H244" s="3" t="n"/>
       <c r="I244" s="3" t="n"/>
       <c r="J244" s="3" t="n"/>
@@ -11366,7 +11416,7 @@
       <c r="D245" s="4" t="n"/>
       <c r="E245" s="4" t="n"/>
       <c r="F245" s="3" t="n"/>
-      <c r="G245" t="inlineStr"/>
+      <c r="G245" s="0" t="inlineStr"/>
       <c r="H245" s="3" t="n"/>
       <c r="I245" s="3" t="n"/>
       <c r="J245" s="3" t="n"/>
@@ -11395,7 +11445,7 @@
       <c r="D246" s="4" t="n"/>
       <c r="E246" s="4" t="n"/>
       <c r="F246" s="3" t="n"/>
-      <c r="G246" t="inlineStr"/>
+      <c r="G246" s="0" t="inlineStr"/>
       <c r="H246" s="3" t="n"/>
       <c r="I246" s="3" t="n"/>
       <c r="J246" s="3" t="n"/>
@@ -11424,7 +11474,7 @@
       <c r="D247" s="4" t="n"/>
       <c r="E247" s="4" t="n"/>
       <c r="F247" s="3" t="n"/>
-      <c r="G247" t="inlineStr"/>
+      <c r="G247" s="0" t="inlineStr"/>
       <c r="H247" s="3" t="n"/>
       <c r="I247" s="3" t="n"/>
       <c r="J247" s="3" t="n"/>
@@ -11453,7 +11503,7 @@
       <c r="D248" s="4" t="n"/>
       <c r="E248" s="4" t="n"/>
       <c r="F248" s="3" t="n"/>
-      <c r="G248" t="inlineStr"/>
+      <c r="G248" s="0" t="inlineStr"/>
       <c r="H248" s="3" t="n"/>
       <c r="I248" s="3" t="n"/>
       <c r="J248" s="3" t="n"/>
@@ -11482,7 +11532,7 @@
       <c r="D249" s="4" t="n"/>
       <c r="E249" s="4" t="n"/>
       <c r="F249" s="3" t="n"/>
-      <c r="G249" t="inlineStr"/>
+      <c r="G249" s="0" t="inlineStr"/>
       <c r="H249" s="3" t="n"/>
       <c r="I249" s="3" t="n"/>
       <c r="J249" s="3" t="n"/>
@@ -11511,7 +11561,7 @@
       <c r="D250" s="4" t="n"/>
       <c r="E250" s="4" t="n"/>
       <c r="F250" s="3" t="n"/>
-      <c r="G250" t="inlineStr"/>
+      <c r="G250" s="0" t="inlineStr"/>
       <c r="H250" s="3" t="n"/>
       <c r="I250" s="3" t="n"/>
       <c r="J250" s="3" t="n"/>
@@ -11540,7 +11590,7 @@
       <c r="D251" s="4" t="n"/>
       <c r="E251" s="4" t="n"/>
       <c r="F251" s="3" t="n"/>
-      <c r="G251" t="inlineStr"/>
+      <c r="G251" s="0" t="inlineStr"/>
       <c r="H251" s="3" t="n"/>
       <c r="I251" s="3" t="n"/>
       <c r="J251" s="3" t="n"/>
@@ -11569,7 +11619,7 @@
       <c r="D252" s="4" t="n"/>
       <c r="E252" s="4" t="n"/>
       <c r="F252" s="3" t="n"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="G252" s="0" t="inlineStr"/>
       <c r="H252" s="3" t="n"/>
       <c r="I252" s="3" t="n"/>
       <c r="J252" s="3" t="n"/>
@@ -11598,7 +11648,7 @@
       <c r="D253" s="4" t="n"/>
       <c r="E253" s="4" t="n"/>
       <c r="F253" s="3" t="n"/>
-      <c r="G253" t="inlineStr"/>
+      <c r="G253" s="0" t="inlineStr"/>
       <c r="H253" s="3" t="n"/>
       <c r="I253" s="3" t="n"/>
       <c r="J253" s="3" t="n"/>
@@ -11627,7 +11677,7 @@
       <c r="D254" s="4" t="n"/>
       <c r="E254" s="4" t="n"/>
       <c r="F254" s="3" t="n"/>
-      <c r="G254" t="inlineStr"/>
+      <c r="G254" s="0" t="inlineStr"/>
       <c r="H254" s="3" t="n"/>
       <c r="I254" s="3" t="n"/>
       <c r="J254" s="3" t="n"/>
@@ -11656,7 +11706,7 @@
       <c r="D255" s="4" t="n"/>
       <c r="E255" s="4" t="n"/>
       <c r="F255" s="3" t="n"/>
-      <c r="G255" t="inlineStr"/>
+      <c r="G255" s="0" t="inlineStr"/>
       <c r="H255" s="3" t="n"/>
       <c r="I255" s="3" t="n"/>
       <c r="J255" s="3" t="n"/>
@@ -11685,7 +11735,7 @@
       <c r="D256" s="4" t="n"/>
       <c r="E256" s="4" t="n"/>
       <c r="F256" s="3" t="n"/>
-      <c r="G256" t="inlineStr"/>
+      <c r="G256" s="0" t="inlineStr"/>
       <c r="H256" s="3" t="n"/>
       <c r="I256" s="3" t="n"/>
       <c r="J256" s="3" t="n"/>
@@ -11714,7 +11764,7 @@
       <c r="D257" s="4" t="n"/>
       <c r="E257" s="4" t="n"/>
       <c r="F257" s="3" t="n"/>
-      <c r="G257" t="inlineStr"/>
+      <c r="G257" s="0" t="inlineStr"/>
       <c r="H257" s="3" t="n"/>
       <c r="I257" s="3" t="n"/>
       <c r="J257" s="3" t="n"/>
@@ -11743,7 +11793,7 @@
       <c r="D258" s="4" t="n"/>
       <c r="E258" s="4" t="n"/>
       <c r="F258" s="3" t="n"/>
-      <c r="G258" t="inlineStr"/>
+      <c r="G258" s="0" t="inlineStr"/>
       <c r="H258" s="3" t="n"/>
       <c r="I258" s="3" t="n"/>
       <c r="J258" s="3" t="n"/>
@@ -11772,7 +11822,7 @@
       <c r="D259" s="4" t="n"/>
       <c r="E259" s="4" t="n"/>
       <c r="F259" s="3" t="n"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="G259" s="0" t="inlineStr"/>
       <c r="H259" s="3" t="n"/>
       <c r="I259" s="3" t="n"/>
       <c r="J259" s="3" t="n"/>
@@ -11801,7 +11851,7 @@
       <c r="D260" s="4" t="n"/>
       <c r="E260" s="4" t="n"/>
       <c r="F260" s="3" t="n"/>
-      <c r="G260" t="inlineStr"/>
+      <c r="G260" s="0" t="inlineStr"/>
       <c r="H260" s="3" t="n"/>
       <c r="I260" s="3" t="n"/>
       <c r="J260" s="3" t="n"/>
@@ -11830,7 +11880,7 @@
       <c r="D261" s="4" t="n"/>
       <c r="E261" s="4" t="n"/>
       <c r="F261" s="3" t="n"/>
-      <c r="G261" t="inlineStr"/>
+      <c r="G261" s="0" t="inlineStr"/>
       <c r="H261" s="3" t="n"/>
       <c r="I261" s="3" t="n"/>
       <c r="J261" s="3" t="n"/>
@@ -11859,7 +11909,7 @@
       <c r="D262" s="4" t="n"/>
       <c r="E262" s="4" t="n"/>
       <c r="F262" s="3" t="n"/>
-      <c r="G262" t="inlineStr"/>
+      <c r="G262" s="0" t="inlineStr"/>
       <c r="H262" s="3" t="n"/>
       <c r="I262" s="3" t="n"/>
       <c r="J262" s="3" t="n"/>
@@ -11888,7 +11938,7 @@
       <c r="D263" s="4" t="n"/>
       <c r="E263" s="4" t="n"/>
       <c r="F263" s="3" t="n"/>
-      <c r="G263" t="inlineStr"/>
+      <c r="G263" s="0" t="inlineStr"/>
       <c r="H263" s="3" t="n"/>
       <c r="I263" s="3" t="n"/>
       <c r="J263" s="3" t="n"/>
@@ -11917,7 +11967,7 @@
       <c r="D264" s="4" t="n"/>
       <c r="E264" s="4" t="n"/>
       <c r="F264" s="3" t="n"/>
-      <c r="G264" t="inlineStr"/>
+      <c r="G264" s="0" t="inlineStr"/>
       <c r="H264" s="3" t="n"/>
       <c r="I264" s="3" t="n"/>
       <c r="J264" s="3" t="n"/>
@@ -11946,7 +11996,7 @@
       <c r="D265" s="4" t="n"/>
       <c r="E265" s="4" t="n"/>
       <c r="F265" s="3" t="n"/>
-      <c r="G265" t="inlineStr"/>
+      <c r="G265" s="0" t="inlineStr"/>
       <c r="H265" s="3" t="n"/>
       <c r="I265" s="3" t="n"/>
       <c r="J265" s="3" t="n"/>
@@ -11975,7 +12025,7 @@
       <c r="D266" s="4" t="n"/>
       <c r="E266" s="4" t="n"/>
       <c r="F266" s="3" t="n"/>
-      <c r="G266" t="inlineStr"/>
+      <c r="G266" s="0" t="inlineStr"/>
       <c r="H266" s="3" t="n"/>
       <c r="I266" s="3" t="n"/>
       <c r="J266" s="3" t="n"/>
@@ -12004,7 +12054,7 @@
       <c r="D267" s="4" t="n"/>
       <c r="E267" s="4" t="n"/>
       <c r="F267" s="3" t="n"/>
-      <c r="G267" t="inlineStr"/>
+      <c r="G267" s="0" t="inlineStr"/>
       <c r="H267" s="3" t="n"/>
       <c r="I267" s="3" t="n"/>
       <c r="J267" s="3" t="n"/>
@@ -12033,7 +12083,7 @@
       <c r="D268" s="4" t="n"/>
       <c r="E268" s="4" t="n"/>
       <c r="F268" s="3" t="n"/>
-      <c r="G268" t="inlineStr"/>
+      <c r="G268" s="0" t="inlineStr"/>
       <c r="H268" s="3" t="n"/>
       <c r="I268" s="3" t="n"/>
       <c r="J268" s="3" t="n"/>
@@ -12062,7 +12112,7 @@
       <c r="D269" s="4" t="n"/>
       <c r="E269" s="4" t="n"/>
       <c r="F269" s="3" t="n"/>
-      <c r="G269" t="inlineStr"/>
+      <c r="G269" s="0" t="inlineStr"/>
       <c r="H269" s="3" t="n"/>
       <c r="I269" s="3" t="n"/>
       <c r="J269" s="3" t="n"/>
@@ -12091,7 +12141,7 @@
       <c r="D270" s="4" t="n"/>
       <c r="E270" s="4" t="n"/>
       <c r="F270" s="3" t="n"/>
-      <c r="G270" t="inlineStr"/>
+      <c r="G270" s="0" t="inlineStr"/>
       <c r="H270" s="3" t="n"/>
       <c r="I270" s="3" t="n"/>
       <c r="J270" s="3" t="n"/>
@@ -12120,7 +12170,7 @@
       <c r="D271" s="4" t="n"/>
       <c r="E271" s="4" t="n"/>
       <c r="F271" s="3" t="n"/>
-      <c r="G271" t="inlineStr"/>
+      <c r="G271" s="0" t="inlineStr"/>
       <c r="H271" s="3" t="n"/>
       <c r="I271" s="3" t="n"/>
       <c r="J271" s="3" t="n"/>
@@ -12149,7 +12199,7 @@
       <c r="D272" s="4" t="n"/>
       <c r="E272" s="4" t="n"/>
       <c r="F272" s="3" t="n"/>
-      <c r="G272" t="inlineStr"/>
+      <c r="G272" s="0" t="inlineStr"/>
       <c r="H272" s="3" t="n"/>
       <c r="I272" s="3" t="n"/>
       <c r="J272" s="3" t="n"/>
@@ -12178,7 +12228,7 @@
       <c r="D273" s="4" t="n"/>
       <c r="E273" s="4" t="n"/>
       <c r="F273" s="3" t="n"/>
-      <c r="G273" t="inlineStr"/>
+      <c r="G273" s="0" t="inlineStr"/>
       <c r="H273" s="3" t="n"/>
       <c r="I273" s="3" t="n"/>
       <c r="J273" s="3" t="n"/>
@@ -12207,7 +12257,7 @@
       <c r="D274" s="4" t="n"/>
       <c r="E274" s="4" t="n"/>
       <c r="F274" s="3" t="n"/>
-      <c r="G274" t="inlineStr"/>
+      <c r="G274" s="0" t="inlineStr"/>
       <c r="H274" s="3" t="n"/>
       <c r="I274" s="3" t="n"/>
       <c r="J274" s="3" t="n"/>
@@ -12236,7 +12286,7 @@
       <c r="D275" s="4" t="n"/>
       <c r="E275" s="4" t="n"/>
       <c r="F275" s="3" t="n"/>
-      <c r="G275" t="inlineStr"/>
+      <c r="G275" s="0" t="inlineStr"/>
       <c r="H275" s="3" t="n"/>
       <c r="I275" s="3" t="n"/>
       <c r="J275" s="3" t="n"/>
@@ -12265,7 +12315,7 @@
       <c r="D276" s="4" t="n"/>
       <c r="E276" s="4" t="n"/>
       <c r="F276" s="3" t="n"/>
-      <c r="G276" t="inlineStr"/>
+      <c r="G276" s="0" t="inlineStr"/>
       <c r="H276" s="3" t="n"/>
       <c r="I276" s="3" t="n"/>
       <c r="J276" s="3" t="n"/>
@@ -12294,7 +12344,7 @@
       <c r="D277" s="4" t="n"/>
       <c r="E277" s="4" t="n"/>
       <c r="F277" s="3" t="n"/>
-      <c r="G277" t="inlineStr"/>
+      <c r="G277" s="0" t="inlineStr"/>
       <c r="H277" s="3" t="n"/>
       <c r="I277" s="3" t="n"/>
       <c r="J277" s="3" t="n"/>
@@ -12323,7 +12373,7 @@
       <c r="D278" s="4" t="n"/>
       <c r="E278" s="4" t="n"/>
       <c r="F278" s="3" t="n"/>
-      <c r="G278" t="inlineStr"/>
+      <c r="G278" s="0" t="inlineStr"/>
       <c r="H278" s="3" t="n"/>
       <c r="I278" s="3" t="n"/>
       <c r="J278" s="3" t="n"/>
@@ -12352,7 +12402,7 @@
       <c r="D279" s="4" t="n"/>
       <c r="E279" s="4" t="n"/>
       <c r="F279" s="3" t="n"/>
-      <c r="G279" t="inlineStr"/>
+      <c r="G279" s="0" t="inlineStr"/>
       <c r="H279" s="3" t="n"/>
       <c r="I279" s="3" t="n"/>
       <c r="J279" s="3" t="n"/>
@@ -12381,7 +12431,7 @@
       <c r="D280" s="4" t="n"/>
       <c r="E280" s="4" t="n"/>
       <c r="F280" s="3" t="n"/>
-      <c r="G280" t="inlineStr"/>
+      <c r="G280" s="0" t="inlineStr"/>
       <c r="H280" s="3" t="n"/>
       <c r="I280" s="3" t="n"/>
       <c r="J280" s="3" t="n"/>
@@ -12410,7 +12460,7 @@
       <c r="D281" s="4" t="n"/>
       <c r="E281" s="4" t="n"/>
       <c r="F281" s="3" t="n"/>
-      <c r="G281" t="inlineStr"/>
+      <c r="G281" s="0" t="inlineStr"/>
       <c r="H281" s="3" t="n"/>
       <c r="I281" s="3" t="n"/>
       <c r="J281" s="3" t="n"/>
@@ -12439,7 +12489,7 @@
       <c r="D282" s="4" t="n"/>
       <c r="E282" s="4" t="n"/>
       <c r="F282" s="3" t="n"/>
-      <c r="G282" t="inlineStr"/>
+      <c r="G282" s="0" t="inlineStr"/>
       <c r="H282" s="3" t="n"/>
       <c r="I282" s="3" t="n"/>
       <c r="J282" s="3" t="n"/>
@@ -12468,7 +12518,7 @@
       <c r="D283" s="4" t="n"/>
       <c r="E283" s="4" t="n"/>
       <c r="F283" s="3" t="n"/>
-      <c r="G283" t="inlineStr"/>
+      <c r="G283" s="0" t="inlineStr"/>
       <c r="H283" s="3" t="n"/>
       <c r="I283" s="3" t="n"/>
       <c r="J283" s="3" t="n"/>
@@ -12497,7 +12547,7 @@
       <c r="D284" s="4" t="n"/>
       <c r="E284" s="4" t="n"/>
       <c r="F284" s="3" t="n"/>
-      <c r="G284" t="inlineStr"/>
+      <c r="G284" s="0" t="inlineStr"/>
       <c r="H284" s="3" t="n"/>
       <c r="I284" s="3" t="n"/>
       <c r="J284" s="3" t="n"/>
@@ -12526,7 +12576,7 @@
       <c r="D285" s="4" t="n"/>
       <c r="E285" s="4" t="n"/>
       <c r="F285" s="3" t="n"/>
-      <c r="G285" t="inlineStr"/>
+      <c r="G285" s="0" t="inlineStr"/>
       <c r="H285" s="3" t="n"/>
       <c r="I285" s="3" t="n"/>
       <c r="J285" s="3" t="n"/>
@@ -12555,7 +12605,7 @@
       <c r="D286" s="4" t="n"/>
       <c r="E286" s="4" t="n"/>
       <c r="F286" s="3" t="n"/>
-      <c r="G286" t="inlineStr"/>
+      <c r="G286" s="0" t="inlineStr"/>
       <c r="H286" s="3" t="n"/>
       <c r="I286" s="3" t="n"/>
       <c r="J286" s="3" t="n"/>
@@ -12584,7 +12634,7 @@
       <c r="D287" s="4" t="n"/>
       <c r="E287" s="4" t="n"/>
       <c r="F287" s="3" t="n"/>
-      <c r="G287" t="inlineStr"/>
+      <c r="G287" s="0" t="inlineStr"/>
       <c r="H287" s="3" t="n"/>
       <c r="I287" s="3" t="n"/>
       <c r="J287" s="3" t="n"/>
@@ -12613,7 +12663,7 @@
       <c r="D288" s="4" t="n"/>
       <c r="E288" s="4" t="n"/>
       <c r="F288" s="3" t="n"/>
-      <c r="G288" t="inlineStr"/>
+      <c r="G288" s="0" t="inlineStr"/>
       <c r="H288" s="3" t="n"/>
       <c r="I288" s="3" t="n"/>
       <c r="J288" s="3" t="n"/>
@@ -12642,7 +12692,7 @@
       <c r="D289" s="4" t="n"/>
       <c r="E289" s="4" t="n"/>
       <c r="F289" s="3" t="n"/>
-      <c r="G289" t="inlineStr"/>
+      <c r="G289" s="0" t="inlineStr"/>
       <c r="H289" s="3" t="n"/>
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="n"/>
@@ -12671,7 +12721,7 @@
       <c r="D290" s="4" t="n"/>
       <c r="E290" s="4" t="n"/>
       <c r="F290" s="3" t="n"/>
-      <c r="G290" t="inlineStr"/>
+      <c r="G290" s="0" t="inlineStr"/>
       <c r="H290" s="3" t="n"/>
       <c r="I290" s="3" t="n"/>
       <c r="J290" s="3" t="n"/>
@@ -12700,7 +12750,7 @@
       <c r="D291" s="4" t="n"/>
       <c r="E291" s="4" t="n"/>
       <c r="F291" s="3" t="n"/>
-      <c r="G291" t="inlineStr"/>
+      <c r="G291" s="0" t="inlineStr"/>
       <c r="H291" s="3" t="n"/>
       <c r="I291" s="3" t="n"/>
       <c r="J291" s="3" t="n"/>
@@ -12729,7 +12779,7 @@
       <c r="D292" s="4" t="n"/>
       <c r="E292" s="4" t="n"/>
       <c r="F292" s="3" t="n"/>
-      <c r="G292" t="inlineStr"/>
+      <c r="G292" s="0" t="inlineStr"/>
       <c r="H292" s="3" t="n"/>
       <c r="I292" s="3" t="n"/>
       <c r="J292" s="3" t="n"/>
@@ -12758,7 +12808,7 @@
       <c r="D293" s="4" t="n"/>
       <c r="E293" s="4" t="n"/>
       <c r="F293" s="3" t="n"/>
-      <c r="G293" t="inlineStr"/>
+      <c r="G293" s="0" t="inlineStr"/>
       <c r="H293" s="3" t="n"/>
       <c r="I293" s="3" t="n"/>
       <c r="J293" s="3" t="n"/>
@@ -12787,7 +12837,7 @@
       <c r="D294" s="4" t="n"/>
       <c r="E294" s="4" t="n"/>
       <c r="F294" s="3" t="n"/>
-      <c r="G294" t="inlineStr"/>
+      <c r="G294" s="0" t="inlineStr"/>
       <c r="H294" s="3" t="n"/>
       <c r="I294" s="3" t="n"/>
       <c r="J294" s="3" t="n"/>
@@ -12816,7 +12866,7 @@
       <c r="D295" s="4" t="n"/>
       <c r="E295" s="4" t="n"/>
       <c r="F295" s="3" t="n"/>
-      <c r="G295" t="inlineStr"/>
+      <c r="G295" s="0" t="inlineStr"/>
       <c r="H295" s="3" t="n"/>
       <c r="I295" s="3" t="n"/>
       <c r="J295" s="3" t="n"/>
@@ -12845,7 +12895,7 @@
       <c r="D296" s="4" t="n"/>
       <c r="E296" s="4" t="n"/>
       <c r="F296" s="3" t="n"/>
-      <c r="G296" t="inlineStr"/>
+      <c r="G296" s="0" t="inlineStr"/>
       <c r="H296" s="3" t="n"/>
       <c r="I296" s="3" t="n"/>
       <c r="J296" s="3" t="n"/>
@@ -12874,7 +12924,7 @@
       <c r="D297" s="4" t="n"/>
       <c r="E297" s="4" t="n"/>
       <c r="F297" s="3" t="n"/>
-      <c r="G297" t="inlineStr"/>
+      <c r="G297" s="0" t="inlineStr"/>
       <c r="H297" s="3" t="n"/>
       <c r="I297" s="3" t="n"/>
       <c r="J297" s="3" t="n"/>
@@ -12903,7 +12953,7 @@
       <c r="D298" s="4" t="n"/>
       <c r="E298" s="4" t="n"/>
       <c r="F298" s="3" t="n"/>
-      <c r="G298" t="inlineStr"/>
+      <c r="G298" s="0" t="inlineStr"/>
       <c r="H298" s="3" t="n"/>
       <c r="I298" s="3" t="n"/>
       <c r="J298" s="3" t="n"/>
@@ -12932,7 +12982,7 @@
       <c r="D299" s="4" t="n"/>
       <c r="E299" s="4" t="n"/>
       <c r="F299" s="3" t="n"/>
-      <c r="G299" t="inlineStr"/>
+      <c r="G299" s="0" t="inlineStr"/>
       <c r="H299" s="3" t="n"/>
       <c r="I299" s="3" t="n"/>
       <c r="J299" s="3" t="n"/>
@@ -12961,7 +13011,7 @@
       <c r="D300" s="4" t="n"/>
       <c r="E300" s="4" t="n"/>
       <c r="F300" s="3" t="n"/>
-      <c r="G300" t="inlineStr"/>
+      <c r="G300" s="0" t="inlineStr"/>
       <c r="H300" s="3" t="n"/>
       <c r="I300" s="3" t="n"/>
       <c r="J300" s="3" t="n"/>
@@ -12990,7 +13040,7 @@
       <c r="D301" s="4" t="n"/>
       <c r="E301" s="4" t="n"/>
       <c r="F301" s="3" t="n"/>
-      <c r="G301" t="inlineStr"/>
+      <c r="G301" s="0" t="inlineStr"/>
       <c r="H301" s="3" t="n"/>
       <c r="I301" s="3" t="n"/>
       <c r="J301" s="3" t="n"/>
@@ -13019,7 +13069,7 @@
       <c r="D302" s="4" t="n"/>
       <c r="E302" s="4" t="n"/>
       <c r="F302" s="3" t="n"/>
-      <c r="G302" t="inlineStr"/>
+      <c r="G302" s="0" t="inlineStr"/>
       <c r="H302" s="3" t="n"/>
       <c r="I302" s="3" t="n"/>
       <c r="J302" s="3" t="n"/>
@@ -13048,7 +13098,7 @@
       <c r="D303" s="4" t="n"/>
       <c r="E303" s="4" t="n"/>
       <c r="F303" s="3" t="n"/>
-      <c r="G303" t="inlineStr"/>
+      <c r="G303" s="0" t="inlineStr"/>
       <c r="H303" s="3" t="n"/>
       <c r="I303" s="3" t="n"/>
       <c r="J303" s="3" t="n"/>
@@ -13077,7 +13127,7 @@
       <c r="D304" s="4" t="n"/>
       <c r="E304" s="4" t="n"/>
       <c r="F304" s="3" t="n"/>
-      <c r="G304" t="inlineStr"/>
+      <c r="G304" s="0" t="inlineStr"/>
       <c r="H304" s="3" t="n"/>
       <c r="I304" s="3" t="n"/>
       <c r="J304" s="3" t="n"/>
@@ -13106,7 +13156,7 @@
       <c r="D305" s="4" t="n"/>
       <c r="E305" s="4" t="n"/>
       <c r="F305" s="3" t="n"/>
-      <c r="G305" t="inlineStr"/>
+      <c r="G305" s="0" t="inlineStr"/>
       <c r="H305" s="3" t="n"/>
       <c r="I305" s="3" t="n"/>
       <c r="J305" s="3" t="n"/>
@@ -13135,7 +13185,7 @@
       <c r="D306" s="4" t="n"/>
       <c r="E306" s="4" t="n"/>
       <c r="F306" s="3" t="n"/>
-      <c r="G306" t="inlineStr"/>
+      <c r="G306" s="0" t="inlineStr"/>
       <c r="H306" s="3" t="n"/>
       <c r="I306" s="3" t="n"/>
       <c r="J306" s="3" t="n"/>
@@ -13164,7 +13214,7 @@
       <c r="D307" s="4" t="n"/>
       <c r="E307" s="4" t="n"/>
       <c r="F307" s="3" t="n"/>
-      <c r="G307" t="inlineStr"/>
+      <c r="G307" s="0" t="inlineStr"/>
       <c r="H307" s="3" t="n"/>
       <c r="I307" s="3" t="n"/>
       <c r="J307" s="3" t="n"/>
@@ -13193,7 +13243,7 @@
       <c r="D308" s="4" t="n"/>
       <c r="E308" s="4" t="n"/>
       <c r="F308" s="3" t="n"/>
-      <c r="G308" t="inlineStr"/>
+      <c r="G308" s="0" t="inlineStr"/>
       <c r="H308" s="3" t="n"/>
       <c r="I308" s="3" t="n"/>
       <c r="J308" s="3" t="n"/>
@@ -13222,7 +13272,7 @@
       <c r="D309" s="4" t="n"/>
       <c r="E309" s="4" t="n"/>
       <c r="F309" s="3" t="n"/>
-      <c r="G309" t="inlineStr"/>
+      <c r="G309" s="0" t="inlineStr"/>
       <c r="H309" s="3" t="n"/>
       <c r="I309" s="3" t="n"/>
       <c r="J309" s="3" t="n"/>
@@ -13251,7 +13301,7 @@
       <c r="D310" s="4" t="n"/>
       <c r="E310" s="4" t="n"/>
       <c r="F310" s="3" t="n"/>
-      <c r="G310" t="inlineStr"/>
+      <c r="G310" s="0" t="inlineStr"/>
       <c r="H310" s="3" t="n"/>
       <c r="I310" s="3" t="n"/>
       <c r="J310" s="3" t="n"/>
@@ -13280,7 +13330,7 @@
       <c r="D311" s="4" t="n"/>
       <c r="E311" s="4" t="n"/>
       <c r="F311" s="3" t="n"/>
-      <c r="G311" t="inlineStr"/>
+      <c r="G311" s="0" t="inlineStr"/>
       <c r="H311" s="3" t="n"/>
       <c r="I311" s="3" t="n"/>
       <c r="J311" s="3" t="n"/>
@@ -13309,7 +13359,7 @@
       <c r="D312" s="4" t="n"/>
       <c r="E312" s="4" t="n"/>
       <c r="F312" s="3" t="n"/>
-      <c r="G312" t="inlineStr"/>
+      <c r="G312" s="0" t="inlineStr"/>
       <c r="H312" s="3" t="n"/>
       <c r="I312" s="3" t="n"/>
       <c r="J312" s="3" t="n"/>
@@ -13338,7 +13388,7 @@
       <c r="D313" s="4" t="n"/>
       <c r="E313" s="4" t="n"/>
       <c r="F313" s="3" t="n"/>
-      <c r="G313" t="inlineStr"/>
+      <c r="G313" s="0" t="inlineStr"/>
       <c r="H313" s="3" t="n"/>
       <c r="I313" s="3" t="n"/>
       <c r="J313" s="3" t="n"/>
@@ -13367,7 +13417,7 @@
       <c r="D314" s="4" t="n"/>
       <c r="E314" s="4" t="n"/>
       <c r="F314" s="3" t="n"/>
-      <c r="G314" t="inlineStr"/>
+      <c r="G314" s="0" t="inlineStr"/>
       <c r="H314" s="3" t="n"/>
       <c r="I314" s="3" t="n"/>
       <c r="J314" s="3" t="n"/>
@@ -13396,7 +13446,7 @@
       <c r="D315" s="4" t="n"/>
       <c r="E315" s="4" t="n"/>
       <c r="F315" s="3" t="n"/>
-      <c r="G315" t="inlineStr"/>
+      <c r="G315" s="0" t="inlineStr"/>
       <c r="H315" s="3" t="n"/>
       <c r="I315" s="3" t="n"/>
       <c r="J315" s="3" t="n"/>
@@ -13425,7 +13475,7 @@
       <c r="D316" s="4" t="n"/>
       <c r="E316" s="4" t="n"/>
       <c r="F316" s="3" t="n"/>
-      <c r="G316" t="inlineStr"/>
+      <c r="G316" s="0" t="inlineStr"/>
       <c r="H316" s="3" t="n"/>
       <c r="I316" s="3" t="n"/>
       <c r="J316" s="3" t="n"/>
@@ -13454,7 +13504,7 @@
       <c r="D317" s="4" t="n"/>
       <c r="E317" s="4" t="n"/>
       <c r="F317" s="3" t="n"/>
-      <c r="G317" t="inlineStr"/>
+      <c r="G317" s="0" t="inlineStr"/>
       <c r="H317" s="3" t="n"/>
       <c r="I317" s="3" t="n"/>
       <c r="J317" s="3" t="n"/>
@@ -13483,7 +13533,7 @@
       <c r="D318" s="4" t="n"/>
       <c r="E318" s="4" t="n"/>
       <c r="F318" s="3" t="n"/>
-      <c r="G318" t="inlineStr"/>
+      <c r="G318" s="0" t="inlineStr"/>
       <c r="H318" s="3" t="n"/>
       <c r="I318" s="3" t="n"/>
       <c r="J318" s="3" t="n"/>
@@ -13512,7 +13562,7 @@
       <c r="D319" s="4" t="n"/>
       <c r="E319" s="4" t="n"/>
       <c r="F319" s="3" t="n"/>
-      <c r="G319" t="inlineStr"/>
+      <c r="G319" s="0" t="inlineStr"/>
       <c r="H319" s="3" t="n"/>
       <c r="I319" s="3" t="n"/>
       <c r="J319" s="3" t="n"/>
@@ -13541,7 +13591,7 @@
       <c r="D320" s="4" t="n"/>
       <c r="E320" s="4" t="n"/>
       <c r="F320" s="3" t="n"/>
-      <c r="G320" t="inlineStr"/>
+      <c r="G320" s="0" t="inlineStr"/>
       <c r="H320" s="3" t="n"/>
       <c r="I320" s="3" t="n"/>
       <c r="J320" s="3" t="n"/>
@@ -13570,7 +13620,7 @@
       <c r="D321" s="4" t="n"/>
       <c r="E321" s="4" t="n"/>
       <c r="F321" s="3" t="n"/>
-      <c r="G321" t="inlineStr"/>
+      <c r="G321" s="0" t="inlineStr"/>
       <c r="H321" s="3" t="n"/>
       <c r="I321" s="3" t="n"/>
       <c r="J321" s="3" t="n"/>
@@ -13599,7 +13649,7 @@
       <c r="D322" s="4" t="n"/>
       <c r="E322" s="4" t="n"/>
       <c r="F322" s="3" t="n"/>
-      <c r="G322" t="inlineStr"/>
+      <c r="G322" s="0" t="inlineStr"/>
       <c r="H322" s="3" t="n"/>
       <c r="I322" s="3" t="n"/>
       <c r="J322" s="3" t="n"/>
@@ -13628,7 +13678,7 @@
       <c r="D323" s="4" t="n"/>
       <c r="E323" s="4" t="n"/>
       <c r="F323" s="3" t="n"/>
-      <c r="G323" t="inlineStr"/>
+      <c r="G323" s="0" t="inlineStr"/>
       <c r="H323" s="3" t="n"/>
       <c r="I323" s="3" t="n"/>
       <c r="J323" s="3" t="n"/>
@@ -13657,7 +13707,7 @@
       <c r="D324" s="4" t="n"/>
       <c r="E324" s="4" t="n"/>
       <c r="F324" s="3" t="n"/>
-      <c r="G324" t="inlineStr"/>
+      <c r="G324" s="0" t="inlineStr"/>
       <c r="H324" s="3" t="n"/>
       <c r="I324" s="3" t="n"/>
       <c r="J324" s="3" t="n"/>
@@ -13686,7 +13736,7 @@
       <c r="D325" s="4" t="n"/>
       <c r="E325" s="4" t="n"/>
       <c r="F325" s="3" t="n"/>
-      <c r="G325" t="inlineStr"/>
+      <c r="G325" s="0" t="inlineStr"/>
       <c r="H325" s="3" t="n"/>
       <c r="I325" s="3" t="n"/>
       <c r="J325" s="3" t="n"/>
@@ -13715,7 +13765,7 @@
       <c r="D326" s="4" t="n"/>
       <c r="E326" s="4" t="n"/>
       <c r="F326" s="3" t="n"/>
-      <c r="G326" t="inlineStr"/>
+      <c r="G326" s="0" t="inlineStr"/>
       <c r="H326" s="3" t="n"/>
       <c r="I326" s="3" t="n"/>
       <c r="J326" s="3" t="n"/>
@@ -13744,7 +13794,7 @@
       <c r="D327" s="4" t="n"/>
       <c r="E327" s="4" t="n"/>
       <c r="F327" s="3" t="n"/>
-      <c r="G327" t="inlineStr"/>
+      <c r="G327" s="0" t="inlineStr"/>
       <c r="H327" s="3" t="n"/>
       <c r="I327" s="3" t="n"/>
       <c r="J327" s="3" t="n"/>
@@ -13773,7 +13823,7 @@
       <c r="D328" s="4" t="n"/>
       <c r="E328" s="4" t="n"/>
       <c r="F328" s="3" t="n"/>
-      <c r="G328" t="inlineStr"/>
+      <c r="G328" s="0" t="inlineStr"/>
       <c r="H328" s="3" t="n"/>
       <c r="I328" s="3" t="n"/>
       <c r="J328" s="3" t="n"/>
@@ -13802,7 +13852,7 @@
       <c r="D329" s="4" t="n"/>
       <c r="E329" s="4" t="n"/>
       <c r="F329" s="3" t="n"/>
-      <c r="G329" t="inlineStr"/>
+      <c r="G329" s="0" t="inlineStr"/>
       <c r="H329" s="3" t="n"/>
       <c r="I329" s="3" t="n"/>
       <c r="J329" s="3" t="n"/>
@@ -13831,7 +13881,7 @@
       <c r="D330" s="4" t="n"/>
       <c r="E330" s="4" t="n"/>
       <c r="F330" s="3" t="n"/>
-      <c r="G330" t="inlineStr"/>
+      <c r="G330" s="0" t="inlineStr"/>
       <c r="H330" s="3" t="n"/>
       <c r="I330" s="3" t="n"/>
       <c r="J330" s="3" t="n"/>
@@ -13860,7 +13910,7 @@
       <c r="D331" s="4" t="n"/>
       <c r="E331" s="4" t="n"/>
       <c r="F331" s="3" t="n"/>
-      <c r="G331" t="inlineStr"/>
+      <c r="G331" s="0" t="inlineStr"/>
       <c r="H331" s="3" t="n"/>
       <c r="I331" s="3" t="n"/>
       <c r="J331" s="3" t="n"/>
@@ -13889,7 +13939,7 @@
       <c r="D332" s="4" t="n"/>
       <c r="E332" s="4" t="n"/>
       <c r="F332" s="3" t="n"/>
-      <c r="G332" t="inlineStr"/>
+      <c r="G332" s="0" t="inlineStr"/>
       <c r="H332" s="3" t="n"/>
       <c r="I332" s="3" t="n"/>
       <c r="J332" s="3" t="n"/>
@@ -13918,7 +13968,7 @@
       <c r="D333" s="4" t="n"/>
       <c r="E333" s="4" t="n"/>
       <c r="F333" s="3" t="n"/>
-      <c r="G333" t="inlineStr"/>
+      <c r="G333" s="0" t="inlineStr"/>
       <c r="H333" s="3" t="n"/>
       <c r="I333" s="3" t="n"/>
       <c r="J333" s="3" t="n"/>
@@ -13947,7 +13997,7 @@
       <c r="D334" s="4" t="n"/>
       <c r="E334" s="4" t="n"/>
       <c r="F334" s="3" t="n"/>
-      <c r="G334" t="inlineStr"/>
+      <c r="G334" s="0" t="inlineStr"/>
       <c r="H334" s="3" t="n"/>
       <c r="I334" s="3" t="n"/>
       <c r="J334" s="3" t="n"/>
@@ -13976,7 +14026,7 @@
       <c r="D335" s="4" t="n"/>
       <c r="E335" s="4" t="n"/>
       <c r="F335" s="3" t="n"/>
-      <c r="G335" t="inlineStr"/>
+      <c r="G335" s="0" t="inlineStr"/>
       <c r="H335" s="3" t="n"/>
       <c r="I335" s="3" t="n"/>
       <c r="J335" s="3" t="n"/>
@@ -14005,7 +14055,7 @@
       <c r="D336" s="4" t="n"/>
       <c r="E336" s="4" t="n"/>
       <c r="F336" s="3" t="n"/>
-      <c r="G336" t="inlineStr"/>
+      <c r="G336" s="0" t="inlineStr"/>
       <c r="H336" s="3" t="n"/>
       <c r="I336" s="3" t="n"/>
       <c r="J336" s="3" t="n"/>
@@ -14034,7 +14084,7 @@
       <c r="D337" s="4" t="n"/>
       <c r="E337" s="4" t="n"/>
       <c r="F337" s="3" t="n"/>
-      <c r="G337" t="inlineStr"/>
+      <c r="G337" s="0" t="inlineStr"/>
       <c r="H337" s="3" t="n"/>
       <c r="I337" s="3" t="n"/>
       <c r="J337" s="3" t="n"/>
@@ -14063,7 +14113,7 @@
       <c r="D338" s="4" t="n"/>
       <c r="E338" s="4" t="n"/>
       <c r="F338" s="3" t="n"/>
-      <c r="G338" t="inlineStr"/>
+      <c r="G338" s="0" t="inlineStr"/>
       <c r="H338" s="3" t="n"/>
       <c r="I338" s="3" t="n"/>
       <c r="J338" s="3" t="n"/>
@@ -14092,7 +14142,7 @@
       <c r="D339" s="4" t="n"/>
       <c r="E339" s="4" t="n"/>
       <c r="F339" s="3" t="n"/>
-      <c r="G339" t="inlineStr"/>
+      <c r="G339" s="0" t="inlineStr"/>
       <c r="H339" s="3" t="n"/>
       <c r="I339" s="3" t="n"/>
       <c r="J339" s="3" t="n"/>
@@ -14121,7 +14171,7 @@
       <c r="D340" s="4" t="n"/>
       <c r="E340" s="4" t="n"/>
       <c r="F340" s="3" t="n"/>
-      <c r="G340" t="inlineStr"/>
+      <c r="G340" s="0" t="inlineStr"/>
       <c r="H340" s="3" t="n"/>
       <c r="I340" s="3" t="n"/>
       <c r="J340" s="3" t="n"/>
@@ -14150,7 +14200,7 @@
       <c r="D341" s="4" t="n"/>
       <c r="E341" s="4" t="n"/>
       <c r="F341" s="3" t="n"/>
-      <c r="G341" t="inlineStr"/>
+      <c r="G341" s="0" t="inlineStr"/>
       <c r="H341" s="3" t="n"/>
       <c r="I341" s="3" t="n"/>
       <c r="J341" s="3" t="n"/>
@@ -14179,7 +14229,7 @@
       <c r="D342" s="4" t="n"/>
       <c r="E342" s="4" t="n"/>
       <c r="F342" s="3" t="n"/>
-      <c r="G342" t="inlineStr"/>
+      <c r="G342" s="0" t="inlineStr"/>
       <c r="H342" s="3" t="n"/>
       <c r="I342" s="3" t="n"/>
       <c r="J342" s="3" t="n"/>
@@ -14208,7 +14258,7 @@
       <c r="D343" s="4" t="n"/>
       <c r="E343" s="4" t="n"/>
       <c r="F343" s="3" t="n"/>
-      <c r="G343" t="inlineStr"/>
+      <c r="G343" s="0" t="inlineStr"/>
       <c r="H343" s="3" t="n"/>
       <c r="I343" s="3" t="n"/>
       <c r="J343" s="3" t="n"/>
@@ -14237,7 +14287,7 @@
       <c r="D344" s="4" t="n"/>
       <c r="E344" s="4" t="n"/>
       <c r="F344" s="3" t="n"/>
-      <c r="G344" t="inlineStr"/>
+      <c r="G344" s="0" t="inlineStr"/>
       <c r="H344" s="3" t="n"/>
       <c r="I344" s="3" t="n"/>
       <c r="J344" s="3" t="n"/>
@@ -14266,7 +14316,7 @@
       <c r="D345" s="4" t="n"/>
       <c r="E345" s="4" t="n"/>
       <c r="F345" s="3" t="n"/>
-      <c r="G345" t="inlineStr"/>
+      <c r="G345" s="0" t="inlineStr"/>
       <c r="H345" s="3" t="n"/>
       <c r="I345" s="3" t="n"/>
       <c r="J345" s="3" t="n"/>
@@ -14295,7 +14345,7 @@
       <c r="D346" s="4" t="n"/>
       <c r="E346" s="4" t="n"/>
       <c r="F346" s="3" t="n"/>
-      <c r="G346" t="inlineStr"/>
+      <c r="G346" s="0" t="inlineStr"/>
       <c r="H346" s="3" t="n"/>
       <c r="I346" s="3" t="n"/>
       <c r="J346" s="3" t="n"/>
@@ -14324,7 +14374,7 @@
       <c r="D347" s="4" t="n"/>
       <c r="E347" s="4" t="n"/>
       <c r="F347" s="3" t="n"/>
-      <c r="G347" t="inlineStr"/>
+      <c r="G347" s="0" t="inlineStr"/>
       <c r="H347" s="3" t="n"/>
       <c r="I347" s="3" t="n"/>
       <c r="J347" s="3" t="n"/>
@@ -14353,7 +14403,7 @@
       <c r="D348" s="4" t="n"/>
       <c r="E348" s="4" t="n"/>
       <c r="F348" s="3" t="n"/>
-      <c r="G348" t="inlineStr"/>
+      <c r="G348" s="0" t="inlineStr"/>
       <c r="H348" s="3" t="n"/>
       <c r="I348" s="3" t="n"/>
       <c r="J348" s="3" t="n"/>
@@ -14382,7 +14432,7 @@
       <c r="D349" s="4" t="n"/>
       <c r="E349" s="4" t="n"/>
       <c r="F349" s="3" t="n"/>
-      <c r="G349" t="inlineStr"/>
+      <c r="G349" s="0" t="inlineStr"/>
       <c r="H349" s="3" t="n"/>
       <c r="I349" s="3" t="n"/>
       <c r="J349" s="3" t="n"/>
@@ -14411,7 +14461,7 @@
       <c r="D350" s="4" t="n"/>
       <c r="E350" s="4" t="n"/>
       <c r="F350" s="3" t="n"/>
-      <c r="G350" t="inlineStr"/>
+      <c r="G350" s="0" t="inlineStr"/>
       <c r="H350" s="3" t="n"/>
       <c r="I350" s="3" t="n"/>
       <c r="J350" s="3" t="n"/>
@@ -14440,7 +14490,7 @@
       <c r="D351" s="4" t="n"/>
       <c r="E351" s="4" t="n"/>
       <c r="F351" s="3" t="n"/>
-      <c r="G351" t="inlineStr"/>
+      <c r="G351" s="0" t="inlineStr"/>
       <c r="H351" s="3" t="n"/>
       <c r="I351" s="3" t="n"/>
       <c r="J351" s="3" t="n"/>
@@ -14469,7 +14519,7 @@
       <c r="D352" s="4" t="n"/>
       <c r="E352" s="4" t="n"/>
       <c r="F352" s="3" t="n"/>
-      <c r="G352" t="inlineStr"/>
+      <c r="G352" s="0" t="inlineStr"/>
       <c r="H352" s="3" t="n"/>
       <c r="I352" s="3" t="n"/>
       <c r="J352" s="3" t="n"/>
@@ -14498,7 +14548,7 @@
       <c r="D353" s="4" t="n"/>
       <c r="E353" s="4" t="n"/>
       <c r="F353" s="3" t="n"/>
-      <c r="G353" t="inlineStr"/>
+      <c r="G353" s="0" t="inlineStr"/>
       <c r="H353" s="3" t="n"/>
       <c r="I353" s="3" t="n"/>
       <c r="J353" s="3" t="n"/>
@@ -14527,7 +14577,7 @@
       <c r="D354" s="4" t="n"/>
       <c r="E354" s="4" t="n"/>
       <c r="F354" s="3" t="n"/>
-      <c r="G354" t="inlineStr"/>
+      <c r="G354" s="0" t="inlineStr"/>
       <c r="H354" s="3" t="n"/>
       <c r="I354" s="3" t="n"/>
       <c r="J354" s="3" t="n"/>
@@ -14556,7 +14606,7 @@
       <c r="D355" s="4" t="n"/>
       <c r="E355" s="4" t="n"/>
       <c r="F355" s="3" t="n"/>
-      <c r="G355" t="inlineStr"/>
+      <c r="G355" s="0" t="inlineStr"/>
       <c r="H355" s="3" t="n"/>
       <c r="I355" s="3" t="n"/>
       <c r="J355" s="3" t="n"/>
@@ -14585,7 +14635,7 @@
       <c r="D356" s="4" t="n"/>
       <c r="E356" s="4" t="n"/>
       <c r="F356" s="3" t="n"/>
-      <c r="G356" t="inlineStr"/>
+      <c r="G356" s="0" t="inlineStr"/>
       <c r="H356" s="3" t="n"/>
       <c r="I356" s="3" t="n"/>
       <c r="J356" s="3" t="n"/>
@@ -14614,7 +14664,7 @@
       <c r="D357" s="4" t="n"/>
       <c r="E357" s="4" t="n"/>
       <c r="F357" s="3" t="n"/>
-      <c r="G357" t="inlineStr"/>
+      <c r="G357" s="0" t="inlineStr"/>
       <c r="H357" s="3" t="n"/>
       <c r="I357" s="3" t="n"/>
       <c r="J357" s="3" t="n"/>
@@ -14643,7 +14693,7 @@
       <c r="D358" s="4" t="n"/>
       <c r="E358" s="4" t="n"/>
       <c r="F358" s="3" t="n"/>
-      <c r="G358" t="inlineStr"/>
+      <c r="G358" s="0" t="inlineStr"/>
       <c r="H358" s="3" t="n"/>
       <c r="I358" s="3" t="n"/>
       <c r="J358" s="3" t="n"/>
@@ -14672,7 +14722,7 @@
       <c r="D359" s="4" t="n"/>
       <c r="E359" s="4" t="n"/>
       <c r="F359" s="3" t="n"/>
-      <c r="G359" t="inlineStr"/>
+      <c r="G359" s="0" t="inlineStr"/>
       <c r="H359" s="3" t="n"/>
       <c r="I359" s="3" t="n"/>
       <c r="J359" s="3" t="n"/>
@@ -14701,7 +14751,7 @@
       <c r="D360" s="4" t="n"/>
       <c r="E360" s="4" t="n"/>
       <c r="F360" s="3" t="n"/>
-      <c r="G360" t="inlineStr"/>
+      <c r="G360" s="0" t="inlineStr"/>
       <c r="H360" s="3" t="n"/>
       <c r="I360" s="3" t="n"/>
       <c r="J360" s="3" t="n"/>
@@ -14730,7 +14780,7 @@
       <c r="D361" s="4" t="n"/>
       <c r="E361" s="4" t="n"/>
       <c r="F361" s="3" t="n"/>
-      <c r="G361" t="inlineStr"/>
+      <c r="G361" s="0" t="inlineStr"/>
       <c r="H361" s="3" t="n"/>
       <c r="I361" s="3" t="n"/>
       <c r="J361" s="3" t="n"/>
@@ -14759,7 +14809,7 @@
       <c r="D362" s="4" t="n"/>
       <c r="E362" s="4" t="n"/>
       <c r="F362" s="3" t="n"/>
-      <c r="G362" t="inlineStr"/>
+      <c r="G362" s="0" t="inlineStr"/>
       <c r="H362" s="3" t="n"/>
       <c r="I362" s="3" t="n"/>
       <c r="J362" s="3" t="n"/>
@@ -14788,7 +14838,7 @@
       <c r="D363" s="4" t="n"/>
       <c r="E363" s="4" t="n"/>
       <c r="F363" s="3" t="n"/>
-      <c r="G363" t="inlineStr"/>
+      <c r="G363" s="0" t="inlineStr"/>
       <c r="H363" s="3" t="n"/>
       <c r="I363" s="3" t="n"/>
       <c r="J363" s="3" t="n"/>
@@ -14817,7 +14867,7 @@
       <c r="D364" s="4" t="n"/>
       <c r="E364" s="4" t="n"/>
       <c r="F364" s="3" t="n"/>
-      <c r="G364" t="inlineStr"/>
+      <c r="G364" s="0" t="inlineStr"/>
       <c r="H364" s="3" t="n"/>
       <c r="I364" s="3" t="n"/>
       <c r="J364" s="3" t="n"/>
@@ -14846,7 +14896,7 @@
       <c r="D365" s="4" t="n"/>
       <c r="E365" s="4" t="n"/>
       <c r="F365" s="3" t="n"/>
-      <c r="G365" t="inlineStr"/>
+      <c r="G365" s="0" t="inlineStr"/>
       <c r="H365" s="3" t="n"/>
       <c r="I365" s="3" t="n"/>
       <c r="J365" s="3" t="n"/>
@@ -14875,7 +14925,7 @@
       <c r="D366" s="4" t="n"/>
       <c r="E366" s="4" t="n"/>
       <c r="F366" s="3" t="n"/>
-      <c r="G366" t="inlineStr"/>
+      <c r="G366" s="0" t="inlineStr"/>
       <c r="H366" s="3" t="n"/>
       <c r="I366" s="3" t="n"/>
       <c r="J366" s="3" t="n"/>
@@ -14904,7 +14954,7 @@
       <c r="D367" s="4" t="n"/>
       <c r="E367" s="4" t="n"/>
       <c r="F367" s="3" t="n"/>
-      <c r="G367" t="inlineStr"/>
+      <c r="G367" s="0" t="inlineStr"/>
       <c r="H367" s="3" t="n"/>
       <c r="I367" s="3" t="n"/>
       <c r="J367" s="3" t="n"/>
@@ -14933,7 +14983,7 @@
       <c r="D368" s="4" t="n"/>
       <c r="E368" s="4" t="n"/>
       <c r="F368" s="3" t="n"/>
-      <c r="G368" t="inlineStr"/>
+      <c r="G368" s="0" t="inlineStr"/>
       <c r="H368" s="3" t="n"/>
       <c r="I368" s="3" t="n"/>
       <c r="J368" s="3" t="n"/>
@@ -14962,7 +15012,7 @@
       <c r="D369" s="4" t="n"/>
       <c r="E369" s="4" t="n"/>
       <c r="F369" s="3" t="n"/>
-      <c r="G369" t="inlineStr"/>
+      <c r="G369" s="0" t="inlineStr"/>
       <c r="H369" s="3" t="n"/>
       <c r="I369" s="3" t="n"/>
       <c r="J369" s="3" t="n"/>
@@ -14991,7 +15041,7 @@
       <c r="D370" s="4" t="n"/>
       <c r="E370" s="4" t="n"/>
       <c r="F370" s="3" t="n"/>
-      <c r="G370" t="inlineStr"/>
+      <c r="G370" s="0" t="inlineStr"/>
       <c r="H370" s="3" t="n"/>
       <c r="I370" s="3" t="n"/>
       <c r="J370" s="3" t="n"/>
@@ -15020,7 +15070,7 @@
       <c r="D371" s="4" t="n"/>
       <c r="E371" s="4" t="n"/>
       <c r="F371" s="3" t="n"/>
-      <c r="G371" t="inlineStr"/>
+      <c r="G371" s="0" t="inlineStr"/>
       <c r="H371" s="3" t="n"/>
       <c r="I371" s="3" t="n"/>
       <c r="J371" s="3" t="n"/>
@@ -15049,7 +15099,7 @@
       <c r="D372" s="4" t="n"/>
       <c r="E372" s="4" t="n"/>
       <c r="F372" s="3" t="n"/>
-      <c r="G372" t="inlineStr"/>
+      <c r="G372" s="0" t="inlineStr"/>
       <c r="H372" s="3" t="n"/>
       <c r="I372" s="3" t="n"/>
       <c r="J372" s="3" t="n"/>
@@ -15078,7 +15128,7 @@
       <c r="D373" s="4" t="n"/>
       <c r="E373" s="4" t="n"/>
       <c r="F373" s="3" t="n"/>
-      <c r="G373" t="inlineStr"/>
+      <c r="G373" s="0" t="inlineStr"/>
       <c r="H373" s="3" t="n"/>
       <c r="I373" s="3" t="n"/>
       <c r="J373" s="3" t="n"/>
@@ -15107,7 +15157,7 @@
       <c r="D374" s="4" t="n"/>
       <c r="E374" s="4" t="n"/>
       <c r="F374" s="3" t="n"/>
-      <c r="G374" t="inlineStr"/>
+      <c r="G374" s="0" t="inlineStr"/>
       <c r="H374" s="3" t="n"/>
       <c r="I374" s="3" t="n"/>
       <c r="J374" s="3" t="n"/>
@@ -15136,7 +15186,7 @@
       <c r="D375" s="4" t="n"/>
       <c r="E375" s="4" t="n"/>
       <c r="F375" s="3" t="n"/>
-      <c r="G375" t="inlineStr"/>
+      <c r="G375" s="0" t="inlineStr"/>
       <c r="H375" s="3" t="n"/>
       <c r="I375" s="3" t="n"/>
       <c r="J375" s="3" t="n"/>
@@ -15165,7 +15215,7 @@
       <c r="D376" s="4" t="n"/>
       <c r="E376" s="4" t="n"/>
       <c r="F376" s="3" t="n"/>
-      <c r="G376" t="inlineStr"/>
+      <c r="G376" s="0" t="inlineStr"/>
       <c r="H376" s="3" t="n"/>
       <c r="I376" s="3" t="n"/>
       <c r="J376" s="3" t="n"/>
@@ -15194,7 +15244,7 @@
       <c r="D377" s="4" t="n"/>
       <c r="E377" s="4" t="n"/>
       <c r="F377" s="3" t="n"/>
-      <c r="G377" t="inlineStr"/>
+      <c r="G377" s="0" t="inlineStr"/>
       <c r="H377" s="3" t="n"/>
       <c r="I377" s="3" t="n"/>
       <c r="J377" s="3" t="n"/>
@@ -15223,7 +15273,7 @@
       <c r="D378" s="4" t="n"/>
       <c r="E378" s="4" t="n"/>
       <c r="F378" s="3" t="n"/>
-      <c r="G378" t="inlineStr"/>
+      <c r="G378" s="0" t="inlineStr"/>
       <c r="H378" s="3" t="n"/>
       <c r="I378" s="3" t="n"/>
       <c r="J378" s="3" t="n"/>
@@ -15252,7 +15302,7 @@
       <c r="D379" s="4" t="n"/>
       <c r="E379" s="4" t="n"/>
       <c r="F379" s="3" t="n"/>
-      <c r="G379" t="inlineStr"/>
+      <c r="G379" s="0" t="inlineStr"/>
       <c r="H379" s="3" t="n"/>
       <c r="I379" s="3" t="n"/>
       <c r="J379" s="3" t="n"/>
@@ -15281,7 +15331,7 @@
       <c r="D380" s="4" t="n"/>
       <c r="E380" s="4" t="n"/>
       <c r="F380" s="3" t="n"/>
-      <c r="G380" t="inlineStr"/>
+      <c r="G380" s="0" t="inlineStr"/>
       <c r="H380" s="3" t="n"/>
       <c r="I380" s="3" t="n"/>
       <c r="J380" s="3" t="n"/>
@@ -15310,7 +15360,7 @@
       <c r="D381" s="4" t="n"/>
       <c r="E381" s="4" t="n"/>
       <c r="F381" s="3" t="n"/>
-      <c r="G381" t="inlineStr"/>
+      <c r="G381" s="0" t="inlineStr"/>
       <c r="H381" s="3" t="n"/>
       <c r="I381" s="3" t="n"/>
       <c r="J381" s="3" t="n"/>
@@ -15339,7 +15389,7 @@
       <c r="D382" s="4" t="n"/>
       <c r="E382" s="4" t="n"/>
       <c r="F382" s="3" t="n"/>
-      <c r="G382" t="inlineStr"/>
+      <c r="G382" s="0" t="inlineStr"/>
       <c r="H382" s="3" t="n"/>
       <c r="I382" s="3" t="n"/>
       <c r="J382" s="3" t="n"/>
@@ -15368,7 +15418,7 @@
       <c r="D383" s="4" t="n"/>
       <c r="E383" s="4" t="n"/>
       <c r="F383" s="3" t="n"/>
-      <c r="G383" t="inlineStr"/>
+      <c r="G383" s="0" t="inlineStr"/>
       <c r="H383" s="3" t="n"/>
       <c r="I383" s="3" t="n"/>
       <c r="J383" s="3" t="n"/>
@@ -15397,7 +15447,7 @@
       <c r="D384" s="4" t="n"/>
       <c r="E384" s="4" t="n"/>
       <c r="F384" s="3" t="n"/>
-      <c r="G384" t="inlineStr"/>
+      <c r="G384" s="0" t="inlineStr"/>
       <c r="H384" s="3" t="n"/>
       <c r="I384" s="3" t="n"/>
       <c r="J384" s="3" t="n"/>
@@ -15426,7 +15476,7 @@
       <c r="D385" s="4" t="n"/>
       <c r="E385" s="4" t="n"/>
       <c r="F385" s="3" t="n"/>
-      <c r="G385" t="inlineStr"/>
+      <c r="G385" s="0" t="inlineStr"/>
       <c r="H385" s="3" t="n"/>
       <c r="I385" s="3" t="n"/>
       <c r="J385" s="3" t="n"/>
@@ -15455,7 +15505,7 @@
       <c r="D386" s="4" t="n"/>
       <c r="E386" s="4" t="n"/>
       <c r="F386" s="3" t="n"/>
-      <c r="G386" t="inlineStr"/>
+      <c r="G386" s="0" t="inlineStr"/>
       <c r="H386" s="3" t="n"/>
       <c r="I386" s="3" t="n"/>
       <c r="J386" s="3" t="n"/>
@@ -15484,7 +15534,7 @@
       <c r="D387" s="4" t="n"/>
       <c r="E387" s="4" t="n"/>
       <c r="F387" s="3" t="n"/>
-      <c r="G387" t="inlineStr"/>
+      <c r="G387" s="0" t="inlineStr"/>
       <c r="H387" s="3" t="n"/>
       <c r="I387" s="3" t="n"/>
       <c r="J387" s="3" t="n"/>
@@ -15513,7 +15563,7 @@
       <c r="D388" s="4" t="n"/>
       <c r="E388" s="4" t="n"/>
       <c r="F388" s="3" t="n"/>
-      <c r="G388" t="inlineStr"/>
+      <c r="G388" s="0" t="inlineStr"/>
       <c r="H388" s="3" t="n"/>
       <c r="I388" s="3" t="n"/>
       <c r="J388" s="3" t="n"/>
@@ -15542,7 +15592,7 @@
       <c r="D389" s="4" t="n"/>
       <c r="E389" s="4" t="n"/>
       <c r="F389" s="3" t="n"/>
-      <c r="G389" t="inlineStr"/>
+      <c r="G389" s="0" t="inlineStr"/>
       <c r="H389" s="3" t="n"/>
       <c r="I389" s="3" t="n"/>
       <c r="J389" s="3" t="n"/>
@@ -15571,7 +15621,7 @@
       <c r="D390" s="4" t="n"/>
       <c r="E390" s="4" t="n"/>
       <c r="F390" s="3" t="n"/>
-      <c r="G390" t="inlineStr"/>
+      <c r="G390" s="0" t="inlineStr"/>
       <c r="H390" s="3" t="n"/>
       <c r="I390" s="3" t="n"/>
       <c r="J390" s="3" t="n"/>
@@ -15600,7 +15650,7 @@
       <c r="D391" s="4" t="n"/>
       <c r="E391" s="4" t="n"/>
       <c r="F391" s="3" t="n"/>
-      <c r="G391" t="inlineStr"/>
+      <c r="G391" s="0" t="inlineStr"/>
       <c r="H391" s="3" t="n"/>
       <c r="I391" s="3" t="n"/>
       <c r="J391" s="3" t="n"/>
@@ -15629,7 +15679,7 @@
       <c r="D392" s="4" t="n"/>
       <c r="E392" s="4" t="n"/>
       <c r="F392" s="3" t="n"/>
-      <c r="G392" t="inlineStr"/>
+      <c r="G392" s="0" t="inlineStr"/>
       <c r="H392" s="3" t="n"/>
       <c r="I392" s="3" t="n"/>
       <c r="J392" s="3" t="n"/>
@@ -15658,7 +15708,7 @@
       <c r="D393" s="4" t="n"/>
       <c r="E393" s="4" t="n"/>
       <c r="F393" s="3" t="n"/>
-      <c r="G393" t="inlineStr"/>
+      <c r="G393" s="0" t="inlineStr"/>
       <c r="H393" s="3" t="n"/>
       <c r="I393" s="3" t="n"/>
       <c r="J393" s="3" t="n"/>
@@ -15687,7 +15737,7 @@
       <c r="D394" s="4" t="n"/>
       <c r="E394" s="4" t="n"/>
       <c r="F394" s="3" t="n"/>
-      <c r="G394" t="inlineStr"/>
+      <c r="G394" s="0" t="inlineStr"/>
       <c r="H394" s="3" t="n"/>
       <c r="I394" s="3" t="n"/>
       <c r="J394" s="3" t="n"/>
@@ -15716,7 +15766,7 @@
       <c r="D395" s="4" t="n"/>
       <c r="E395" s="4" t="n"/>
       <c r="F395" s="3" t="n"/>
-      <c r="G395" t="inlineStr"/>
+      <c r="G395" s="0" t="inlineStr"/>
       <c r="H395" s="3" t="n"/>
       <c r="I395" s="3" t="n"/>
       <c r="J395" s="3" t="n"/>
@@ -15745,7 +15795,7 @@
       <c r="D396" s="4" t="n"/>
       <c r="E396" s="4" t="n"/>
       <c r="F396" s="3" t="n"/>
-      <c r="G396" t="inlineStr"/>
+      <c r="G396" s="0" t="inlineStr"/>
       <c r="H396" s="3" t="n"/>
       <c r="I396" s="3" t="n"/>
       <c r="J396" s="3" t="n"/>
@@ -15774,7 +15824,7 @@
       <c r="D397" s="4" t="n"/>
       <c r="E397" s="4" t="n"/>
       <c r="F397" s="3" t="n"/>
-      <c r="G397" t="inlineStr"/>
+      <c r="G397" s="0" t="inlineStr"/>
       <c r="H397" s="3" t="n"/>
       <c r="I397" s="3" t="n"/>
       <c r="J397" s="3" t="n"/>
@@ -15803,7 +15853,7 @@
       <c r="D398" s="4" t="n"/>
       <c r="E398" s="4" t="n"/>
       <c r="F398" s="3" t="n"/>
-      <c r="G398" t="inlineStr"/>
+      <c r="G398" s="0" t="inlineStr"/>
       <c r="H398" s="3" t="n"/>
       <c r="I398" s="3" t="n"/>
       <c r="J398" s="3" t="n"/>
@@ -15832,7 +15882,7 @@
       <c r="D399" s="4" t="n"/>
       <c r="E399" s="4" t="n"/>
       <c r="F399" s="3" t="n"/>
-      <c r="G399" t="inlineStr"/>
+      <c r="G399" s="0" t="inlineStr"/>
       <c r="H399" s="3" t="n"/>
       <c r="I399" s="3" t="n"/>
       <c r="J399" s="3" t="n"/>
@@ -15861,7 +15911,7 @@
       <c r="D400" s="4" t="n"/>
       <c r="E400" s="4" t="n"/>
       <c r="F400" s="3" t="n"/>
-      <c r="G400" t="inlineStr"/>
+      <c r="G400" s="0" t="inlineStr"/>
       <c r="H400" s="3" t="n"/>
       <c r="I400" s="3" t="n"/>
       <c r="J400" s="3" t="n"/>
@@ -15890,7 +15940,7 @@
       <c r="D401" s="4" t="n"/>
       <c r="E401" s="4" t="n"/>
       <c r="F401" s="3" t="n"/>
-      <c r="G401" t="inlineStr"/>
+      <c r="G401" s="0" t="inlineStr"/>
       <c r="H401" s="3" t="n"/>
       <c r="I401" s="3" t="n"/>
       <c r="J401" s="3" t="n"/>
@@ -15919,7 +15969,7 @@
       <c r="D402" s="4" t="n"/>
       <c r="E402" s="4" t="n"/>
       <c r="F402" s="3" t="n"/>
-      <c r="G402" t="inlineStr"/>
+      <c r="G402" s="0" t="inlineStr"/>
       <c r="H402" s="3" t="n"/>
       <c r="I402" s="3" t="n"/>
       <c r="J402" s="3" t="n"/>
@@ -15948,7 +15998,7 @@
       <c r="D403" s="4" t="n"/>
       <c r="E403" s="4" t="n"/>
       <c r="F403" s="3" t="n"/>
-      <c r="G403" t="inlineStr"/>
+      <c r="G403" s="0" t="inlineStr"/>
       <c r="H403" s="3" t="n"/>
       <c r="I403" s="3" t="n"/>
       <c r="J403" s="3" t="n"/>
@@ -15977,7 +16027,7 @@
       <c r="D404" s="4" t="n"/>
       <c r="E404" s="4" t="n"/>
       <c r="F404" s="3" t="n"/>
-      <c r="G404" t="inlineStr"/>
+      <c r="G404" s="0" t="inlineStr"/>
       <c r="H404" s="3" t="n"/>
       <c r="I404" s="3" t="n"/>
       <c r="J404" s="3" t="n"/>
@@ -16006,7 +16056,7 @@
       <c r="D405" s="4" t="n"/>
       <c r="E405" s="4" t="n"/>
       <c r="F405" s="3" t="n"/>
-      <c r="G405" t="inlineStr"/>
+      <c r="G405" s="0" t="inlineStr"/>
       <c r="H405" s="3" t="n"/>
       <c r="I405" s="3" t="n"/>
       <c r="J405" s="3" t="n"/>
@@ -16035,7 +16085,7 @@
       <c r="D406" s="4" t="n"/>
       <c r="E406" s="4" t="n"/>
       <c r="F406" s="3" t="n"/>
-      <c r="G406" t="inlineStr"/>
+      <c r="G406" s="0" t="inlineStr"/>
       <c r="H406" s="3" t="n"/>
       <c r="I406" s="3" t="n"/>
       <c r="J406" s="3" t="n"/>
@@ -16064,7 +16114,7 @@
       <c r="D407" s="4" t="n"/>
       <c r="E407" s="4" t="n"/>
       <c r="F407" s="3" t="n"/>
-      <c r="G407" t="inlineStr"/>
+      <c r="G407" s="0" t="inlineStr"/>
       <c r="H407" s="3" t="n"/>
       <c r="I407" s="3" t="n"/>
       <c r="J407" s="3" t="n"/>
@@ -16093,7 +16143,7 @@
       <c r="D408" s="4" t="n"/>
       <c r="E408" s="4" t="n"/>
       <c r="F408" s="3" t="n"/>
-      <c r="G408" t="inlineStr"/>
+      <c r="G408" s="0" t="inlineStr"/>
       <c r="H408" s="3" t="n"/>
       <c r="I408" s="3" t="n"/>
       <c r="J408" s="3" t="n"/>
@@ -16122,7 +16172,7 @@
       <c r="D409" s="4" t="n"/>
       <c r="E409" s="4" t="n"/>
       <c r="F409" s="3" t="n"/>
-      <c r="G409" t="inlineStr"/>
+      <c r="G409" s="0" t="inlineStr"/>
       <c r="H409" s="3" t="n"/>
       <c r="I409" s="3" t="n"/>
       <c r="J409" s="3" t="n"/>
@@ -16151,7 +16201,7 @@
       <c r="D410" s="4" t="n"/>
       <c r="E410" s="4" t="n"/>
       <c r="F410" s="3" t="n"/>
-      <c r="G410" t="inlineStr"/>
+      <c r="G410" s="0" t="inlineStr"/>
       <c r="H410" s="3" t="n"/>
       <c r="I410" s="3" t="n"/>
       <c r="J410" s="3" t="n"/>
@@ -16180,7 +16230,7 @@
       <c r="D411" s="4" t="n"/>
       <c r="E411" s="4" t="n"/>
       <c r="F411" s="3" t="n"/>
-      <c r="G411" t="inlineStr"/>
+      <c r="G411" s="0" t="inlineStr"/>
       <c r="H411" s="3" t="n"/>
       <c r="I411" s="3" t="n"/>
       <c r="J411" s="3" t="n"/>
@@ -16209,7 +16259,7 @@
       <c r="D412" s="4" t="n"/>
       <c r="E412" s="4" t="n"/>
       <c r="F412" s="3" t="n"/>
-      <c r="G412" t="inlineStr"/>
+      <c r="G412" s="0" t="inlineStr"/>
       <c r="H412" s="3" t="n"/>
       <c r="I412" s="3" t="n"/>
       <c r="J412" s="3" t="n"/>
@@ -16238,7 +16288,7 @@
       <c r="D413" s="4" t="n"/>
       <c r="E413" s="4" t="n"/>
       <c r="F413" s="3" t="n"/>
-      <c r="G413" t="inlineStr"/>
+      <c r="G413" s="0" t="inlineStr"/>
       <c r="H413" s="3" t="n"/>
       <c r="I413" s="3" t="n"/>
       <c r="J413" s="3" t="n"/>
@@ -16267,7 +16317,7 @@
       <c r="D414" s="4" t="n"/>
       <c r="E414" s="4" t="n"/>
       <c r="F414" s="3" t="n"/>
-      <c r="G414" t="inlineStr"/>
+      <c r="G414" s="0" t="inlineStr"/>
       <c r="H414" s="3" t="n"/>
       <c r="I414" s="3" t="n"/>
       <c r="J414" s="3" t="n"/>
@@ -16296,7 +16346,7 @@
       <c r="D415" s="4" t="n"/>
       <c r="E415" s="4" t="n"/>
       <c r="F415" s="3" t="n"/>
-      <c r="G415" t="inlineStr"/>
+      <c r="G415" s="0" t="inlineStr"/>
       <c r="H415" s="3" t="n"/>
       <c r="I415" s="3" t="n"/>
       <c r="J415" s="3" t="n"/>
@@ -16325,7 +16375,7 @@
       <c r="D416" s="4" t="n"/>
       <c r="E416" s="4" t="n"/>
       <c r="F416" s="3" t="n"/>
-      <c r="G416" t="inlineStr"/>
+      <c r="G416" s="0" t="inlineStr"/>
       <c r="H416" s="3" t="n"/>
       <c r="I416" s="3" t="n"/>
       <c r="J416" s="3" t="n"/>
@@ -16354,7 +16404,7 @@
       <c r="D417" s="4" t="n"/>
       <c r="E417" s="4" t="n"/>
       <c r="F417" s="3" t="n"/>
-      <c r="G417" t="inlineStr"/>
+      <c r="G417" s="0" t="inlineStr"/>
       <c r="H417" s="3" t="n"/>
       <c r="I417" s="3" t="n"/>
       <c r="J417" s="3" t="n"/>
@@ -16383,7 +16433,7 @@
       <c r="D418" s="4" t="n"/>
       <c r="E418" s="4" t="n"/>
       <c r="F418" s="3" t="n"/>
-      <c r="G418" t="inlineStr"/>
+      <c r="G418" s="0" t="inlineStr"/>
       <c r="H418" s="3" t="n"/>
       <c r="I418" s="3" t="n"/>
       <c r="J418" s="3" t="n"/>
@@ -16412,7 +16462,7 @@
       <c r="D419" s="4" t="n"/>
       <c r="E419" s="4" t="n"/>
       <c r="F419" s="3" t="n"/>
-      <c r="G419" t="inlineStr"/>
+      <c r="G419" s="0" t="inlineStr"/>
       <c r="H419" s="3" t="n"/>
       <c r="I419" s="3" t="n"/>
       <c r="J419" s="3" t="n"/>
@@ -16441,7 +16491,7 @@
       <c r="D420" s="4" t="n"/>
       <c r="E420" s="4" t="n"/>
       <c r="F420" s="3" t="n"/>
-      <c r="G420" t="inlineStr"/>
+      <c r="G420" s="0" t="inlineStr"/>
       <c r="H420" s="3" t="n"/>
       <c r="I420" s="3" t="n"/>
       <c r="J420" s="3" t="n"/>
@@ -16470,7 +16520,7 @@
       <c r="D421" s="4" t="n"/>
       <c r="E421" s="4" t="n"/>
       <c r="F421" s="3" t="n"/>
-      <c r="G421" t="inlineStr"/>
+      <c r="G421" s="0" t="inlineStr"/>
       <c r="H421" s="3" t="n"/>
       <c r="I421" s="3" t="n"/>
       <c r="J421" s="3" t="n"/>
@@ -16499,7 +16549,7 @@
       <c r="D422" s="4" t="n"/>
       <c r="E422" s="4" t="n"/>
       <c r="F422" s="3" t="n"/>
-      <c r="G422" t="inlineStr"/>
+      <c r="G422" s="0" t="inlineStr"/>
       <c r="H422" s="3" t="n"/>
       <c r="I422" s="3" t="n"/>
       <c r="J422" s="3" t="n"/>
@@ -16528,7 +16578,7 @@
       <c r="D423" s="4" t="n"/>
       <c r="E423" s="4" t="n"/>
       <c r="F423" s="3" t="n"/>
-      <c r="G423" t="inlineStr"/>
+      <c r="G423" s="0" t="inlineStr"/>
       <c r="H423" s="3" t="n"/>
       <c r="I423" s="3" t="n"/>
       <c r="J423" s="3" t="n"/>
@@ -16557,7 +16607,7 @@
       <c r="D424" s="4" t="n"/>
       <c r="E424" s="4" t="n"/>
       <c r="F424" s="3" t="n"/>
-      <c r="G424" t="inlineStr"/>
+      <c r="G424" s="0" t="inlineStr"/>
       <c r="H424" s="3" t="n"/>
       <c r="I424" s="3" t="n"/>
       <c r="J424" s="3" t="n"/>
@@ -16586,7 +16636,7 @@
       <c r="D425" s="4" t="n"/>
       <c r="E425" s="4" t="n"/>
       <c r="F425" s="3" t="n"/>
-      <c r="G425" t="inlineStr"/>
+      <c r="G425" s="0" t="inlineStr"/>
       <c r="H425" s="3" t="n"/>
       <c r="I425" s="3" t="n"/>
       <c r="J425" s="3" t="n"/>
@@ -16615,7 +16665,7 @@
       <c r="D426" s="4" t="n"/>
       <c r="E426" s="4" t="n"/>
       <c r="F426" s="3" t="n"/>
-      <c r="G426" t="inlineStr"/>
+      <c r="G426" s="0" t="inlineStr"/>
       <c r="H426" s="3" t="n"/>
       <c r="I426" s="3" t="n"/>
       <c r="J426" s="3" t="n"/>
@@ -16644,7 +16694,7 @@
       <c r="D427" s="4" t="n"/>
       <c r="E427" s="4" t="n"/>
       <c r="F427" s="3" t="n"/>
-      <c r="G427" t="inlineStr"/>
+      <c r="G427" s="0" t="inlineStr"/>
       <c r="H427" s="3" t="n"/>
       <c r="I427" s="3" t="n"/>
       <c r="J427" s="3" t="n"/>
@@ -16673,7 +16723,7 @@
       <c r="D428" s="4" t="n"/>
       <c r="E428" s="4" t="n"/>
       <c r="F428" s="3" t="n"/>
-      <c r="G428" t="inlineStr"/>
+      <c r="G428" s="0" t="inlineStr"/>
       <c r="H428" s="3" t="n"/>
       <c r="I428" s="3" t="n"/>
       <c r="J428" s="3" t="n"/>
@@ -16702,7 +16752,7 @@
       <c r="D429" s="4" t="n"/>
       <c r="E429" s="4" t="n"/>
       <c r="F429" s="3" t="n"/>
-      <c r="G429" t="inlineStr"/>
+      <c r="G429" s="0" t="inlineStr"/>
       <c r="H429" s="3" t="n"/>
       <c r="I429" s="3" t="n"/>
       <c r="J429" s="3" t="n"/>
@@ -16731,7 +16781,7 @@
       <c r="D430" s="4" t="n"/>
       <c r="E430" s="4" t="n"/>
       <c r="F430" s="3" t="n"/>
-      <c r="G430" t="inlineStr"/>
+      <c r="G430" s="0" t="inlineStr"/>
       <c r="H430" s="3" t="n"/>
       <c r="I430" s="3" t="n"/>
       <c r="J430" s="3" t="n"/>
@@ -16760,7 +16810,7 @@
       <c r="D431" s="4" t="n"/>
       <c r="E431" s="4" t="n"/>
       <c r="F431" s="3" t="n"/>
-      <c r="G431" t="inlineStr"/>
+      <c r="G431" s="0" t="inlineStr"/>
       <c r="H431" s="3" t="n"/>
       <c r="I431" s="3" t="n"/>
       <c r="J431" s="3" t="n"/>
@@ -16789,7 +16839,7 @@
       <c r="D432" s="4" t="n"/>
       <c r="E432" s="4" t="n"/>
       <c r="F432" s="3" t="n"/>
-      <c r="G432" t="inlineStr"/>
+      <c r="G432" s="0" t="inlineStr"/>
       <c r="H432" s="3" t="n"/>
       <c r="I432" s="3" t="n"/>
       <c r="J432" s="3" t="n"/>
@@ -16818,7 +16868,7 @@
       <c r="D433" s="4" t="n"/>
       <c r="E433" s="4" t="n"/>
       <c r="F433" s="3" t="n"/>
-      <c r="G433" t="inlineStr"/>
+      <c r="G433" s="0" t="inlineStr"/>
       <c r="H433" s="3" t="n"/>
       <c r="I433" s="3" t="n"/>
       <c r="J433" s="3" t="n"/>
@@ -16847,7 +16897,7 @@
       <c r="D434" s="4" t="n"/>
       <c r="E434" s="4" t="n"/>
       <c r="F434" s="3" t="n"/>
-      <c r="G434" t="inlineStr"/>
+      <c r="G434" s="0" t="inlineStr"/>
       <c r="H434" s="3" t="n"/>
       <c r="I434" s="3" t="n"/>
       <c r="J434" s="3" t="n"/>
@@ -16876,7 +16926,7 @@
       <c r="D435" s="4" t="n"/>
       <c r="E435" s="4" t="n"/>
       <c r="F435" s="3" t="n"/>
-      <c r="G435" t="inlineStr"/>
+      <c r="G435" s="0" t="inlineStr"/>
       <c r="H435" s="3" t="n"/>
       <c r="I435" s="3" t="n"/>
       <c r="J435" s="3" t="n"/>
@@ -16905,7 +16955,7 @@
       <c r="D436" s="4" t="n"/>
       <c r="E436" s="4" t="n"/>
       <c r="F436" s="3" t="n"/>
-      <c r="G436" t="inlineStr"/>
+      <c r="G436" s="0" t="inlineStr"/>
       <c r="H436" s="3" t="n"/>
       <c r="I436" s="3" t="n"/>
       <c r="J436" s="3" t="n"/>
@@ -16934,7 +16984,7 @@
       <c r="D437" s="4" t="n"/>
       <c r="E437" s="4" t="n"/>
       <c r="F437" s="3" t="n"/>
-      <c r="G437" t="inlineStr"/>
+      <c r="G437" s="0" t="inlineStr"/>
       <c r="H437" s="3" t="n"/>
       <c r="I437" s="3" t="n"/>
       <c r="J437" s="3" t="n"/>
@@ -16963,7 +17013,7 @@
       <c r="D438" s="4" t="n"/>
       <c r="E438" s="4" t="n"/>
       <c r="F438" s="3" t="n"/>
-      <c r="G438" t="inlineStr"/>
+      <c r="G438" s="0" t="inlineStr"/>
       <c r="H438" s="3" t="n"/>
       <c r="I438" s="3" t="n"/>
       <c r="J438" s="3" t="n"/>
@@ -16992,7 +17042,7 @@
       <c r="D439" s="4" t="n"/>
       <c r="E439" s="4" t="n"/>
       <c r="F439" s="3" t="n"/>
-      <c r="G439" t="inlineStr"/>
+      <c r="G439" s="0" t="inlineStr"/>
       <c r="H439" s="3" t="n"/>
       <c r="I439" s="3" t="n"/>
       <c r="J439" s="3" t="n"/>
@@ -17021,7 +17071,7 @@
       <c r="D440" s="4" t="n"/>
       <c r="E440" s="4" t="n"/>
       <c r="F440" s="3" t="n"/>
-      <c r="G440" t="inlineStr"/>
+      <c r="G440" s="0" t="inlineStr"/>
       <c r="H440" s="3" t="n"/>
       <c r="I440" s="3" t="n"/>
       <c r="J440" s="3" t="n"/>
@@ -17050,7 +17100,7 @@
       <c r="D441" s="4" t="n"/>
       <c r="E441" s="4" t="n"/>
       <c r="F441" s="3" t="n"/>
-      <c r="G441" t="inlineStr"/>
+      <c r="G441" s="0" t="inlineStr"/>
       <c r="H441" s="3" t="n"/>
       <c r="I441" s="3" t="n"/>
       <c r="J441" s="3" t="n"/>
@@ -17079,7 +17129,7 @@
       <c r="D442" s="4" t="n"/>
       <c r="E442" s="4" t="n"/>
       <c r="F442" s="3" t="n"/>
-      <c r="G442" t="inlineStr"/>
+      <c r="G442" s="0" t="inlineStr"/>
       <c r="H442" s="3" t="n"/>
       <c r="I442" s="3" t="n"/>
       <c r="J442" s="3" t="n"/>
@@ -17108,7 +17158,7 @@
       <c r="D443" s="4" t="n"/>
       <c r="E443" s="4" t="n"/>
       <c r="F443" s="3" t="n"/>
-      <c r="G443" t="inlineStr"/>
+      <c r="G443" s="0" t="inlineStr"/>
       <c r="H443" s="3" t="n"/>
       <c r="I443" s="3" t="n"/>
       <c r="J443" s="3" t="n"/>
@@ -17137,7 +17187,7 @@
       <c r="D444" s="4" t="n"/>
       <c r="E444" s="4" t="n"/>
       <c r="F444" s="3" t="n"/>
-      <c r="G444" t="inlineStr"/>
+      <c r="G444" s="0" t="inlineStr"/>
       <c r="H444" s="3" t="n"/>
       <c r="I444" s="3" t="n"/>
       <c r="J444" s="3" t="n"/>
@@ -17166,7 +17216,7 @@
       <c r="D445" s="4" t="n"/>
       <c r="E445" s="4" t="n"/>
       <c r="F445" s="3" t="n"/>
-      <c r="G445" t="inlineStr"/>
+      <c r="G445" s="0" t="inlineStr"/>
       <c r="H445" s="3" t="n"/>
       <c r="I445" s="3" t="n"/>
       <c r="J445" s="3" t="n"/>
@@ -17195,7 +17245,7 @@
       <c r="D446" s="4" t="n"/>
       <c r="E446" s="4" t="n"/>
       <c r="F446" s="3" t="n"/>
-      <c r="G446" t="inlineStr"/>
+      <c r="G446" s="0" t="inlineStr"/>
       <c r="H446" s="3" t="n"/>
       <c r="I446" s="3" t="n"/>
       <c r="J446" s="3" t="n"/>
@@ -17224,7 +17274,7 @@
       <c r="D447" s="4" t="n"/>
       <c r="E447" s="4" t="n"/>
       <c r="F447" s="3" t="n"/>
-      <c r="G447" t="inlineStr"/>
+      <c r="G447" s="0" t="inlineStr"/>
       <c r="H447" s="3" t="n"/>
       <c r="I447" s="3" t="n"/>
       <c r="J447" s="3" t="n"/>
@@ -17253,7 +17303,7 @@
       <c r="D448" s="4" t="n"/>
       <c r="E448" s="4" t="n"/>
       <c r="F448" s="3" t="n"/>
-      <c r="G448" t="inlineStr"/>
+      <c r="G448" s="0" t="inlineStr"/>
       <c r="H448" s="3" t="n"/>
       <c r="I448" s="3" t="n"/>
       <c r="J448" s="3" t="n"/>
@@ -17282,7 +17332,7 @@
       <c r="D449" s="4" t="n"/>
       <c r="E449" s="4" t="n"/>
       <c r="F449" s="3" t="n"/>
-      <c r="G449" t="inlineStr"/>
+      <c r="G449" s="0" t="inlineStr"/>
       <c r="H449" s="3" t="n"/>
       <c r="I449" s="3" t="n"/>
       <c r="J449" s="3" t="n"/>
@@ -17311,7 +17361,7 @@
       <c r="D450" s="4" t="n"/>
       <c r="E450" s="4" t="n"/>
       <c r="F450" s="3" t="n"/>
-      <c r="G450" t="inlineStr"/>
+      <c r="G450" s="0" t="inlineStr"/>
       <c r="H450" s="3" t="n"/>
       <c r="I450" s="3" t="n"/>
       <c r="J450" s="3" t="n"/>
@@ -17340,7 +17390,7 @@
       <c r="D451" s="4" t="n"/>
       <c r="E451" s="4" t="n"/>
       <c r="F451" s="3" t="n"/>
-      <c r="G451" t="inlineStr"/>
+      <c r="G451" s="0" t="inlineStr"/>
       <c r="H451" s="3" t="n"/>
       <c r="I451" s="3" t="n"/>
       <c r="J451" s="3" t="n"/>
@@ -17369,7 +17419,7 @@
       <c r="D452" s="4" t="n"/>
       <c r="E452" s="4" t="n"/>
       <c r="F452" s="3" t="n"/>
-      <c r="G452" t="inlineStr"/>
+      <c r="G452" s="0" t="inlineStr"/>
       <c r="H452" s="3" t="n"/>
       <c r="I452" s="3" t="n"/>
       <c r="J452" s="3" t="n"/>
@@ -17398,7 +17448,7 @@
       <c r="D453" s="4" t="n"/>
       <c r="E453" s="4" t="n"/>
       <c r="F453" s="3" t="n"/>
-      <c r="G453" t="inlineStr"/>
+      <c r="G453" s="0" t="inlineStr"/>
       <c r="H453" s="3" t="n"/>
       <c r="I453" s="3" t="n"/>
       <c r="J453" s="3" t="n"/>
@@ -17427,7 +17477,7 @@
       <c r="D454" s="4" t="n"/>
       <c r="E454" s="4" t="n"/>
       <c r="F454" s="3" t="n"/>
-      <c r="G454" t="inlineStr"/>
+      <c r="G454" s="0" t="inlineStr"/>
       <c r="H454" s="3" t="n"/>
       <c r="I454" s="3" t="n"/>
       <c r="J454" s="3" t="n"/>
@@ -17456,7 +17506,7 @@
       <c r="D455" s="4" t="n"/>
       <c r="E455" s="4" t="n"/>
       <c r="F455" s="3" t="n"/>
-      <c r="G455" t="inlineStr"/>
+      <c r="G455" s="0" t="inlineStr"/>
       <c r="H455" s="3" t="n"/>
       <c r="I455" s="3" t="n"/>
       <c r="J455" s="3" t="n"/>
@@ -17485,7 +17535,7 @@
       <c r="D456" s="4" t="n"/>
       <c r="E456" s="4" t="n"/>
       <c r="F456" s="3" t="n"/>
-      <c r="G456" t="inlineStr"/>
+      <c r="G456" s="0" t="inlineStr"/>
       <c r="H456" s="3" t="n"/>
       <c r="I456" s="3" t="n"/>
       <c r="J456" s="3" t="n"/>
@@ -17514,7 +17564,7 @@
       <c r="D457" s="4" t="n"/>
       <c r="E457" s="4" t="n"/>
       <c r="F457" s="3" t="n"/>
-      <c r="G457" t="inlineStr"/>
+      <c r="G457" s="0" t="inlineStr"/>
       <c r="H457" s="3" t="n"/>
       <c r="I457" s="3" t="n"/>
       <c r="J457" s="3" t="n"/>
@@ -17543,7 +17593,7 @@
       <c r="D458" s="4" t="n"/>
       <c r="E458" s="4" t="n"/>
       <c r="F458" s="3" t="n"/>
-      <c r="G458" t="inlineStr"/>
+      <c r="G458" s="0" t="inlineStr"/>
       <c r="H458" s="3" t="n"/>
       <c r="I458" s="3" t="n"/>
       <c r="J458" s="3" t="n"/>
@@ -17572,7 +17622,7 @@
       <c r="D459" s="4" t="n"/>
       <c r="E459" s="4" t="n"/>
       <c r="F459" s="3" t="n"/>
-      <c r="G459" t="inlineStr"/>
+      <c r="G459" s="0" t="inlineStr"/>
       <c r="H459" s="3" t="n"/>
       <c r="I459" s="3" t="n"/>
       <c r="J459" s="3" t="n"/>
@@ -17601,7 +17651,7 @@
       <c r="D460" s="4" t="n"/>
       <c r="E460" s="4" t="n"/>
       <c r="F460" s="3" t="n"/>
-      <c r="G460" t="inlineStr"/>
+      <c r="G460" s="0" t="inlineStr"/>
       <c r="H460" s="3" t="n"/>
       <c r="I460" s="3" t="n"/>
       <c r="J460" s="3" t="n"/>
@@ -17630,7 +17680,7 @@
       <c r="D461" s="4" t="n"/>
       <c r="E461" s="4" t="n"/>
       <c r="F461" s="3" t="n"/>
-      <c r="G461" t="inlineStr"/>
+      <c r="G461" s="0" t="inlineStr"/>
       <c r="H461" s="3" t="n"/>
       <c r="I461" s="3" t="n"/>
       <c r="J461" s="3" t="n"/>
@@ -17659,7 +17709,7 @@
       <c r="D462" s="4" t="n"/>
       <c r="E462" s="4" t="n"/>
       <c r="F462" s="3" t="n"/>
-      <c r="G462" t="inlineStr"/>
+      <c r="G462" s="0" t="inlineStr"/>
       <c r="H462" s="3" t="n"/>
       <c r="I462" s="3" t="n"/>
       <c r="J462" s="3" t="n"/>
@@ -17688,7 +17738,7 @@
       <c r="D463" s="4" t="n"/>
       <c r="E463" s="4" t="n"/>
       <c r="F463" s="3" t="n"/>
-      <c r="G463" t="inlineStr"/>
+      <c r="G463" s="0" t="inlineStr"/>
       <c r="H463" s="3" t="n"/>
       <c r="I463" s="3" t="n"/>
       <c r="J463" s="3" t="n"/>
@@ -17717,7 +17767,7 @@
       <c r="D464" s="4" t="n"/>
       <c r="E464" s="4" t="n"/>
       <c r="F464" s="3" t="n"/>
-      <c r="G464" t="inlineStr"/>
+      <c r="G464" s="0" t="inlineStr"/>
       <c r="H464" s="3" t="n"/>
       <c r="I464" s="3" t="n"/>
       <c r="J464" s="3" t="n"/>
@@ -17746,7 +17796,7 @@
       <c r="D465" s="4" t="n"/>
       <c r="E465" s="4" t="n"/>
       <c r="F465" s="3" t="n"/>
-      <c r="G465" t="inlineStr"/>
+      <c r="G465" s="0" t="inlineStr"/>
       <c r="H465" s="3" t="n"/>
       <c r="I465" s="3" t="n"/>
       <c r="J465" s="3" t="n"/>
@@ -17775,7 +17825,7 @@
       <c r="D466" s="4" t="n"/>
       <c r="E466" s="4" t="n"/>
       <c r="F466" s="3" t="n"/>
-      <c r="G466" t="inlineStr"/>
+      <c r="G466" s="0" t="inlineStr"/>
       <c r="H466" s="3" t="n"/>
       <c r="I466" s="3" t="n"/>
       <c r="J466" s="3" t="n"/>
@@ -17804,7 +17854,7 @@
       <c r="D467" s="4" t="n"/>
       <c r="E467" s="4" t="n"/>
       <c r="F467" s="3" t="n"/>
-      <c r="G467" t="inlineStr"/>
+      <c r="G467" s="0" t="inlineStr"/>
       <c r="H467" s="3" t="n"/>
       <c r="I467" s="3" t="n"/>
       <c r="J467" s="3" t="n"/>
@@ -17833,7 +17883,7 @@
       <c r="D468" s="4" t="n"/>
       <c r="E468" s="4" t="n"/>
       <c r="F468" s="3" t="n"/>
-      <c r="G468" t="inlineStr"/>
+      <c r="G468" s="0" t="inlineStr"/>
       <c r="H468" s="3" t="n"/>
       <c r="I468" s="3" t="n"/>
       <c r="J468" s="3" t="n"/>
@@ -17862,7 +17912,7 @@
       <c r="D469" s="4" t="n"/>
       <c r="E469" s="4" t="n"/>
       <c r="F469" s="3" t="n"/>
-      <c r="G469" t="inlineStr"/>
+      <c r="G469" s="0" t="inlineStr"/>
       <c r="H469" s="3" t="n"/>
       <c r="I469" s="3" t="n"/>
       <c r="J469" s="3" t="n"/>
@@ -17891,7 +17941,7 @@
       <c r="D470" s="4" t="n"/>
       <c r="E470" s="4" t="n"/>
       <c r="F470" s="3" t="n"/>
-      <c r="G470" t="inlineStr"/>
+      <c r="G470" s="0" t="inlineStr"/>
       <c r="H470" s="3" t="n"/>
       <c r="I470" s="3" t="n"/>
       <c r="J470" s="3" t="n"/>
@@ -17920,7 +17970,7 @@
       <c r="D471" s="4" t="n"/>
       <c r="E471" s="4" t="n"/>
       <c r="F471" s="3" t="n"/>
-      <c r="G471" t="inlineStr"/>
+      <c r="G471" s="0" t="inlineStr"/>
       <c r="H471" s="3" t="n"/>
       <c r="I471" s="3" t="n"/>
       <c r="J471" s="3" t="n"/>
@@ -17949,7 +17999,7 @@
       <c r="D472" s="4" t="n"/>
       <c r="E472" s="4" t="n"/>
       <c r="F472" s="3" t="n"/>
-      <c r="G472" t="inlineStr"/>
+      <c r="G472" s="0" t="inlineStr"/>
       <c r="H472" s="3" t="n"/>
       <c r="I472" s="3" t="n"/>
       <c r="J472" s="3" t="n"/>
@@ -17978,7 +18028,7 @@
       <c r="D473" s="4" t="n"/>
       <c r="E473" s="4" t="n"/>
       <c r="F473" s="3" t="n"/>
-      <c r="G473" t="inlineStr"/>
+      <c r="G473" s="0" t="inlineStr"/>
       <c r="H473" s="3" t="n"/>
       <c r="I473" s="3" t="n"/>
       <c r="J473" s="3" t="n"/>
@@ -18007,7 +18057,7 @@
       <c r="D474" s="4" t="n"/>
       <c r="E474" s="4" t="n"/>
       <c r="F474" s="3" t="n"/>
-      <c r="G474" t="inlineStr"/>
+      <c r="G474" s="0" t="inlineStr"/>
       <c r="H474" s="3" t="n"/>
       <c r="I474" s="3" t="n"/>
       <c r="J474" s="3" t="n"/>
@@ -18036,7 +18086,7 @@
       <c r="D475" s="4" t="n"/>
       <c r="E475" s="4" t="n"/>
       <c r="F475" s="3" t="n"/>
-      <c r="G475" t="inlineStr"/>
+      <c r="G475" s="0" t="inlineStr"/>
       <c r="H475" s="3" t="n"/>
       <c r="I475" s="3" t="n"/>
       <c r="J475" s="3" t="n"/>
@@ -18065,7 +18115,7 @@
       <c r="D476" s="4" t="n"/>
       <c r="E476" s="4" t="n"/>
       <c r="F476" s="3" t="n"/>
-      <c r="G476" t="inlineStr"/>
+      <c r="G476" s="0" t="inlineStr"/>
       <c r="H476" s="3" t="n"/>
       <c r="I476" s="3" t="n"/>
       <c r="J476" s="3" t="n"/>
@@ -18094,7 +18144,7 @@
       <c r="D477" s="4" t="n"/>
       <c r="E477" s="4" t="n"/>
       <c r="F477" s="3" t="n"/>
-      <c r="G477" t="inlineStr"/>
+      <c r="G477" s="0" t="inlineStr"/>
       <c r="H477" s="3" t="n"/>
       <c r="I477" s="3" t="n"/>
       <c r="J477" s="3" t="n"/>
@@ -18123,7 +18173,7 @@
       <c r="D478" s="4" t="n"/>
       <c r="E478" s="4" t="n"/>
       <c r="F478" s="3" t="n"/>
-      <c r="G478" t="inlineStr"/>
+      <c r="G478" s="0" t="inlineStr"/>
       <c r="H478" s="3" t="n"/>
       <c r="I478" s="3" t="n"/>
       <c r="J478" s="3" t="n"/>
@@ -18152,7 +18202,7 @@
       <c r="D479" s="4" t="n"/>
       <c r="E479" s="4" t="n"/>
       <c r="F479" s="3" t="n"/>
-      <c r="G479" t="inlineStr"/>
+      <c r="G479" s="0" t="inlineStr"/>
       <c r="H479" s="3" t="n"/>
       <c r="I479" s="3" t="n"/>
       <c r="J479" s="3" t="n"/>
@@ -18181,7 +18231,7 @@
       <c r="D480" s="4" t="n"/>
       <c r="E480" s="4" t="n"/>
       <c r="F480" s="3" t="n"/>
-      <c r="G480" t="inlineStr"/>
+      <c r="G480" s="0" t="inlineStr"/>
       <c r="H480" s="3" t="n"/>
       <c r="I480" s="3" t="n"/>
       <c r="J480" s="3" t="n"/>
@@ -18210,7 +18260,7 @@
       <c r="D481" s="4" t="n"/>
       <c r="E481" s="4" t="n"/>
       <c r="F481" s="3" t="n"/>
-      <c r="G481" t="inlineStr"/>
+      <c r="G481" s="0" t="inlineStr"/>
       <c r="H481" s="3" t="n"/>
       <c r="I481" s="3" t="n"/>
       <c r="J481" s="3" t="n"/>
@@ -18239,7 +18289,7 @@
       <c r="D482" s="4" t="n"/>
       <c r="E482" s="4" t="n"/>
       <c r="F482" s="3" t="n"/>
-      <c r="G482" t="inlineStr"/>
+      <c r="G482" s="0" t="inlineStr"/>
       <c r="H482" s="3" t="n"/>
       <c r="I482" s="3" t="n"/>
       <c r="J482" s="3" t="n"/>
@@ -18268,7 +18318,7 @@
       <c r="D483" s="4" t="n"/>
       <c r="E483" s="4" t="n"/>
       <c r="F483" s="3" t="n"/>
-      <c r="G483" t="inlineStr"/>
+      <c r="G483" s="0" t="inlineStr"/>
       <c r="H483" s="3" t="n"/>
       <c r="I483" s="3" t="n"/>
       <c r="J483" s="3" t="n"/>
@@ -18297,7 +18347,7 @@
       <c r="D484" s="4" t="n"/>
       <c r="E484" s="4" t="n"/>
       <c r="F484" s="3" t="n"/>
-      <c r="G484" t="inlineStr"/>
+      <c r="G484" s="0" t="inlineStr"/>
       <c r="H484" s="3" t="n"/>
       <c r="I484" s="3" t="n"/>
       <c r="J484" s="3" t="n"/>
@@ -18326,7 +18376,7 @@
       <c r="D485" s="4" t="n"/>
       <c r="E485" s="4" t="n"/>
       <c r="F485" s="3" t="n"/>
-      <c r="G485" t="inlineStr"/>
+      <c r="G485" s="0" t="inlineStr"/>
       <c r="H485" s="3" t="n"/>
       <c r="I485" s="3" t="n"/>
       <c r="J485" s="3" t="n"/>
@@ -18355,7 +18405,7 @@
       <c r="D486" s="4" t="n"/>
       <c r="E486" s="4" t="n"/>
       <c r="F486" s="3" t="n"/>
-      <c r="G486" t="inlineStr"/>
+      <c r="G486" s="0" t="inlineStr"/>
       <c r="H486" s="3" t="n"/>
       <c r="I486" s="3" t="n"/>
       <c r="J486" s="3" t="n"/>
@@ -18384,7 +18434,7 @@
       <c r="D487" s="4" t="n"/>
       <c r="E487" s="4" t="n"/>
       <c r="F487" s="3" t="n"/>
-      <c r="G487" t="inlineStr"/>
+      <c r="G487" s="0" t="inlineStr"/>
       <c r="H487" s="3" t="n"/>
       <c r="I487" s="3" t="n"/>
       <c r="J487" s="3" t="n"/>
@@ -18413,7 +18463,7 @@
       <c r="D488" s="4" t="n"/>
       <c r="E488" s="4" t="n"/>
       <c r="F488" s="3" t="n"/>
-      <c r="G488" t="inlineStr"/>
+      <c r="G488" s="0" t="inlineStr"/>
       <c r="H488" s="3" t="n"/>
       <c r="I488" s="3" t="n"/>
       <c r="J488" s="3" t="n"/>
@@ -18442,7 +18492,7 @@
       <c r="D489" s="4" t="n"/>
       <c r="E489" s="4" t="n"/>
       <c r="F489" s="3" t="n"/>
-      <c r="G489" t="inlineStr"/>
+      <c r="G489" s="0" t="inlineStr"/>
       <c r="H489" s="3" t="n"/>
       <c r="I489" s="3" t="n"/>
       <c r="J489" s="3" t="n"/>
@@ -18471,7 +18521,7 @@
       <c r="D490" s="4" t="n"/>
       <c r="E490" s="4" t="n"/>
       <c r="F490" s="3" t="n"/>
-      <c r="G490" t="inlineStr"/>
+      <c r="G490" s="0" t="inlineStr"/>
       <c r="H490" s="3" t="n"/>
       <c r="I490" s="3" t="n"/>
       <c r="J490" s="3" t="n"/>
@@ -18500,7 +18550,7 @@
       <c r="D491" s="4" t="n"/>
       <c r="E491" s="4" t="n"/>
       <c r="F491" s="3" t="n"/>
-      <c r="G491" t="inlineStr"/>
+      <c r="G491" s="0" t="inlineStr"/>
       <c r="H491" s="3" t="n"/>
       <c r="I491" s="3" t="n"/>
       <c r="J491" s="3" t="n"/>
@@ -18529,7 +18579,7 @@
       <c r="D492" s="4" t="n"/>
       <c r="E492" s="4" t="n"/>
       <c r="F492" s="3" t="n"/>
-      <c r="G492" t="inlineStr"/>
+      <c r="G492" s="0" t="inlineStr"/>
       <c r="H492" s="3" t="n"/>
       <c r="I492" s="3" t="n"/>
       <c r="J492" s="3" t="n"/>
@@ -18558,7 +18608,7 @@
       <c r="D493" s="4" t="n"/>
       <c r="E493" s="4" t="n"/>
       <c r="F493" s="3" t="n"/>
-      <c r="G493" t="inlineStr"/>
+      <c r="G493" s="0" t="inlineStr"/>
       <c r="H493" s="3" t="n"/>
       <c r="I493" s="3" t="n"/>
       <c r="J493" s="3" t="n"/>
@@ -18587,7 +18637,7 @@
       <c r="D494" s="4" t="n"/>
       <c r="E494" s="4" t="n"/>
       <c r="F494" s="3" t="n"/>
-      <c r="G494" t="inlineStr"/>
+      <c r="G494" s="0" t="inlineStr"/>
       <c r="H494" s="3" t="n"/>
       <c r="I494" s="3" t="n"/>
       <c r="J494" s="3" t="n"/>
@@ -18616,7 +18666,7 @@
       <c r="D495" s="4" t="n"/>
       <c r="E495" s="4" t="n"/>
       <c r="F495" s="3" t="n"/>
-      <c r="G495" t="inlineStr"/>
+      <c r="G495" s="0" t="inlineStr"/>
       <c r="H495" s="3" t="n"/>
       <c r="I495" s="3" t="n"/>
       <c r="J495" s="3" t="n"/>
@@ -18645,7 +18695,7 @@
       <c r="D496" s="4" t="n"/>
       <c r="E496" s="4" t="n"/>
       <c r="F496" s="3" t="n"/>
-      <c r="G496" t="inlineStr"/>
+      <c r="G496" s="0" t="inlineStr"/>
       <c r="H496" s="3" t="n"/>
       <c r="I496" s="3" t="n"/>
       <c r="J496" s="3" t="n"/>
@@ -18674,7 +18724,7 @@
       <c r="D497" s="4" t="n"/>
       <c r="E497" s="4" t="n"/>
       <c r="F497" s="3" t="n"/>
-      <c r="G497" t="inlineStr"/>
+      <c r="G497" s="0" t="inlineStr"/>
       <c r="H497" s="3" t="n"/>
       <c r="I497" s="3" t="n"/>
       <c r="J497" s="3" t="n"/>
@@ -18703,7 +18753,7 @@
       <c r="D498" s="4" t="n"/>
       <c r="E498" s="4" t="n"/>
       <c r="F498" s="3" t="n"/>
-      <c r="G498" t="inlineStr"/>
+      <c r="G498" s="0" t="inlineStr"/>
       <c r="H498" s="3" t="n"/>
       <c r="I498" s="3" t="n"/>
       <c r="J498" s="3" t="n"/>
@@ -18732,7 +18782,7 @@
       <c r="D499" s="4" t="n"/>
       <c r="E499" s="4" t="n"/>
       <c r="F499" s="3" t="n"/>
-      <c r="G499" t="inlineStr"/>
+      <c r="G499" s="0" t="inlineStr"/>
       <c r="H499" s="3" t="n"/>
       <c r="I499" s="3" t="n"/>
       <c r="J499" s="3" t="n"/>
@@ -18761,7 +18811,7 @@
       <c r="D500" s="4" t="n"/>
       <c r="E500" s="4" t="n"/>
       <c r="F500" s="3" t="n"/>
-      <c r="G500" t="inlineStr"/>
+      <c r="G500" s="0" t="inlineStr"/>
       <c r="H500" s="3" t="n"/>
       <c r="I500" s="3" t="n"/>
       <c r="J500" s="3" t="n"/>
@@ -18790,7 +18840,7 @@
       <c r="D501" s="4" t="n"/>
       <c r="E501" s="4" t="n"/>
       <c r="F501" s="3" t="n"/>
-      <c r="G501" t="inlineStr"/>
+      <c r="G501" s="0" t="inlineStr"/>
       <c r="H501" s="3" t="n"/>
       <c r="I501" s="3" t="n"/>
       <c r="J501" s="3" t="n"/>
@@ -18819,7 +18869,7 @@
       <c r="D502" s="4" t="n"/>
       <c r="E502" s="4" t="n"/>
       <c r="F502" s="3" t="n"/>
-      <c r="G502" t="inlineStr"/>
+      <c r="G502" s="0" t="inlineStr"/>
       <c r="H502" s="3" t="n"/>
       <c r="I502" s="3" t="n"/>
       <c r="J502" s="3" t="n"/>
@@ -18848,7 +18898,7 @@
       <c r="D503" s="4" t="n"/>
       <c r="E503" s="4" t="n"/>
       <c r="F503" s="3" t="n"/>
-      <c r="G503" t="inlineStr"/>
+      <c r="G503" s="0" t="inlineStr"/>
       <c r="H503" s="3" t="n"/>
       <c r="I503" s="3" t="n"/>
       <c r="J503" s="3" t="n"/>
@@ -18877,7 +18927,7 @@
       <c r="D504" s="4" t="n"/>
       <c r="E504" s="4" t="n"/>
       <c r="F504" s="3" t="n"/>
-      <c r="G504" t="inlineStr"/>
+      <c r="G504" s="0" t="inlineStr"/>
       <c r="H504" s="3" t="n"/>
       <c r="I504" s="3" t="n"/>
       <c r="J504" s="3" t="n"/>
@@ -18906,7 +18956,7 @@
       <c r="D505" s="4" t="n"/>
       <c r="E505" s="4" t="n"/>
       <c r="F505" s="3" t="n"/>
-      <c r="G505" t="inlineStr"/>
+      <c r="G505" s="0" t="inlineStr"/>
       <c r="H505" s="3" t="n"/>
       <c r="I505" s="3" t="n"/>
       <c r="J505" s="3" t="n"/>
@@ -18935,7 +18985,7 @@
       <c r="D506" s="4" t="n"/>
       <c r="E506" s="4" t="n"/>
       <c r="F506" s="3" t="n"/>
-      <c r="G506" t="inlineStr"/>
+      <c r="G506" s="0" t="inlineStr"/>
       <c r="H506" s="3" t="n"/>
       <c r="I506" s="3" t="n"/>
       <c r="J506" s="3" t="n"/>
@@ -18964,7 +19014,7 @@
       <c r="D507" s="4" t="n"/>
       <c r="E507" s="4" t="n"/>
       <c r="F507" s="3" t="n"/>
-      <c r="G507" t="inlineStr"/>
+      <c r="G507" s="0" t="inlineStr"/>
       <c r="H507" s="3" t="n"/>
       <c r="I507" s="3" t="n"/>
       <c r="J507" s="3" t="n"/>
@@ -18993,7 +19043,7 @@
       <c r="D508" s="4" t="n"/>
       <c r="E508" s="4" t="n"/>
       <c r="F508" s="3" t="n"/>
-      <c r="G508" t="inlineStr"/>
+      <c r="G508" s="0" t="inlineStr"/>
       <c r="H508" s="3" t="n"/>
       <c r="I508" s="3" t="n"/>
       <c r="J508" s="3" t="n"/>
@@ -19022,7 +19072,7 @@
       <c r="D509" s="4" t="n"/>
       <c r="E509" s="4" t="n"/>
       <c r="F509" s="3" t="n"/>
-      <c r="G509" t="inlineStr"/>
+      <c r="G509" s="0" t="inlineStr"/>
       <c r="H509" s="3" t="n"/>
       <c r="I509" s="3" t="n"/>
       <c r="J509" s="3" t="n"/>
@@ -19051,7 +19101,7 @@
       <c r="D510" s="4" t="n"/>
       <c r="E510" s="4" t="n"/>
       <c r="F510" s="3" t="n"/>
-      <c r="G510" t="inlineStr"/>
+      <c r="G510" s="0" t="inlineStr"/>
       <c r="H510" s="3" t="n"/>
       <c r="I510" s="3" t="n"/>
       <c r="J510" s="3" t="n"/>
@@ -19080,7 +19130,7 @@
       <c r="D511" s="4" t="n"/>
       <c r="E511" s="4" t="n"/>
       <c r="F511" s="3" t="n"/>
-      <c r="G511" t="inlineStr"/>
+      <c r="G511" s="0" t="inlineStr"/>
       <c r="H511" s="3" t="n"/>
       <c r="I511" s="3" t="n"/>
       <c r="J511" s="3" t="n"/>
@@ -19109,7 +19159,7 @@
       <c r="D512" s="4" t="n"/>
       <c r="E512" s="4" t="n"/>
       <c r="F512" s="3" t="n"/>
-      <c r="G512" t="inlineStr"/>
+      <c r="G512" s="0" t="inlineStr"/>
       <c r="H512" s="3" t="n"/>
       <c r="I512" s="3" t="n"/>
       <c r="J512" s="3" t="n"/>
@@ -19138,7 +19188,7 @@
       <c r="D513" s="4" t="n"/>
       <c r="E513" s="4" t="n"/>
       <c r="F513" s="3" t="n"/>
-      <c r="G513" t="inlineStr"/>
+      <c r="G513" s="0" t="inlineStr"/>
       <c r="H513" s="3" t="n"/>
       <c r="I513" s="3" t="n"/>
       <c r="J513" s="3" t="n"/>
@@ -19167,7 +19217,7 @@
       <c r="D514" s="4" t="n"/>
       <c r="E514" s="4" t="n"/>
       <c r="F514" s="3" t="n"/>
-      <c r="G514" t="inlineStr"/>
+      <c r="G514" s="0" t="inlineStr"/>
       <c r="H514" s="3" t="n"/>
       <c r="I514" s="3" t="n"/>
       <c r="J514" s="3" t="n"/>
@@ -19196,7 +19246,7 @@
       <c r="D515" s="4" t="n"/>
       <c r="E515" s="4" t="n"/>
       <c r="F515" s="3" t="n"/>
-      <c r="G515" t="inlineStr"/>
+      <c r="G515" s="0" t="inlineStr"/>
       <c r="H515" s="3" t="n"/>
       <c r="I515" s="3" t="n"/>
       <c r="J515" s="3" t="n"/>
@@ -19225,7 +19275,7 @@
       <c r="D516" s="4" t="n"/>
       <c r="E516" s="4" t="n"/>
       <c r="F516" s="3" t="n"/>
-      <c r="G516" t="inlineStr"/>
+      <c r="G516" s="0" t="inlineStr"/>
       <c r="H516" s="3" t="n"/>
       <c r="I516" s="3" t="n"/>
       <c r="J516" s="3" t="n"/>
@@ -19254,7 +19304,7 @@
       <c r="D517" s="4" t="n"/>
       <c r="E517" s="4" t="n"/>
       <c r="F517" s="3" t="n"/>
-      <c r="G517" t="inlineStr"/>
+      <c r="G517" s="0" t="inlineStr"/>
       <c r="H517" s="3" t="n"/>
       <c r="I517" s="3" t="n"/>
       <c r="J517" s="3" t="n"/>
@@ -19283,7 +19333,7 @@
       <c r="D518" s="4" t="n"/>
       <c r="E518" s="4" t="n"/>
       <c r="F518" s="3" t="n"/>
-      <c r="G518" t="inlineStr"/>
+      <c r="G518" s="0" t="inlineStr"/>
       <c r="H518" s="3" t="n"/>
       <c r="I518" s="3" t="n"/>
       <c r="J518" s="3" t="n"/>
@@ -19312,7 +19362,7 @@
       <c r="D519" s="4" t="n"/>
       <c r="E519" s="4" t="n"/>
       <c r="F519" s="3" t="n"/>
-      <c r="G519" t="inlineStr"/>
+      <c r="G519" s="0" t="inlineStr"/>
       <c r="H519" s="3" t="n"/>
       <c r="I519" s="3" t="n"/>
       <c r="J519" s="3" t="n"/>
@@ -19341,7 +19391,7 @@
       <c r="D520" s="4" t="n"/>
       <c r="E520" s="4" t="n"/>
       <c r="F520" s="3" t="n"/>
-      <c r="G520" t="inlineStr"/>
+      <c r="G520" s="0" t="inlineStr"/>
       <c r="H520" s="3" t="n"/>
       <c r="I520" s="3" t="n"/>
       <c r="J520" s="3" t="n"/>
@@ -19370,7 +19420,7 @@
       <c r="D521" s="4" t="n"/>
       <c r="E521" s="4" t="n"/>
       <c r="F521" s="3" t="n"/>
-      <c r="G521" t="inlineStr"/>
+      <c r="G521" s="0" t="inlineStr"/>
       <c r="H521" s="3" t="n"/>
       <c r="I521" s="3" t="n"/>
       <c r="J521" s="3" t="n"/>
@@ -19399,7 +19449,7 @@
       <c r="D522" s="4" t="n"/>
       <c r="E522" s="4" t="n"/>
       <c r="F522" s="3" t="n"/>
-      <c r="G522" t="inlineStr"/>
+      <c r="G522" s="0" t="inlineStr"/>
       <c r="H522" s="3" t="n"/>
       <c r="I522" s="3" t="n"/>
       <c r="J522" s="3" t="n"/>
@@ -19428,7 +19478,7 @@
       <c r="D523" s="4" t="n"/>
       <c r="E523" s="4" t="n"/>
       <c r="F523" s="3" t="n"/>
-      <c r="G523" t="inlineStr"/>
+      <c r="G523" s="0" t="inlineStr"/>
       <c r="H523" s="3" t="n"/>
       <c r="I523" s="3" t="n"/>
       <c r="J523" s="3" t="n"/>
@@ -19457,7 +19507,7 @@
       <c r="D524" s="4" t="n"/>
       <c r="E524" s="4" t="n"/>
       <c r="F524" s="3" t="n"/>
-      <c r="G524" t="inlineStr"/>
+      <c r="G524" s="0" t="inlineStr"/>
       <c r="H524" s="3" t="n"/>
       <c r="I524" s="3" t="n"/>
       <c r="J524" s="3" t="n"/>
@@ -19486,7 +19536,7 @@
       <c r="D525" s="4" t="n"/>
       <c r="E525" s="4" t="n"/>
       <c r="F525" s="3" t="n"/>
-      <c r="G525" t="inlineStr"/>
+      <c r="G525" s="0" t="inlineStr"/>
       <c r="H525" s="3" t="n"/>
       <c r="I525" s="3" t="n"/>
       <c r="J525" s="3" t="n"/>
@@ -19515,7 +19565,7 @@
       <c r="D526" s="4" t="n"/>
       <c r="E526" s="4" t="n"/>
       <c r="F526" s="3" t="n"/>
-      <c r="G526" t="inlineStr"/>
+      <c r="G526" s="0" t="inlineStr"/>
       <c r="H526" s="3" t="n"/>
       <c r="I526" s="3" t="n"/>
       <c r="J526" s="3" t="n"/>
@@ -19544,7 +19594,7 @@
       <c r="D527" s="4" t="n"/>
       <c r="E527" s="4" t="n"/>
       <c r="F527" s="3" t="n"/>
-      <c r="G527" t="inlineStr"/>
+      <c r="G527" s="0" t="inlineStr"/>
       <c r="H527" s="3" t="n"/>
       <c r="I527" s="3" t="n"/>
       <c r="J527" s="3" t="n"/>
@@ -19573,7 +19623,7 @@
       <c r="D528" s="4" t="n"/>
       <c r="E528" s="4" t="n"/>
       <c r="F528" s="3" t="n"/>
-      <c r="G528" t="inlineStr"/>
+      <c r="G528" s="0" t="inlineStr"/>
       <c r="H528" s="3" t="n"/>
       <c r="I528" s="3" t="n"/>
       <c r="J528" s="3" t="n"/>
@@ -19602,7 +19652,7 @@
       <c r="D529" s="4" t="n"/>
       <c r="E529" s="4" t="n"/>
       <c r="F529" s="3" t="n"/>
-      <c r="G529" t="inlineStr"/>
+      <c r="G529" s="0" t="inlineStr"/>
       <c r="H529" s="3" t="n"/>
       <c r="I529" s="3" t="n"/>
       <c r="J529" s="3" t="n"/>
@@ -19631,7 +19681,7 @@
       <c r="D530" s="4" t="n"/>
       <c r="E530" s="4" t="n"/>
       <c r="F530" s="3" t="n"/>
-      <c r="G530" t="inlineStr"/>
+      <c r="G530" s="0" t="inlineStr"/>
       <c r="H530" s="3" t="n"/>
       <c r="I530" s="3" t="n"/>
       <c r="J530" s="3" t="n"/>
@@ -19660,7 +19710,7 @@
       <c r="D531" s="4" t="n"/>
       <c r="E531" s="4" t="n"/>
       <c r="F531" s="3" t="n"/>
-      <c r="G531" t="inlineStr"/>
+      <c r="G531" s="0" t="inlineStr"/>
       <c r="H531" s="3" t="n"/>
       <c r="I531" s="3" t="n"/>
       <c r="J531" s="3" t="n"/>
@@ -19689,7 +19739,7 @@
       <c r="D532" s="4" t="n"/>
       <c r="E532" s="4" t="n"/>
       <c r="F532" s="3" t="n"/>
-      <c r="G532" t="inlineStr"/>
+      <c r="G532" s="0" t="inlineStr"/>
       <c r="H532" s="3" t="n"/>
       <c r="I532" s="3" t="n"/>
       <c r="J532" s="3" t="n"/>
@@ -19718,7 +19768,7 @@
       <c r="D533" s="4" t="n"/>
       <c r="E533" s="4" t="n"/>
       <c r="F533" s="3" t="n"/>
-      <c r="G533" t="inlineStr"/>
+      <c r="G533" s="0" t="inlineStr"/>
       <c r="H533" s="3" t="n"/>
       <c r="I533" s="3" t="n"/>
       <c r="J533" s="3" t="n"/>
@@ -19747,7 +19797,7 @@
       <c r="D534" s="4" t="n"/>
       <c r="E534" s="4" t="n"/>
       <c r="F534" s="3" t="n"/>
-      <c r="G534" t="inlineStr"/>
+      <c r="G534" s="0" t="inlineStr"/>
       <c r="H534" s="3" t="n"/>
       <c r="I534" s="3" t="n"/>
       <c r="J534" s="3" t="n"/>
@@ -19776,7 +19826,7 @@
       <c r="D535" s="4" t="n"/>
       <c r="E535" s="4" t="n"/>
       <c r="F535" s="3" t="n"/>
-      <c r="G535" t="inlineStr"/>
+      <c r="G535" s="0" t="inlineStr"/>
       <c r="H535" s="3" t="n"/>
       <c r="I535" s="3" t="n"/>
       <c r="J535" s="3" t="n"/>
@@ -19805,7 +19855,7 @@
       <c r="D536" s="4" t="n"/>
       <c r="E536" s="4" t="n"/>
       <c r="F536" s="3" t="n"/>
-      <c r="G536" t="inlineStr"/>
+      <c r="G536" s="0" t="inlineStr"/>
       <c r="H536" s="3" t="n"/>
       <c r="I536" s="3" t="n"/>
       <c r="J536" s="3" t="n"/>
@@ -19834,7 +19884,7 @@
       <c r="D537" s="4" t="n"/>
       <c r="E537" s="4" t="n"/>
       <c r="F537" s="3" t="n"/>
-      <c r="G537" t="inlineStr"/>
+      <c r="G537" s="0" t="inlineStr"/>
       <c r="H537" s="3" t="n"/>
       <c r="I537" s="3" t="n"/>
       <c r="J537" s="3" t="n"/>
@@ -19863,7 +19913,7 @@
       <c r="D538" s="4" t="n"/>
       <c r="E538" s="4" t="n"/>
       <c r="F538" s="3" t="n"/>
-      <c r="G538" t="inlineStr"/>
+      <c r="G538" s="0" t="inlineStr"/>
       <c r="H538" s="3" t="n"/>
       <c r="I538" s="3" t="n"/>
       <c r="J538" s="3" t="n"/>
@@ -19892,7 +19942,7 @@
       <c r="D539" s="4" t="n"/>
       <c r="E539" s="4" t="n"/>
       <c r="F539" s="3" t="n"/>
-      <c r="G539" t="inlineStr"/>
+      <c r="G539" s="0" t="inlineStr"/>
       <c r="H539" s="3" t="n"/>
       <c r="I539" s="3" t="n"/>
       <c r="J539" s="3" t="n"/>
@@ -19921,7 +19971,7 @@
       <c r="D540" s="4" t="n"/>
       <c r="E540" s="4" t="n"/>
       <c r="F540" s="3" t="n"/>
-      <c r="G540" t="inlineStr"/>
+      <c r="G540" s="0" t="inlineStr"/>
       <c r="H540" s="3" t="n"/>
       <c r="I540" s="3" t="n"/>
       <c r="J540" s="3" t="n"/>
@@ -19950,7 +20000,7 @@
       <c r="D541" s="4" t="n"/>
       <c r="E541" s="4" t="n"/>
       <c r="F541" s="3" t="n"/>
-      <c r="G541" t="inlineStr"/>
+      <c r="G541" s="0" t="inlineStr"/>
       <c r="H541" s="3" t="n"/>
       <c r="I541" s="3" t="n"/>
       <c r="J541" s="3" t="n"/>
@@ -19979,7 +20029,7 @@
       <c r="D542" s="4" t="n"/>
       <c r="E542" s="4" t="n"/>
       <c r="F542" s="3" t="n"/>
-      <c r="G542" t="inlineStr"/>
+      <c r="G542" s="0" t="inlineStr"/>
       <c r="H542" s="3" t="n"/>
       <c r="I542" s="3" t="n"/>
       <c r="J542" s="3" t="n"/>
@@ -20008,7 +20058,7 @@
       <c r="D543" s="4" t="n"/>
       <c r="E543" s="4" t="n"/>
       <c r="F543" s="3" t="n"/>
-      <c r="G543" t="inlineStr"/>
+      <c r="G543" s="0" t="inlineStr"/>
       <c r="H543" s="3" t="n"/>
       <c r="I543" s="3" t="n"/>
       <c r="J543" s="3" t="n"/>
@@ -20037,7 +20087,7 @@
       <c r="D544" s="4" t="n"/>
       <c r="E544" s="4" t="n"/>
       <c r="F544" s="3" t="n"/>
-      <c r="G544" t="inlineStr"/>
+      <c r="G544" s="0" t="inlineStr"/>
       <c r="H544" s="3" t="n"/>
       <c r="I544" s="3" t="n"/>
       <c r="J544" s="3" t="n"/>
@@ -20066,7 +20116,7 @@
       <c r="D545" s="4" t="n"/>
       <c r="E545" s="4" t="n"/>
       <c r="F545" s="3" t="n"/>
-      <c r="G545" t="inlineStr"/>
+      <c r="G545" s="0" t="inlineStr"/>
       <c r="H545" s="3" t="n"/>
       <c r="I545" s="3" t="n"/>
       <c r="J545" s="3" t="n"/>
@@ -20095,7 +20145,7 @@
       <c r="D546" s="4" t="n"/>
       <c r="E546" s="4" t="n"/>
       <c r="F546" s="3" t="n"/>
-      <c r="G546" t="inlineStr"/>
+      <c r="G546" s="0" t="inlineStr"/>
       <c r="H546" s="3" t="n"/>
       <c r="I546" s="3" t="n"/>
       <c r="J546" s="3" t="n"/>
@@ -20124,7 +20174,7 @@
       <c r="D547" s="4" t="n"/>
       <c r="E547" s="4" t="n"/>
       <c r="F547" s="3" t="n"/>
-      <c r="G547" t="inlineStr"/>
+      <c r="G547" s="0" t="inlineStr"/>
       <c r="H547" s="3" t="n"/>
       <c r="I547" s="3" t="n"/>
       <c r="J547" s="3" t="n"/>
@@ -20153,7 +20203,7 @@
       <c r="D548" s="4" t="n"/>
       <c r="E548" s="4" t="n"/>
       <c r="F548" s="3" t="n"/>
-      <c r="G548" t="inlineStr"/>
+      <c r="G548" s="0" t="inlineStr"/>
       <c r="H548" s="3" t="n"/>
       <c r="I548" s="3" t="n"/>
       <c r="J548" s="3" t="n"/>
@@ -20182,7 +20232,7 @@
       <c r="D549" s="4" t="n"/>
       <c r="E549" s="4" t="n"/>
       <c r="F549" s="3" t="n"/>
-      <c r="G549" t="inlineStr"/>
+      <c r="G549" s="0" t="inlineStr"/>
       <c r="H549" s="3" t="n"/>
       <c r="I549" s="3" t="n"/>
       <c r="J549" s="3" t="n"/>
@@ -20211,7 +20261,7 @@
       <c r="D550" s="4" t="n"/>
       <c r="E550" s="4" t="n"/>
       <c r="F550" s="3" t="n"/>
-      <c r="G550" t="inlineStr"/>
+      <c r="G550" s="0" t="inlineStr"/>
       <c r="H550" s="3" t="n"/>
       <c r="I550" s="3" t="n"/>
       <c r="J550" s="3" t="n"/>
@@ -20240,7 +20290,7 @@
       <c r="D551" s="4" t="n"/>
       <c r="E551" s="4" t="n"/>
       <c r="F551" s="3" t="n"/>
-      <c r="G551" t="inlineStr"/>
+      <c r="G551" s="0" t="inlineStr"/>
       <c r="H551" s="3" t="n"/>
       <c r="I551" s="3" t="n"/>
       <c r="J551" s="3" t="n"/>
@@ -20269,7 +20319,7 @@
       <c r="D552" s="4" t="n"/>
       <c r="E552" s="4" t="n"/>
       <c r="F552" s="3" t="n"/>
-      <c r="G552" t="inlineStr"/>
+      <c r="G552" s="0" t="inlineStr"/>
       <c r="H552" s="3" t="n"/>
       <c r="I552" s="3" t="n"/>
       <c r="J552" s="3" t="n"/>
@@ -20298,7 +20348,7 @@
       <c r="D553" s="4" t="n"/>
       <c r="E553" s="4" t="n"/>
       <c r="F553" s="3" t="n"/>
-      <c r="G553" t="inlineStr"/>
+      <c r="G553" s="0" t="inlineStr"/>
       <c r="H553" s="3" t="n"/>
       <c r="I553" s="3" t="n"/>
       <c r="J553" s="3" t="n"/>
@@ -20327,7 +20377,7 @@
       <c r="D554" s="4" t="n"/>
       <c r="E554" s="4" t="n"/>
       <c r="F554" s="3" t="n"/>
-      <c r="G554" t="inlineStr"/>
+      <c r="G554" s="0" t="inlineStr"/>
       <c r="H554" s="3" t="n"/>
       <c r="I554" s="3" t="n"/>
       <c r="J554" s="3" t="n"/>
@@ -20356,7 +20406,7 @@
       <c r="D555" s="4" t="n"/>
       <c r="E555" s="4" t="n"/>
       <c r="F555" s="3" t="n"/>
-      <c r="G555" t="inlineStr"/>
+      <c r="G555" s="0" t="inlineStr"/>
       <c r="H555" s="3" t="n"/>
       <c r="I555" s="3" t="n"/>
       <c r="J555" s="3" t="n"/>
@@ -20385,7 +20435,7 @@
       <c r="D556" s="4" t="n"/>
       <c r="E556" s="4" t="n"/>
       <c r="F556" s="3" t="n"/>
-      <c r="G556" t="inlineStr"/>
+      <c r="G556" s="0" t="inlineStr"/>
       <c r="H556" s="3" t="n"/>
       <c r="I556" s="3" t="n"/>
       <c r="J556" s="3" t="n"/>
@@ -20414,7 +20464,7 @@
       <c r="D557" s="4" t="n"/>
       <c r="E557" s="4" t="n"/>
       <c r="F557" s="3" t="n"/>
-      <c r="G557" t="inlineStr"/>
+      <c r="G557" s="0" t="inlineStr"/>
       <c r="H557" s="3" t="n"/>
       <c r="I557" s="3" t="n"/>
       <c r="J557" s="3" t="n"/>
@@ -20443,7 +20493,7 @@
       <c r="D558" s="4" t="n"/>
       <c r="E558" s="4" t="n"/>
       <c r="F558" s="3" t="n"/>
-      <c r="G558" t="inlineStr"/>
+      <c r="G558" s="0" t="inlineStr"/>
       <c r="H558" s="3" t="n"/>
       <c r="I558" s="3" t="n"/>
       <c r="J558" s="3" t="n"/>
@@ -20472,7 +20522,7 @@
       <c r="D559" s="4" t="n"/>
       <c r="E559" s="4" t="n"/>
       <c r="F559" s="3" t="n"/>
-      <c r="G559" t="inlineStr"/>
+      <c r="G559" s="0" t="inlineStr"/>
       <c r="H559" s="3" t="n"/>
       <c r="I559" s="3" t="n"/>
       <c r="J559" s="3" t="n"/>
@@ -20501,7 +20551,7 @@
       <c r="D560" s="4" t="n"/>
       <c r="E560" s="4" t="n"/>
       <c r="F560" s="3" t="n"/>
-      <c r="G560" t="inlineStr"/>
+      <c r="G560" s="0" t="inlineStr"/>
       <c r="H560" s="3" t="n"/>
       <c r="I560" s="3" t="n"/>
       <c r="J560" s="3" t="n"/>
@@ -20530,7 +20580,7 @@
       <c r="D561" s="4" t="n"/>
       <c r="E561" s="4" t="n"/>
       <c r="F561" s="3" t="n"/>
-      <c r="G561" t="inlineStr"/>
+      <c r="G561" s="0" t="inlineStr"/>
       <c r="H561" s="3" t="n"/>
       <c r="I561" s="3" t="n"/>
       <c r="J561" s="3" t="n"/>
@@ -20559,7 +20609,7 @@
       <c r="D562" s="4" t="n"/>
       <c r="E562" s="4" t="n"/>
       <c r="F562" s="3" t="n"/>
-      <c r="G562" t="inlineStr"/>
+      <c r="G562" s="0" t="inlineStr"/>
       <c r="H562" s="3" t="n"/>
       <c r="I562" s="3" t="n"/>
       <c r="J562" s="3" t="n"/>
@@ -20588,7 +20638,7 @@
       <c r="D563" s="4" t="n"/>
       <c r="E563" s="4" t="n"/>
       <c r="F563" s="3" t="n"/>
-      <c r="G563" t="inlineStr"/>
+      <c r="G563" s="0" t="inlineStr"/>
       <c r="H563" s="3" t="n"/>
       <c r="I563" s="3" t="n"/>
       <c r="J563" s="3" t="n"/>
@@ -20617,7 +20667,7 @@
       <c r="D564" s="4" t="n"/>
       <c r="E564" s="4" t="n"/>
       <c r="F564" s="3" t="n"/>
-      <c r="G564" t="inlineStr"/>
+      <c r="G564" s="0" t="inlineStr"/>
       <c r="H564" s="3" t="n"/>
       <c r="I564" s="3" t="n"/>
       <c r="J564" s="3" t="n"/>
@@ -20646,7 +20696,7 @@
       <c r="D565" s="4" t="n"/>
       <c r="E565" s="4" t="n"/>
       <c r="F565" s="3" t="n"/>
-      <c r="G565" t="inlineStr"/>
+      <c r="G565" s="0" t="inlineStr"/>
       <c r="H565" s="3" t="n"/>
       <c r="I565" s="3" t="n"/>
       <c r="J565" s="3" t="n"/>
@@ -20675,7 +20725,7 @@
       <c r="D566" s="4" t="n"/>
       <c r="E566" s="4" t="n"/>
       <c r="F566" s="3" t="n"/>
-      <c r="G566" t="inlineStr"/>
+      <c r="G566" s="0" t="inlineStr"/>
       <c r="H566" s="3" t="n"/>
       <c r="I566" s="3" t="n"/>
       <c r="J566" s="3" t="n"/>
@@ -20704,7 +20754,7 @@
       <c r="D567" s="4" t="n"/>
       <c r="E567" s="4" t="n"/>
       <c r="F567" s="3" t="n"/>
-      <c r="G567" t="inlineStr"/>
+      <c r="G567" s="0" t="inlineStr"/>
       <c r="H567" s="3" t="n"/>
       <c r="I567" s="3" t="n"/>
       <c r="J567" s="3" t="n"/>
@@ -20733,7 +20783,7 @@
       <c r="D568" s="4" t="n"/>
       <c r="E568" s="4" t="n"/>
       <c r="F568" s="3" t="n"/>
-      <c r="G568" t="inlineStr"/>
+      <c r="G568" s="0" t="inlineStr"/>
       <c r="H568" s="3" t="n"/>
       <c r="I568" s="3" t="n"/>
       <c r="J568" s="3" t="n"/>
@@ -20762,7 +20812,7 @@
       <c r="D569" s="4" t="n"/>
       <c r="E569" s="4" t="n"/>
       <c r="F569" s="3" t="n"/>
-      <c r="G569" t="inlineStr"/>
+      <c r="G569" s="0" t="inlineStr"/>
       <c r="H569" s="3" t="n"/>
       <c r="I569" s="3" t="n"/>
       <c r="J569" s="3" t="n"/>
@@ -20791,7 +20841,7 @@
       <c r="D570" s="4" t="n"/>
       <c r="E570" s="4" t="n"/>
       <c r="F570" s="3" t="n"/>
-      <c r="G570" t="inlineStr"/>
+      <c r="G570" s="0" t="inlineStr"/>
       <c r="H570" s="3" t="n"/>
       <c r="I570" s="3" t="n"/>
       <c r="J570" s="3" t="n"/>
@@ -20820,7 +20870,7 @@
       <c r="D571" s="4" t="n"/>
       <c r="E571" s="4" t="n"/>
       <c r="F571" s="3" t="n"/>
-      <c r="G571" t="inlineStr"/>
+      <c r="G571" s="0" t="inlineStr"/>
       <c r="H571" s="3" t="n"/>
       <c r="I571" s="3" t="n"/>
       <c r="J571" s="3" t="n"/>
@@ -20849,7 +20899,7 @@
       <c r="D572" s="4" t="n"/>
       <c r="E572" s="4" t="n"/>
       <c r="F572" s="3" t="n"/>
-      <c r="G572" t="inlineStr"/>
+      <c r="G572" s="0" t="inlineStr"/>
       <c r="H572" s="3" t="n"/>
       <c r="I572" s="3" t="n"/>
       <c r="J572" s="3" t="n"/>
@@ -20878,7 +20928,7 @@
       <c r="D573" s="4" t="n"/>
       <c r="E573" s="4" t="n"/>
       <c r="F573" s="3" t="n"/>
-      <c r="G573" t="inlineStr"/>
+      <c r="G573" s="0" t="inlineStr"/>
       <c r="H573" s="3" t="n"/>
       <c r="I573" s="3" t="n"/>
       <c r="J573" s="3" t="n"/>
@@ -20907,7 +20957,7 @@
       <c r="D574" s="4" t="n"/>
       <c r="E574" s="4" t="n"/>
       <c r="F574" s="3" t="n"/>
-      <c r="G574" t="inlineStr"/>
+      <c r="G574" s="0" t="inlineStr"/>
       <c r="H574" s="3" t="n"/>
       <c r="I574" s="3" t="n"/>
       <c r="J574" s="3" t="n"/>
@@ -20936,7 +20986,7 @@
       <c r="D575" s="4" t="n"/>
       <c r="E575" s="4" t="n"/>
       <c r="F575" s="3" t="n"/>
-      <c r="G575" t="inlineStr"/>
+      <c r="G575" s="0" t="inlineStr"/>
       <c r="H575" s="3" t="n"/>
       <c r="I575" s="3" t="n"/>
       <c r="J575" s="3" t="n"/>
@@ -20965,7 +21015,7 @@
       <c r="D576" s="4" t="n"/>
       <c r="E576" s="4" t="n"/>
       <c r="F576" s="3" t="n"/>
-      <c r="G576" t="inlineStr"/>
+      <c r="G576" s="0" t="inlineStr"/>
       <c r="H576" s="3" t="n"/>
       <c r="I576" s="3" t="n"/>
       <c r="J576" s="3" t="n"/>
@@ -20994,7 +21044,7 @@
       <c r="D577" s="4" t="n"/>
       <c r="E577" s="4" t="n"/>
       <c r="F577" s="3" t="n"/>
-      <c r="G577" t="inlineStr"/>
+      <c r="G577" s="0" t="inlineStr"/>
       <c r="H577" s="3" t="n"/>
       <c r="I577" s="3" t="n"/>
       <c r="J577" s="3" t="n"/>
@@ -21023,7 +21073,7 @@
       <c r="D578" s="4" t="n"/>
       <c r="E578" s="4" t="n"/>
       <c r="F578" s="3" t="n"/>
-      <c r="G578" t="inlineStr"/>
+      <c r="G578" s="0" t="inlineStr"/>
       <c r="H578" s="3" t="n"/>
       <c r="I578" s="3" t="n"/>
       <c r="J578" s="3" t="n"/>
@@ -21052,7 +21102,7 @@
       <c r="D579" s="4" t="n"/>
       <c r="E579" s="4" t="n"/>
       <c r="F579" s="3" t="n"/>
-      <c r="G579" t="inlineStr"/>
+      <c r="G579" s="0" t="inlineStr"/>
       <c r="H579" s="3" t="n"/>
       <c r="I579" s="3" t="n"/>
       <c r="J579" s="3" t="n"/>
@@ -21081,7 +21131,7 @@
       <c r="D580" s="4" t="n"/>
       <c r="E580" s="4" t="n"/>
       <c r="F580" s="3" t="n"/>
-      <c r="G580" t="inlineStr"/>
+      <c r="G580" s="0" t="inlineStr"/>
       <c r="H580" s="3" t="n"/>
       <c r="I580" s="3" t="n"/>
       <c r="J580" s="3" t="n"/>
@@ -21110,7 +21160,7 @@
       <c r="D581" s="4" t="n"/>
       <c r="E581" s="4" t="n"/>
       <c r="F581" s="3" t="n"/>
-      <c r="G581" t="inlineStr"/>
+      <c r="G581" s="0" t="inlineStr"/>
       <c r="H581" s="3" t="n"/>
       <c r="I581" s="3" t="n"/>
       <c r="J581" s="3" t="n"/>
@@ -21139,7 +21189,7 @@
       <c r="D582" s="4" t="n"/>
       <c r="E582" s="4" t="n"/>
       <c r="F582" s="3" t="n"/>
-      <c r="G582" t="inlineStr"/>
+      <c r="G582" s="0" t="inlineStr"/>
       <c r="H582" s="3" t="n"/>
       <c r="I582" s="3" t="n"/>
       <c r="J582" s="3" t="n"/>
@@ -21168,7 +21218,7 @@
       <c r="D583" s="4" t="n"/>
       <c r="E583" s="4" t="n"/>
       <c r="F583" s="3" t="n"/>
-      <c r="G583" t="inlineStr"/>
+      <c r="G583" s="0" t="inlineStr"/>
       <c r="H583" s="3" t="n"/>
       <c r="I583" s="3" t="n"/>
       <c r="J583" s="3" t="n"/>
@@ -21197,7 +21247,7 @@
       <c r="D584" s="4" t="n"/>
       <c r="E584" s="4" t="n"/>
       <c r="F584" s="3" t="n"/>
-      <c r="G584" t="inlineStr"/>
+      <c r="G584" s="0" t="inlineStr"/>
       <c r="H584" s="3" t="n"/>
       <c r="I584" s="3" t="n"/>
       <c r="J584" s="3" t="n"/>
@@ -21226,7 +21276,7 @@
       <c r="D585" s="4" t="n"/>
       <c r="E585" s="4" t="n"/>
       <c r="F585" s="3" t="n"/>
-      <c r="G585" t="inlineStr"/>
+      <c r="G585" s="0" t="inlineStr"/>
       <c r="H585" s="3" t="n"/>
       <c r="I585" s="3" t="n"/>
       <c r="J585" s="3" t="n"/>
@@ -21255,7 +21305,7 @@
       <c r="D586" s="4" t="n"/>
       <c r="E586" s="4" t="n"/>
       <c r="F586" s="3" t="n"/>
-      <c r="G586" t="inlineStr"/>
+      <c r="G586" s="0" t="inlineStr"/>
       <c r="H586" s="3" t="n"/>
       <c r="I586" s="3" t="n"/>
       <c r="J586" s="3" t="n"/>
@@ -21284,7 +21334,7 @@
       <c r="D587" s="4" t="n"/>
       <c r="E587" s="4" t="n"/>
       <c r="F587" s="3" t="n"/>
-      <c r="G587" t="inlineStr"/>
+      <c r="G587" s="0" t="inlineStr"/>
       <c r="H587" s="3" t="n"/>
       <c r="I587" s="3" t="n"/>
       <c r="J587" s="3" t="n"/>
@@ -21313,7 +21363,7 @@
       <c r="D588" s="4" t="n"/>
       <c r="E588" s="4" t="n"/>
       <c r="F588" s="3" t="n"/>
-      <c r="G588" t="inlineStr"/>
+      <c r="G588" s="0" t="inlineStr"/>
       <c r="H588" s="3" t="n"/>
       <c r="I588" s="3" t="n"/>
       <c r="J588" s="3" t="n"/>
@@ -21342,7 +21392,7 @@
       <c r="D589" s="4" t="n"/>
       <c r="E589" s="4" t="n"/>
       <c r="F589" s="3" t="n"/>
-      <c r="G589" t="inlineStr"/>
+      <c r="G589" s="0" t="inlineStr"/>
       <c r="H589" s="3" t="n"/>
       <c r="I589" s="3" t="n"/>
       <c r="J589" s="3" t="n"/>
@@ -21371,7 +21421,7 @@
       <c r="D590" s="4" t="n"/>
       <c r="E590" s="4" t="n"/>
       <c r="F590" s="3" t="n"/>
-      <c r="G590" t="inlineStr"/>
+      <c r="G590" s="0" t="inlineStr"/>
       <c r="H590" s="3" t="n"/>
       <c r="I590" s="3" t="n"/>
       <c r="J590" s="3" t="n"/>
@@ -21400,7 +21450,7 @@
       <c r="D591" s="4" t="n"/>
       <c r="E591" s="4" t="n"/>
       <c r="F591" s="3" t="n"/>
-      <c r="G591" t="inlineStr"/>
+      <c r="G591" s="0" t="inlineStr"/>
       <c r="H591" s="3" t="n"/>
       <c r="I591" s="3" t="n"/>
       <c r="J591" s="3" t="n"/>
@@ -21429,7 +21479,7 @@
       <c r="D592" s="4" t="n"/>
       <c r="E592" s="4" t="n"/>
       <c r="F592" s="3" t="n"/>
-      <c r="G592" t="inlineStr"/>
+      <c r="G592" s="0" t="inlineStr"/>
       <c r="H592" s="3" t="n"/>
       <c r="I592" s="3" t="n"/>
       <c r="J592" s="3" t="n"/>
@@ -21458,7 +21508,7 @@
       <c r="D593" s="4" t="n"/>
       <c r="E593" s="4" t="n"/>
       <c r="F593" s="3" t="n"/>
-      <c r="G593" t="inlineStr"/>
+      <c r="G593" s="0" t="inlineStr"/>
       <c r="H593" s="3" t="n"/>
       <c r="I593" s="3" t="n"/>
       <c r="J593" s="3" t="n"/>
@@ -21487,7 +21537,7 @@
       <c r="D594" s="4" t="n"/>
       <c r="E594" s="4" t="n"/>
       <c r="F594" s="3" t="n"/>
-      <c r="G594" t="inlineStr"/>
+      <c r="G594" s="0" t="inlineStr"/>
       <c r="H594" s="3" t="n"/>
       <c r="I594" s="3" t="n"/>
       <c r="J594" s="3" t="n"/>
@@ -21516,7 +21566,7 @@
       <c r="D595" s="4" t="n"/>
       <c r="E595" s="4" t="n"/>
       <c r="F595" s="3" t="n"/>
-      <c r="G595" t="inlineStr"/>
+      <c r="G595" s="0" t="inlineStr"/>
       <c r="H595" s="3" t="n"/>
       <c r="I595" s="3" t="n"/>
       <c r="J595" s="3" t="n"/>
@@ -21545,7 +21595,7 @@
       <c r="D596" s="4" t="n"/>
       <c r="E596" s="4" t="n"/>
       <c r="F596" s="3" t="n"/>
-      <c r="G596" t="inlineStr"/>
+      <c r="G596" s="0" t="inlineStr"/>
       <c r="H596" s="3" t="n"/>
       <c r="I596" s="3" t="n"/>
       <c r="J596" s="3" t="n"/>
@@ -21574,7 +21624,7 @@
       <c r="D597" s="4" t="n"/>
       <c r="E597" s="4" t="n"/>
       <c r="F597" s="3" t="n"/>
-      <c r="G597" t="inlineStr"/>
+      <c r="G597" s="0" t="inlineStr"/>
       <c r="H597" s="3" t="n"/>
       <c r="I597" s="3" t="n"/>
       <c r="J597" s="3" t="n"/>
@@ -21603,7 +21653,7 @@
       <c r="D598" s="4" t="n"/>
       <c r="E598" s="4" t="n"/>
       <c r="F598" s="3" t="n"/>
-      <c r="G598" t="inlineStr"/>
+      <c r="G598" s="0" t="inlineStr"/>
       <c r="H598" s="3" t="n"/>
       <c r="I598" s="3" t="n"/>
       <c r="J598" s="3" t="n"/>
@@ -21632,7 +21682,7 @@
       <c r="D599" s="4" t="n"/>
       <c r="E599" s="4" t="n"/>
       <c r="F599" s="3" t="n"/>
-      <c r="G599" t="inlineStr"/>
+      <c r="G599" s="0" t="inlineStr"/>
       <c r="H599" s="3" t="n"/>
       <c r="I599" s="3" t="n"/>
       <c r="J599" s="3" t="n"/>
@@ -21661,7 +21711,7 @@
       <c r="D600" s="4" t="n"/>
       <c r="E600" s="4" t="n"/>
       <c r="F600" s="3" t="n"/>
-      <c r="G600" t="inlineStr"/>
+      <c r="G600" s="0" t="inlineStr"/>
       <c r="H600" s="3" t="n"/>
       <c r="I600" s="3" t="n"/>
       <c r="J600" s="3" t="n"/>
@@ -21690,7 +21740,7 @@
       <c r="D601" s="4" t="n"/>
       <c r="E601" s="4" t="n"/>
       <c r="F601" s="3" t="n"/>
-      <c r="G601" t="inlineStr"/>
+      <c r="G601" s="0" t="inlineStr"/>
       <c r="H601" s="3" t="n"/>
       <c r="I601" s="3" t="n"/>
       <c r="J601" s="3" t="n"/>
@@ -21719,7 +21769,7 @@
       <c r="D602" s="4" t="n"/>
       <c r="E602" s="4" t="n"/>
       <c r="F602" s="3" t="n"/>
-      <c r="G602" t="inlineStr"/>
+      <c r="G602" s="0" t="inlineStr"/>
       <c r="H602" s="3" t="n"/>
       <c r="I602" s="3" t="n"/>
       <c r="J602" s="3" t="n"/>
@@ -21748,7 +21798,7 @@
       <c r="D603" s="4" t="n"/>
       <c r="E603" s="4" t="n"/>
       <c r="F603" s="3" t="n"/>
-      <c r="G603" t="inlineStr"/>
+      <c r="G603" s="0" t="inlineStr"/>
       <c r="H603" s="3" t="n"/>
       <c r="I603" s="3" t="n"/>
       <c r="J603" s="3" t="n"/>
@@ -21777,7 +21827,7 @@
       <c r="D604" s="4" t="n"/>
       <c r="E604" s="4" t="n"/>
       <c r="F604" s="3" t="n"/>
-      <c r="G604" t="inlineStr"/>
+      <c r="G604" s="0" t="inlineStr"/>
       <c r="H604" s="3" t="n"/>
       <c r="I604" s="3" t="n"/>
       <c r="J604" s="3" t="n"/>
@@ -21806,7 +21856,7 @@
       <c r="D605" s="4" t="n"/>
       <c r="E605" s="4" t="n"/>
       <c r="F605" s="3" t="n"/>
-      <c r="G605" t="inlineStr"/>
+      <c r="G605" s="0" t="inlineStr"/>
       <c r="H605" s="3" t="n"/>
       <c r="I605" s="3" t="n"/>
       <c r="J605" s="3" t="n"/>
@@ -21835,7 +21885,7 @@
       <c r="D606" s="4" t="n"/>
       <c r="E606" s="4" t="n"/>
       <c r="F606" s="3" t="n"/>
-      <c r="G606" t="inlineStr"/>
+      <c r="G606" s="0" t="inlineStr"/>
       <c r="H606" s="3" t="n"/>
       <c r="I606" s="3" t="n"/>
       <c r="J606" s="3" t="n"/>
@@ -21864,7 +21914,7 @@
       <c r="D607" s="4" t="n"/>
       <c r="E607" s="4" t="n"/>
       <c r="F607" s="3" t="n"/>
-      <c r="G607" t="inlineStr"/>
+      <c r="G607" s="0" t="inlineStr"/>
       <c r="H607" s="3" t="n"/>
       <c r="I607" s="3" t="n"/>
       <c r="J607" s="3" t="n"/>
@@ -21893,7 +21943,7 @@
       <c r="D608" s="4" t="n"/>
       <c r="E608" s="4" t="n"/>
       <c r="F608" s="3" t="n"/>
-      <c r="G608" t="inlineStr"/>
+      <c r="G608" s="0" t="inlineStr"/>
       <c r="H608" s="3" t="n"/>
       <c r="I608" s="3" t="n"/>
       <c r="J608" s="3" t="n"/>
@@ -21922,7 +21972,7 @@
       <c r="D609" s="4" t="n"/>
       <c r="E609" s="4" t="n"/>
       <c r="F609" s="3" t="n"/>
-      <c r="G609" t="inlineStr"/>
+      <c r="G609" s="0" t="inlineStr"/>
       <c r="H609" s="3" t="n"/>
       <c r="I609" s="3" t="n"/>
       <c r="J609" s="3" t="n"/>
@@ -21951,7 +22001,7 @@
       <c r="D610" s="4" t="n"/>
       <c r="E610" s="4" t="n"/>
       <c r="F610" s="3" t="n"/>
-      <c r="G610" t="inlineStr"/>
+      <c r="G610" s="0" t="inlineStr"/>
       <c r="H610" s="3" t="n"/>
       <c r="I610" s="3" t="n"/>
       <c r="J610" s="3" t="n"/>
@@ -21980,7 +22030,7 @@
       <c r="D611" s="4" t="n"/>
       <c r="E611" s="4" t="n"/>
       <c r="F611" s="3" t="n"/>
-      <c r="G611" t="inlineStr"/>
+      <c r="G611" s="0" t="inlineStr"/>
       <c r="H611" s="3" t="n"/>
       <c r="I611" s="3" t="n"/>
       <c r="J611" s="3" t="n"/>
@@ -22009,7 +22059,7 @@
       <c r="D612" s="4" t="n"/>
       <c r="E612" s="4" t="n"/>
       <c r="F612" s="3" t="n"/>
-      <c r="G612" t="inlineStr"/>
+      <c r="G612" s="0" t="inlineStr"/>
       <c r="H612" s="3" t="n"/>
       <c r="I612" s="3" t="n"/>
       <c r="J612" s="3" t="n"/>
@@ -22038,7 +22088,7 @@
       <c r="D613" s="4" t="n"/>
       <c r="E613" s="4" t="n"/>
       <c r="F613" s="3" t="n"/>
-      <c r="G613" t="inlineStr"/>
+      <c r="G613" s="0" t="inlineStr"/>
       <c r="H613" s="3" t="n"/>
       <c r="I613" s="3" t="n"/>
       <c r="J613" s="3" t="n"/>
@@ -22067,7 +22117,7 @@
       <c r="D614" s="4" t="n"/>
       <c r="E614" s="4" t="n"/>
       <c r="F614" s="3" t="n"/>
-      <c r="G614" t="inlineStr"/>
+      <c r="G614" s="0" t="inlineStr"/>
       <c r="H614" s="3" t="n"/>
       <c r="I614" s="3" t="n"/>
       <c r="J614" s="3" t="n"/>
@@ -22096,7 +22146,7 @@
       <c r="D615" s="4" t="n"/>
       <c r="E615" s="4" t="n"/>
       <c r="F615" s="3" t="n"/>
-      <c r="G615" t="inlineStr"/>
+      <c r="G615" s="0" t="inlineStr"/>
       <c r="H615" s="3" t="n"/>
       <c r="I615" s="3" t="n"/>
       <c r="J615" s="3" t="n"/>
@@ -22125,7 +22175,7 @@
       <c r="D616" s="4" t="n"/>
       <c r="E616" s="4" t="n"/>
       <c r="F616" s="3" t="n"/>
-      <c r="G616" t="inlineStr"/>
+      <c r="G616" s="0" t="inlineStr"/>
       <c r="H616" s="3" t="n"/>
       <c r="I616" s="3" t="n"/>
       <c r="J616" s="3" t="n"/>
@@ -22154,7 +22204,7 @@
       <c r="D617" s="4" t="n"/>
       <c r="E617" s="4" t="n"/>
       <c r="F617" s="3" t="n"/>
-      <c r="G617" t="inlineStr"/>
+      <c r="G617" s="0" t="inlineStr"/>
       <c r="H617" s="3" t="n"/>
       <c r="I617" s="3" t="n"/>
       <c r="J617" s="3" t="n"/>
@@ -22183,7 +22233,7 @@
       <c r="D618" s="4" t="n"/>
       <c r="E618" s="4" t="n"/>
       <c r="F618" s="3" t="n"/>
-      <c r="G618" t="inlineStr"/>
+      <c r="G618" s="0" t="inlineStr"/>
       <c r="H618" s="3" t="n"/>
       <c r="I618" s="3" t="n"/>
       <c r="J618" s="3" t="n"/>
@@ -22212,7 +22262,7 @@
       <c r="D619" s="4" t="n"/>
       <c r="E619" s="4" t="n"/>
       <c r="F619" s="3" t="n"/>
-      <c r="G619" t="inlineStr"/>
+      <c r="G619" s="0" t="inlineStr"/>
       <c r="H619" s="3" t="n"/>
       <c r="I619" s="3" t="n"/>
       <c r="J619" s="3" t="n"/>
@@ -22241,7 +22291,7 @@
       <c r="D620" s="4" t="n"/>
       <c r="E620" s="4" t="n"/>
       <c r="F620" s="3" t="n"/>
-      <c r="G620" t="inlineStr"/>
+      <c r="G620" s="0" t="inlineStr"/>
       <c r="H620" s="3" t="n"/>
       <c r="I620" s="3" t="n"/>
       <c r="J620" s="3" t="n"/>
@@ -22270,7 +22320,7 @@
       <c r="D621" s="4" t="n"/>
       <c r="E621" s="4" t="n"/>
       <c r="F621" s="3" t="n"/>
-      <c r="G621" t="inlineStr"/>
+      <c r="G621" s="0" t="inlineStr"/>
       <c r="H621" s="3" t="n"/>
       <c r="I621" s="3" t="n"/>
       <c r="J621" s="3" t="n"/>
@@ -22299,7 +22349,7 @@
       <c r="D622" s="4" t="n"/>
       <c r="E622" s="4" t="n"/>
       <c r="F622" s="3" t="n"/>
-      <c r="G622" t="inlineStr"/>
+      <c r="G622" s="0" t="inlineStr"/>
       <c r="H622" s="3" t="n"/>
       <c r="I622" s="3" t="n"/>
       <c r="J622" s="3" t="n"/>
@@ -22328,7 +22378,7 @@
       <c r="D623" s="4" t="n"/>
       <c r="E623" s="4" t="n"/>
       <c r="F623" s="3" t="n"/>
-      <c r="G623" t="inlineStr"/>
+      <c r="G623" s="0" t="inlineStr"/>
       <c r="H623" s="3" t="n"/>
       <c r="I623" s="3" t="n"/>
       <c r="J623" s="3" t="n"/>
@@ -22357,7 +22407,7 @@
       <c r="D624" s="4" t="n"/>
       <c r="E624" s="4" t="n"/>
       <c r="F624" s="3" t="n"/>
-      <c r="G624" t="inlineStr"/>
+      <c r="G624" s="0" t="inlineStr"/>
       <c r="H624" s="3" t="n"/>
       <c r="I624" s="3" t="n"/>
       <c r="J624" s="3" t="n"/>
@@ -22386,7 +22436,7 @@
       <c r="D625" s="4" t="n"/>
       <c r="E625" s="4" t="n"/>
       <c r="F625" s="3" t="n"/>
-      <c r="G625" t="inlineStr"/>
+      <c r="G625" s="0" t="inlineStr"/>
       <c r="H625" s="3" t="n"/>
       <c r="I625" s="3" t="n"/>
       <c r="J625" s="3" t="n"/>
@@ -22415,7 +22465,7 @@
       <c r="D626" s="4" t="n"/>
       <c r="E626" s="4" t="n"/>
       <c r="F626" s="3" t="n"/>
-      <c r="G626" t="inlineStr"/>
+      <c r="G626" s="0" t="inlineStr"/>
       <c r="H626" s="3" t="n"/>
       <c r="I626" s="3" t="n"/>
       <c r="J626" s="3" t="n"/>
@@ -22444,7 +22494,7 @@
       <c r="D627" s="4" t="n"/>
       <c r="E627" s="4" t="n"/>
       <c r="F627" s="3" t="n"/>
-      <c r="G627" t="inlineStr"/>
+      <c r="G627" s="0" t="inlineStr"/>
       <c r="H627" s="3" t="n"/>
       <c r="I627" s="3" t="n"/>
       <c r="J627" s="3" t="n"/>
@@ -22473,7 +22523,7 @@
       <c r="D628" s="4" t="n"/>
       <c r="E628" s="4" t="n"/>
       <c r="F628" s="3" t="n"/>
-      <c r="G628" t="inlineStr"/>
+      <c r="G628" s="0" t="inlineStr"/>
       <c r="H628" s="3" t="n"/>
       <c r="I628" s="3" t="n"/>
       <c r="J628" s="3" t="n"/>
@@ -22502,7 +22552,7 @@
       <c r="D629" s="4" t="n"/>
       <c r="E629" s="4" t="n"/>
       <c r="F629" s="3" t="n"/>
-      <c r="G629" t="inlineStr"/>
+      <c r="G629" s="0" t="inlineStr"/>
       <c r="H629" s="3" t="n"/>
       <c r="I629" s="3" t="n"/>
       <c r="J629" s="3" t="n"/>
@@ -22531,7 +22581,7 @@
       <c r="D630" s="4" t="n"/>
       <c r="E630" s="4" t="n"/>
       <c r="F630" s="3" t="n"/>
-      <c r="G630" t="inlineStr"/>
+      <c r="G630" s="0" t="inlineStr"/>
       <c r="H630" s="3" t="n"/>
       <c r="I630" s="3" t="n"/>
       <c r="J630" s="3" t="n"/>
@@ -22560,7 +22610,7 @@
       <c r="D631" s="4" t="n"/>
       <c r="E631" s="4" t="n"/>
       <c r="F631" s="3" t="n"/>
-      <c r="G631" t="inlineStr"/>
+      <c r="G631" s="0" t="inlineStr"/>
       <c r="H631" s="3" t="n"/>
       <c r="I631" s="3" t="n"/>
       <c r="J631" s="3" t="n"/>
@@ -22589,7 +22639,7 @@
       <c r="D632" s="4" t="n"/>
       <c r="E632" s="4" t="n"/>
       <c r="F632" s="3" t="n"/>
-      <c r="G632" t="inlineStr"/>
+      <c r="G632" s="0" t="inlineStr"/>
       <c r="H632" s="3" t="n"/>
       <c r="I632" s="3" t="n"/>
       <c r="J632" s="3" t="n"/>
@@ -22618,7 +22668,7 @@
       <c r="D633" s="4" t="n"/>
       <c r="E633" s="4" t="n"/>
       <c r="F633" s="3" t="n"/>
-      <c r="G633" t="inlineStr"/>
+      <c r="G633" s="0" t="inlineStr"/>
       <c r="H633" s="3" t="n"/>
       <c r="I633" s="3" t="n"/>
       <c r="J633" s="3" t="n"/>
@@ -22647,7 +22697,7 @@
       <c r="D634" s="4" t="n"/>
       <c r="E634" s="4" t="n"/>
       <c r="F634" s="3" t="n"/>
-      <c r="G634" t="inlineStr"/>
+      <c r="G634" s="0" t="inlineStr"/>
       <c r="H634" s="3" t="n"/>
       <c r="I634" s="3" t="n"/>
       <c r="J634" s="3" t="n"/>
@@ -22676,7 +22726,7 @@
       <c r="D635" s="4" t="n"/>
       <c r="E635" s="4" t="n"/>
       <c r="F635" s="3" t="n"/>
-      <c r="G635" t="inlineStr"/>
+      <c r="G635" s="0" t="inlineStr"/>
       <c r="H635" s="3" t="n"/>
       <c r="I635" s="3" t="n"/>
       <c r="J635" s="3" t="n"/>
@@ -22705,7 +22755,7 @@
       <c r="D636" s="4" t="n"/>
       <c r="E636" s="4" t="n"/>
       <c r="F636" s="3" t="n"/>
-      <c r="G636" t="inlineStr"/>
+      <c r="G636" s="0" t="inlineStr"/>
       <c r="H636" s="3" t="n"/>
       <c r="I636" s="3" t="n"/>
       <c r="J636" s="3" t="n"/>
@@ -22734,7 +22784,7 @@
       <c r="D637" s="4" t="n"/>
       <c r="E637" s="4" t="n"/>
       <c r="F637" s="3" t="n"/>
-      <c r="G637" t="inlineStr"/>
+      <c r="G637" s="0" t="inlineStr"/>
       <c r="H637" s="3" t="n"/>
       <c r="I637" s="3" t="n"/>
       <c r="J637" s="3" t="n"/>
@@ -22763,7 +22813,7 @@
       <c r="D638" s="4" t="n"/>
       <c r="E638" s="4" t="n"/>
       <c r="F638" s="3" t="n"/>
-      <c r="G638" t="inlineStr"/>
+      <c r="G638" s="0" t="inlineStr"/>
       <c r="H638" s="3" t="n"/>
       <c r="I638" s="3" t="n"/>
       <c r="J638" s="3" t="n"/>
@@ -22792,7 +22842,7 @@
       <c r="D639" s="4" t="n"/>
       <c r="E639" s="4" t="n"/>
       <c r="F639" s="3" t="n"/>
-      <c r="G639" t="inlineStr"/>
+      <c r="G639" s="0" t="inlineStr"/>
       <c r="H639" s="3" t="n"/>
       <c r="I639" s="3" t="n"/>
       <c r="J639" s="3" t="n"/>
@@ -22821,7 +22871,7 @@
       <c r="D640" s="4" t="n"/>
       <c r="E640" s="4" t="n"/>
       <c r="F640" s="3" t="n"/>
-      <c r="G640" t="inlineStr"/>
+      <c r="G640" s="0" t="inlineStr"/>
       <c r="H640" s="3" t="n"/>
       <c r="I640" s="3" t="n"/>
       <c r="J640" s="3" t="n"/>
@@ -22850,7 +22900,7 @@
       <c r="D641" s="4" t="n"/>
       <c r="E641" s="4" t="n"/>
       <c r="F641" s="3" t="n"/>
-      <c r="G641" t="inlineStr"/>
+      <c r="G641" s="0" t="inlineStr"/>
       <c r="H641" s="3" t="n"/>
       <c r="I641" s="3" t="n"/>
       <c r="J641" s="3" t="n"/>
@@ -22879,7 +22929,7 @@
       <c r="D642" s="4" t="n"/>
       <c r="E642" s="4" t="n"/>
       <c r="F642" s="3" t="n"/>
-      <c r="G642" t="inlineStr"/>
+      <c r="G642" s="0" t="inlineStr"/>
       <c r="H642" s="3" t="n"/>
       <c r="I642" s="3" t="n"/>
       <c r="J642" s="3" t="n"/>
@@ -22908,7 +22958,7 @@
       <c r="D643" s="4" t="n"/>
       <c r="E643" s="4" t="n"/>
       <c r="F643" s="3" t="n"/>
-      <c r="G643" t="inlineStr"/>
+      <c r="G643" s="0" t="inlineStr"/>
       <c r="H643" s="3" t="n"/>
       <c r="I643" s="3" t="n"/>
       <c r="J643" s="3" t="n"/>
@@ -22937,7 +22987,7 @@
       <c r="D644" s="4" t="n"/>
       <c r="E644" s="4" t="n"/>
       <c r="F644" s="3" t="n"/>
-      <c r="G644" t="inlineStr"/>
+      <c r="G644" s="0" t="inlineStr"/>
       <c r="H644" s="3" t="n"/>
       <c r="I644" s="3" t="n"/>
       <c r="J644" s="3" t="n"/>
@@ -22966,7 +23016,7 @@
       <c r="D645" s="4" t="n"/>
       <c r="E645" s="4" t="n"/>
       <c r="F645" s="3" t="n"/>
-      <c r="G645" t="inlineStr"/>
+      <c r="G645" s="0" t="inlineStr"/>
       <c r="H645" s="3" t="n"/>
       <c r="I645" s="3" t="n"/>
       <c r="J645" s="3" t="n"/>
@@ -22995,7 +23045,7 @@
       <c r="D646" s="4" t="n"/>
       <c r="E646" s="4" t="n"/>
       <c r="F646" s="3" t="n"/>
-      <c r="G646" t="inlineStr"/>
+      <c r="G646" s="0" t="inlineStr"/>
       <c r="H646" s="3" t="n"/>
       <c r="I646" s="3" t="n"/>
       <c r="J646" s="3" t="n"/>
@@ -23024,7 +23074,7 @@
       <c r="D647" s="4" t="n"/>
       <c r="E647" s="4" t="n"/>
       <c r="F647" s="3" t="n"/>
-      <c r="G647" t="inlineStr"/>
+      <c r="G647" s="0" t="inlineStr"/>
       <c r="H647" s="3" t="n"/>
       <c r="I647" s="3" t="n"/>
       <c r="J647" s="3" t="n"/>
@@ -23053,7 +23103,7 @@
       <c r="D648" s="4" t="n"/>
       <c r="E648" s="4" t="n"/>
       <c r="F648" s="3" t="n"/>
-      <c r="G648" t="inlineStr"/>
+      <c r="G648" s="0" t="inlineStr"/>
       <c r="H648" s="3" t="n"/>
       <c r="I648" s="3" t="n"/>
       <c r="J648" s="3" t="n"/>
@@ -23082,7 +23132,7 @@
       <c r="D649" s="4" t="n"/>
       <c r="E649" s="4" t="n"/>
       <c r="F649" s="3" t="n"/>
-      <c r="G649" t="inlineStr"/>
+      <c r="G649" s="0" t="inlineStr"/>
       <c r="H649" s="3" t="n"/>
       <c r="I649" s="3" t="n"/>
       <c r="J649" s="3" t="n"/>
@@ -23111,7 +23161,7 @@
       <c r="D650" s="4" t="n"/>
       <c r="E650" s="4" t="n"/>
       <c r="F650" s="3" t="n"/>
-      <c r="G650" t="inlineStr"/>
+      <c r="G650" s="0" t="inlineStr"/>
       <c r="H650" s="3" t="n"/>
       <c r="I650" s="3" t="n"/>
       <c r="J650" s="3" t="n"/>
@@ -23140,7 +23190,7 @@
       <c r="D651" s="4" t="n"/>
       <c r="E651" s="4" t="n"/>
       <c r="F651" s="3" t="n"/>
-      <c r="G651" t="inlineStr"/>
+      <c r="G651" s="0" t="inlineStr"/>
       <c r="H651" s="3" t="n"/>
       <c r="I651" s="3" t="n"/>
       <c r="J651" s="3" t="n"/>
@@ -23169,7 +23219,7 @@
       <c r="D652" s="4" t="n"/>
       <c r="E652" s="4" t="n"/>
       <c r="F652" s="3" t="n"/>
-      <c r="G652" t="inlineStr"/>
+      <c r="G652" s="0" t="inlineStr"/>
       <c r="H652" s="3" t="n"/>
       <c r="I652" s="3" t="n"/>
       <c r="J652" s="3" t="n"/>
@@ -23198,7 +23248,7 @@
       <c r="D653" s="4" t="n"/>
       <c r="E653" s="4" t="n"/>
       <c r="F653" s="3" t="n"/>
-      <c r="G653" t="inlineStr"/>
+      <c r="G653" s="0" t="inlineStr"/>
       <c r="H653" s="3" t="n"/>
       <c r="I653" s="3" t="n"/>
       <c r="J653" s="3" t="n"/>
@@ -23227,7 +23277,7 @@
       <c r="D654" s="4" t="n"/>
       <c r="E654" s="4" t="n"/>
       <c r="F654" s="3" t="n"/>
-      <c r="G654" t="inlineStr"/>
+      <c r="G654" s="0" t="inlineStr"/>
       <c r="H654" s="3" t="n"/>
       <c r="I654" s="3" t="n"/>
       <c r="J654" s="3" t="n"/>
@@ -23256,7 +23306,7 @@
       <c r="D655" s="4" t="n"/>
       <c r="E655" s="4" t="n"/>
       <c r="F655" s="3" t="n"/>
-      <c r="G655" t="inlineStr"/>
+      <c r="G655" s="0" t="inlineStr"/>
       <c r="H655" s="3" t="n"/>
       <c r="I655" s="3" t="n"/>
       <c r="J655" s="3" t="n"/>
@@ -23285,7 +23335,7 @@
       <c r="D656" s="4" t="n"/>
       <c r="E656" s="4" t="n"/>
       <c r="F656" s="3" t="n"/>
-      <c r="G656" t="inlineStr"/>
+      <c r="G656" s="0" t="inlineStr"/>
       <c r="H656" s="3" t="n"/>
       <c r="I656" s="3" t="n"/>
       <c r="J656" s="3" t="n"/>
@@ -23314,7 +23364,7 @@
       <c r="D657" s="4" t="n"/>
       <c r="E657" s="4" t="n"/>
       <c r="F657" s="3" t="n"/>
-      <c r="G657" t="inlineStr"/>
+      <c r="G657" s="0" t="inlineStr"/>
       <c r="H657" s="3" t="n"/>
       <c r="I657" s="3" t="n"/>
       <c r="J657" s="3" t="n"/>
@@ -23343,7 +23393,7 @@
       <c r="D658" s="4" t="n"/>
       <c r="E658" s="4" t="n"/>
       <c r="F658" s="3" t="n"/>
-      <c r="G658" t="inlineStr"/>
+      <c r="G658" s="0" t="inlineStr"/>
       <c r="H658" s="3" t="n"/>
       <c r="I658" s="3" t="n"/>
       <c r="J658" s="3" t="n"/>
@@ -23372,7 +23422,7 @@
       <c r="D659" s="4" t="n"/>
       <c r="E659" s="4" t="n"/>
       <c r="F659" s="3" t="n"/>
-      <c r="G659" t="inlineStr"/>
+      <c r="G659" s="0" t="inlineStr"/>
       <c r="H659" s="3" t="n"/>
       <c r="I659" s="3" t="n"/>
       <c r="J659" s="3" t="n"/>
@@ -23401,7 +23451,7 @@
       <c r="D660" s="4" t="n"/>
       <c r="E660" s="4" t="n"/>
       <c r="F660" s="3" t="n"/>
-      <c r="G660" t="inlineStr"/>
+      <c r="G660" s="0" t="inlineStr"/>
       <c r="H660" s="3" t="n"/>
       <c r="I660" s="3" t="n"/>
       <c r="J660" s="3" t="n"/>
@@ -23430,7 +23480,7 @@
       <c r="D661" s="4" t="n"/>
       <c r="E661" s="4" t="n"/>
       <c r="F661" s="3" t="n"/>
-      <c r="G661" t="inlineStr"/>
+      <c r="G661" s="0" t="inlineStr"/>
       <c r="H661" s="3" t="n"/>
       <c r="I661" s="3" t="n"/>
       <c r="J661" s="3" t="n"/>
@@ -23459,7 +23509,7 @@
       <c r="D662" s="4" t="n"/>
       <c r="E662" s="4" t="n"/>
       <c r="F662" s="3" t="n"/>
-      <c r="G662" t="inlineStr"/>
+      <c r="G662" s="0" t="inlineStr"/>
       <c r="H662" s="3" t="n"/>
       <c r="I662" s="3" t="n"/>
       <c r="J662" s="3" t="n"/>
@@ -23488,7 +23538,7 @@
       <c r="D663" s="4" t="n"/>
       <c r="E663" s="4" t="n"/>
       <c r="F663" s="3" t="n"/>
-      <c r="G663" t="inlineStr"/>
+      <c r="G663" s="0" t="inlineStr"/>
       <c r="H663" s="3" t="n"/>
       <c r="I663" s="3" t="n"/>
       <c r="J663" s="3" t="n"/>
@@ -23517,7 +23567,7 @@
       <c r="D664" s="4" t="n"/>
       <c r="E664" s="4" t="n"/>
       <c r="F664" s="3" t="n"/>
-      <c r="G664" t="inlineStr"/>
+      <c r="G664" s="0" t="inlineStr"/>
       <c r="H664" s="3" t="n"/>
       <c r="I664" s="3" t="n"/>
       <c r="J664" s="3" t="n"/>
@@ -23546,7 +23596,7 @@
       <c r="D665" s="4" t="n"/>
       <c r="E665" s="4" t="n"/>
       <c r="F665" s="3" t="n"/>
-      <c r="G665" t="inlineStr"/>
+      <c r="G665" s="0" t="inlineStr"/>
       <c r="H665" s="3" t="n"/>
       <c r="I665" s="3" t="n"/>
       <c r="J665" s="3" t="n"/>
@@ -23575,7 +23625,7 @@
       <c r="D666" s="4" t="n"/>
       <c r="E666" s="4" t="n"/>
       <c r="F666" s="3" t="n"/>
-      <c r="G666" t="inlineStr"/>
+      <c r="G666" s="0" t="inlineStr"/>
       <c r="H666" s="3" t="n"/>
       <c r="I666" s="3" t="n"/>
       <c r="J666" s="3" t="n"/>
@@ -23604,7 +23654,7 @@
       <c r="D667" s="4" t="n"/>
       <c r="E667" s="4" t="n"/>
       <c r="F667" s="3" t="n"/>
-      <c r="G667" t="inlineStr"/>
+      <c r="G667" s="0" t="inlineStr"/>
       <c r="H667" s="3" t="n"/>
       <c r="I667" s="3" t="n"/>
       <c r="J667" s="3" t="n"/>
@@ -23633,7 +23683,7 @@
       <c r="D668" s="4" t="n"/>
       <c r="E668" s="4" t="n"/>
       <c r="F668" s="3" t="n"/>
-      <c r="G668" t="inlineStr"/>
+      <c r="G668" s="0" t="inlineStr"/>
       <c r="H668" s="3" t="n"/>
       <c r="I668" s="3" t="n"/>
       <c r="J668" s="3" t="n"/>
@@ -23662,7 +23712,7 @@
       <c r="D669" s="4" t="n"/>
       <c r="E669" s="4" t="n"/>
       <c r="F669" s="3" t="n"/>
-      <c r="G669" t="inlineStr"/>
+      <c r="G669" s="0" t="inlineStr"/>
       <c r="H669" s="3" t="n"/>
       <c r="I669" s="3" t="n"/>
       <c r="J669" s="3" t="n"/>
@@ -23691,7 +23741,7 @@
       <c r="D670" s="4" t="n"/>
       <c r="E670" s="4" t="n"/>
       <c r="F670" s="3" t="n"/>
-      <c r="G670" t="inlineStr"/>
+      <c r="G670" s="0" t="inlineStr"/>
       <c r="H670" s="3" t="n"/>
       <c r="I670" s="3" t="n"/>
       <c r="J670" s="3" t="n"/>
@@ -23720,7 +23770,7 @@
       <c r="D671" s="4" t="n"/>
       <c r="E671" s="4" t="n"/>
       <c r="F671" s="3" t="n"/>
-      <c r="G671" t="inlineStr"/>
+      <c r="G671" s="0" t="inlineStr"/>
       <c r="H671" s="3" t="n"/>
       <c r="I671" s="3" t="n"/>
       <c r="J671" s="3" t="n"/>
@@ -23749,7 +23799,7 @@
       <c r="D672" s="4" t="n"/>
       <c r="E672" s="4" t="n"/>
       <c r="F672" s="3" t="n"/>
-      <c r="G672" t="inlineStr"/>
+      <c r="G672" s="0" t="inlineStr"/>
       <c r="H672" s="3" t="n"/>
       <c r="I672" s="3" t="n"/>
       <c r="J672" s="3" t="n"/>
@@ -23778,7 +23828,7 @@
       <c r="D673" s="4" t="n"/>
       <c r="E673" s="4" t="n"/>
       <c r="F673" s="3" t="n"/>
-      <c r="G673" t="inlineStr"/>
+      <c r="G673" s="0" t="inlineStr"/>
       <c r="H673" s="3" t="n"/>
       <c r="I673" s="3" t="n"/>
       <c r="J673" s="3" t="n"/>
@@ -23807,7 +23857,7 @@
       <c r="D674" s="4" t="n"/>
       <c r="E674" s="4" t="n"/>
       <c r="F674" s="3" t="n"/>
-      <c r="G674" t="inlineStr"/>
+      <c r="G674" s="0" t="inlineStr"/>
       <c r="H674" s="3" t="n"/>
       <c r="I674" s="3" t="n"/>
       <c r="J674" s="3" t="n"/>
@@ -23836,7 +23886,7 @@
       <c r="D675" s="4" t="n"/>
       <c r="E675" s="4" t="n"/>
       <c r="F675" s="3" t="n"/>
-      <c r="G675" t="inlineStr"/>
+      <c r="G675" s="0" t="inlineStr"/>
       <c r="H675" s="3" t="n"/>
       <c r="I675" s="3" t="n"/>
       <c r="J675" s="3" t="n"/>
@@ -23865,7 +23915,7 @@
       <c r="D676" s="4" t="n"/>
       <c r="E676" s="4" t="n"/>
       <c r="F676" s="3" t="n"/>
-      <c r="G676" t="inlineStr"/>
+      <c r="G676" s="0" t="inlineStr"/>
       <c r="H676" s="3" t="n"/>
       <c r="I676" s="3" t="n"/>
       <c r="J676" s="3" t="n"/>
@@ -23894,7 +23944,7 @@
       <c r="D677" s="4" t="n"/>
       <c r="E677" s="4" t="n"/>
       <c r="F677" s="3" t="n"/>
-      <c r="G677" t="inlineStr"/>
+      <c r="G677" s="0" t="inlineStr"/>
       <c r="H677" s="3" t="n"/>
       <c r="I677" s="3" t="n"/>
       <c r="J677" s="3" t="n"/>
@@ -23923,7 +23973,7 @@
       <c r="D678" s="4" t="n"/>
       <c r="E678" s="4" t="n"/>
       <c r="F678" s="3" t="n"/>
-      <c r="G678" t="inlineStr"/>
+      <c r="G678" s="0" t="inlineStr"/>
       <c r="H678" s="3" t="n"/>
       <c r="I678" s="3" t="n"/>
       <c r="J678" s="3" t="n"/>
@@ -23952,7 +24002,7 @@
       <c r="D679" s="4" t="n"/>
       <c r="E679" s="4" t="n"/>
       <c r="F679" s="3" t="n"/>
-      <c r="G679" t="inlineStr"/>
+      <c r="G679" s="0" t="inlineStr"/>
       <c r="H679" s="3" t="n"/>
       <c r="I679" s="3" t="n"/>
       <c r="J679" s="3" t="n"/>
@@ -23981,7 +24031,7 @@
       <c r="D680" s="4" t="n"/>
       <c r="E680" s="4" t="n"/>
       <c r="F680" s="3" t="n"/>
-      <c r="G680" t="inlineStr"/>
+      <c r="G680" s="0" t="inlineStr"/>
       <c r="H680" s="3" t="n"/>
       <c r="I680" s="3" t="n"/>
       <c r="J680" s="3" t="n"/>
@@ -24010,7 +24060,7 @@
       <c r="D681" s="4" t="n"/>
       <c r="E681" s="4" t="n"/>
       <c r="F681" s="3" t="n"/>
-      <c r="G681" t="inlineStr"/>
+      <c r="G681" s="0" t="inlineStr"/>
       <c r="H681" s="3" t="n"/>
       <c r="I681" s="3" t="n"/>
       <c r="J681" s="3" t="n"/>
@@ -24039,7 +24089,7 @@
       <c r="D682" s="4" t="n"/>
       <c r="E682" s="4" t="n"/>
       <c r="F682" s="3" t="n"/>
-      <c r="G682" t="inlineStr"/>
+      <c r="G682" s="0" t="inlineStr"/>
       <c r="H682" s="3" t="n"/>
       <c r="I682" s="3" t="n"/>
       <c r="J682" s="3" t="n"/>
@@ -24068,7 +24118,7 @@
       <c r="D683" s="4" t="n"/>
       <c r="E683" s="4" t="n"/>
       <c r="F683" s="3" t="n"/>
-      <c r="G683" t="inlineStr"/>
+      <c r="G683" s="0" t="inlineStr"/>
       <c r="H683" s="3" t="n"/>
       <c r="I683" s="3" t="n"/>
       <c r="J683" s="3" t="n"/>
@@ -24097,7 +24147,7 @@
       <c r="D684" s="4" t="n"/>
       <c r="E684" s="4" t="n"/>
       <c r="F684" s="3" t="n"/>
-      <c r="G684" t="inlineStr"/>
+      <c r="G684" s="0" t="inlineStr"/>
       <c r="H684" s="3" t="n"/>
       <c r="I684" s="3" t="n"/>
       <c r="J684" s="3" t="n"/>
@@ -24126,7 +24176,7 @@
       <c r="D685" s="4" t="n"/>
       <c r="E685" s="4" t="n"/>
       <c r="F685" s="3" t="n"/>
-      <c r="G685" t="inlineStr"/>
+      <c r="G685" s="0" t="inlineStr"/>
       <c r="H685" s="3" t="n"/>
       <c r="I685" s="3" t="n"/>
       <c r="J685" s="3" t="n"/>
@@ -24155,7 +24205,7 @@
       <c r="D686" s="4" t="n"/>
       <c r="E686" s="4" t="n"/>
       <c r="F686" s="3" t="n"/>
-      <c r="G686" t="inlineStr"/>
+      <c r="G686" s="0" t="inlineStr"/>
       <c r="H686" s="3" t="n"/>
       <c r="I686" s="3" t="n"/>
       <c r="J686" s="3" t="n"/>
@@ -24184,7 +24234,7 @@
       <c r="D687" s="4" t="n"/>
       <c r="E687" s="4" t="n"/>
       <c r="F687" s="3" t="n"/>
-      <c r="G687" t="inlineStr"/>
+      <c r="G687" s="0" t="inlineStr"/>
       <c r="H687" s="3" t="n"/>
       <c r="I687" s="3" t="n"/>
       <c r="J687" s="3" t="n"/>
@@ -24213,7 +24263,7 @@
       <c r="D688" s="4" t="n"/>
       <c r="E688" s="4" t="n"/>
       <c r="F688" s="3" t="n"/>
-      <c r="G688" t="inlineStr"/>
+      <c r="G688" s="0" t="inlineStr"/>
       <c r="H688" s="3" t="n"/>
       <c r="I688" s="3" t="n"/>
       <c r="J688" s="3" t="n"/>
@@ -24242,7 +24292,7 @@
       <c r="D689" s="4" t="n"/>
       <c r="E689" s="4" t="n"/>
       <c r="F689" s="3" t="n"/>
-      <c r="G689" t="inlineStr"/>
+      <c r="G689" s="0" t="inlineStr"/>
       <c r="H689" s="3" t="n"/>
       <c r="I689" s="3" t="n"/>
       <c r="J689" s="3" t="n"/>
@@ -24271,7 +24321,7 @@
       <c r="D690" s="4" t="n"/>
       <c r="E690" s="4" t="n"/>
       <c r="F690" s="3" t="n"/>
-      <c r="G690" t="inlineStr"/>
+      <c r="G690" s="0" t="inlineStr"/>
       <c r="H690" s="3" t="n"/>
       <c r="I690" s="3" t="n"/>
       <c r="J690" s="3" t="n"/>
@@ -24300,7 +24350,7 @@
       <c r="D691" s="4" t="n"/>
       <c r="E691" s="4" t="n"/>
       <c r="F691" s="3" t="n"/>
-      <c r="G691" t="inlineStr"/>
+      <c r="G691" s="0" t="inlineStr"/>
       <c r="H691" s="3" t="n"/>
       <c r="I691" s="3" t="n"/>
       <c r="J691" s="3" t="n"/>
@@ -24329,7 +24379,7 @@
       <c r="D692" s="4" t="n"/>
       <c r="E692" s="4" t="n"/>
       <c r="F692" s="3" t="n"/>
-      <c r="G692" t="inlineStr"/>
+      <c r="G692" s="0" t="inlineStr"/>
       <c r="H692" s="3" t="n"/>
       <c r="I692" s="3" t="n"/>
       <c r="J692" s="3" t="n"/>
@@ -24358,7 +24408,7 @@
       <c r="D693" s="4" t="n"/>
       <c r="E693" s="4" t="n"/>
       <c r="F693" s="3" t="n"/>
-      <c r="G693" t="inlineStr"/>
+      <c r="G693" s="0" t="inlineStr"/>
       <c r="H693" s="3" t="n"/>
       <c r="I693" s="3" t="n"/>
       <c r="J693" s="3" t="n"/>
@@ -24387,7 +24437,7 @@
       <c r="D694" s="4" t="n"/>
       <c r="E694" s="4" t="n"/>
       <c r="F694" s="3" t="n"/>
-      <c r="G694" t="inlineStr"/>
+      <c r="G694" s="0" t="inlineStr"/>
       <c r="H694" s="3" t="n"/>
       <c r="I694" s="3" t="n"/>
       <c r="J694" s="3" t="n"/>
@@ -24416,7 +24466,7 @@
       <c r="D695" s="4" t="n"/>
       <c r="E695" s="4" t="n"/>
       <c r="F695" s="3" t="n"/>
-      <c r="G695" t="inlineStr"/>
+      <c r="G695" s="0" t="inlineStr"/>
       <c r="H695" s="3" t="n"/>
       <c r="I695" s="3" t="n"/>
       <c r="J695" s="3" t="n"/>
@@ -24445,7 +24495,7 @@
       <c r="D696" s="4" t="n"/>
       <c r="E696" s="4" t="n"/>
       <c r="F696" s="3" t="n"/>
-      <c r="G696" t="inlineStr"/>
+      <c r="G696" s="0" t="inlineStr"/>
       <c r="H696" s="3" t="n"/>
       <c r="I696" s="3" t="n"/>
       <c r="J696" s="3" t="n"/>
@@ -24474,7 +24524,7 @@
       <c r="D697" s="4" t="n"/>
       <c r="E697" s="4" t="n"/>
       <c r="F697" s="3" t="n"/>
-      <c r="G697" t="inlineStr"/>
+      <c r="G697" s="0" t="inlineStr"/>
       <c r="H697" s="3" t="n"/>
       <c r="I697" s="3" t="n"/>
       <c r="J697" s="3" t="n"/>
@@ -24503,7 +24553,7 @@
       <c r="D698" s="4" t="n"/>
       <c r="E698" s="4" t="n"/>
       <c r="F698" s="3" t="n"/>
-      <c r="G698" t="inlineStr"/>
+      <c r="G698" s="0" t="inlineStr"/>
       <c r="H698" s="3" t="n"/>
       <c r="I698" s="3" t="n"/>
       <c r="J698" s="3" t="n"/>
@@ -24532,7 +24582,7 @@
       <c r="D699" s="4" t="n"/>
       <c r="E699" s="4" t="n"/>
       <c r="F699" s="3" t="n"/>
-      <c r="G699" t="inlineStr"/>
+      <c r="G699" s="0" t="inlineStr"/>
       <c r="H699" s="3" t="n"/>
       <c r="I699" s="3" t="n"/>
       <c r="J699" s="3" t="n"/>
@@ -24561,7 +24611,7 @@
       <c r="D700" s="4" t="n"/>
       <c r="E700" s="4" t="n"/>
       <c r="F700" s="3" t="n"/>
-      <c r="G700" t="inlineStr"/>
+      <c r="G700" s="0" t="inlineStr"/>
       <c r="H700" s="3" t="n"/>
       <c r="I700" s="3" t="n"/>
       <c r="J700" s="3" t="n"/>
@@ -24590,7 +24640,7 @@
       <c r="D701" s="4" t="n"/>
       <c r="E701" s="4" t="n"/>
       <c r="F701" s="3" t="n"/>
-      <c r="G701" t="inlineStr"/>
+      <c r="G701" s="0" t="inlineStr"/>
       <c r="H701" s="3" t="n"/>
       <c r="I701" s="3" t="n"/>
       <c r="J701" s="3" t="n"/>
@@ -24619,7 +24669,7 @@
       <c r="D702" s="4" t="n"/>
       <c r="E702" s="4" t="n"/>
       <c r="F702" s="3" t="n"/>
-      <c r="G702" t="inlineStr"/>
+      <c r="G702" s="0" t="inlineStr"/>
       <c r="H702" s="3" t="n"/>
       <c r="I702" s="3" t="n"/>
       <c r="J702" s="3" t="n"/>
@@ -24648,7 +24698,7 @@
       <c r="D703" s="4" t="n"/>
       <c r="E703" s="4" t="n"/>
       <c r="F703" s="3" t="n"/>
-      <c r="G703" t="inlineStr"/>
+      <c r="G703" s="0" t="inlineStr"/>
       <c r="H703" s="3" t="n"/>
       <c r="I703" s="3" t="n"/>
       <c r="J703" s="3" t="n"/>
@@ -24677,7 +24727,7 @@
       <c r="D704" s="4" t="n"/>
       <c r="E704" s="4" t="n"/>
       <c r="F704" s="3" t="n"/>
-      <c r="G704" t="inlineStr"/>
+      <c r="G704" s="0" t="inlineStr"/>
       <c r="H704" s="3" t="n"/>
       <c r="I704" s="3" t="n"/>
       <c r="J704" s="3" t="n"/>
@@ -24706,7 +24756,7 @@
       <c r="D705" s="4" t="n"/>
       <c r="E705" s="4" t="n"/>
       <c r="F705" s="3" t="n"/>
-      <c r="G705" t="inlineStr"/>
+      <c r="G705" s="0" t="inlineStr"/>
       <c r="H705" s="3" t="n"/>
       <c r="I705" s="3" t="n"/>
       <c r="J705" s="3" t="n"/>
@@ -24735,7 +24785,7 @@
       <c r="D706" s="4" t="n"/>
       <c r="E706" s="4" t="n"/>
       <c r="F706" s="3" t="n"/>
-      <c r="G706" t="inlineStr"/>
+      <c r="G706" s="0" t="inlineStr"/>
       <c r="H706" s="3" t="n"/>
       <c r="I706" s="3" t="n"/>
       <c r="J706" s="3" t="n"/>
@@ -24764,7 +24814,7 @@
       <c r="D707" s="4" t="n"/>
       <c r="E707" s="4" t="n"/>
       <c r="F707" s="3" t="n"/>
-      <c r="G707" t="inlineStr"/>
+      <c r="G707" s="0" t="inlineStr"/>
       <c r="H707" s="3" t="n"/>
       <c r="I707" s="3" t="n"/>
       <c r="J707" s="3" t="n"/>
@@ -24793,7 +24843,7 @@
       <c r="D708" s="4" t="n"/>
       <c r="E708" s="4" t="n"/>
       <c r="F708" s="3" t="n"/>
-      <c r="G708" t="inlineStr"/>
+      <c r="G708" s="0" t="inlineStr"/>
       <c r="H708" s="3" t="n"/>
       <c r="I708" s="3" t="n"/>
       <c r="J708" s="3" t="n"/>
@@ -24822,7 +24872,7 @@
       <c r="D709" s="4" t="n"/>
       <c r="E709" s="4" t="n"/>
       <c r="F709" s="3" t="n"/>
-      <c r="G709" t="inlineStr"/>
+      <c r="G709" s="0" t="inlineStr"/>
       <c r="H709" s="3" t="n"/>
       <c r="I709" s="3" t="n"/>
       <c r="J709" s="3" t="n"/>
@@ -24851,7 +24901,7 @@
       <c r="D710" s="4" t="n"/>
       <c r="E710" s="4" t="n"/>
       <c r="F710" s="3" t="n"/>
-      <c r="G710" t="inlineStr"/>
+      <c r="G710" s="0" t="inlineStr"/>
       <c r="H710" s="3" t="n"/>
       <c r="I710" s="3" t="n"/>
       <c r="J710" s="3" t="n"/>
@@ -24880,7 +24930,7 @@
       <c r="D711" s="4" t="n"/>
       <c r="E711" s="4" t="n"/>
       <c r="F711" s="3" t="n"/>
-      <c r="G711" t="inlineStr"/>
+      <c r="G711" s="0" t="inlineStr"/>
       <c r="H711" s="3" t="n"/>
       <c r="I711" s="3" t="n"/>
       <c r="J711" s="3" t="n"/>
@@ -24909,7 +24959,7 @@
       <c r="D712" s="4" t="n"/>
       <c r="E712" s="4" t="n"/>
       <c r="F712" s="3" t="n"/>
-      <c r="G712" t="inlineStr"/>
+      <c r="G712" s="0" t="inlineStr"/>
       <c r="H712" s="3" t="n"/>
       <c r="I712" s="3" t="n"/>
       <c r="J712" s="3" t="n"/>
@@ -24938,7 +24988,7 @@
       <c r="D713" s="4" t="n"/>
       <c r="E713" s="4" t="n"/>
       <c r="F713" s="3" t="n"/>
-      <c r="G713" t="inlineStr"/>
+      <c r="G713" s="0" t="inlineStr"/>
       <c r="H713" s="3" t="n"/>
       <c r="I713" s="3" t="n"/>
       <c r="J713" s="3" t="n"/>
@@ -24967,7 +25017,7 @@
       <c r="D714" s="4" t="n"/>
       <c r="E714" s="4" t="n"/>
       <c r="F714" s="3" t="n"/>
-      <c r="G714" t="inlineStr"/>
+      <c r="G714" s="0" t="inlineStr"/>
       <c r="H714" s="3" t="n"/>
       <c r="I714" s="3" t="n"/>
       <c r="J714" s="3" t="n"/>
@@ -24996,7 +25046,7 @@
       <c r="D715" s="4" t="n"/>
       <c r="E715" s="4" t="n"/>
       <c r="F715" s="3" t="n"/>
-      <c r="G715" t="inlineStr"/>
+      <c r="G715" s="0" t="inlineStr"/>
       <c r="H715" s="3" t="n"/>
       <c r="I715" s="3" t="n"/>
       <c r="J715" s="3" t="n"/>
@@ -25025,7 +25075,7 @@
       <c r="D716" s="4" t="n"/>
       <c r="E716" s="4" t="n"/>
       <c r="F716" s="3" t="n"/>
-      <c r="G716" t="inlineStr"/>
+      <c r="G716" s="0" t="inlineStr"/>
       <c r="H716" s="3" t="n"/>
       <c r="I716" s="3" t="n"/>
       <c r="J716" s="3" t="n"/>
@@ -25054,7 +25104,7 @@
       <c r="D717" s="4" t="n"/>
       <c r="E717" s="4" t="n"/>
       <c r="F717" s="3" t="n"/>
-      <c r="G717" t="inlineStr"/>
+      <c r="G717" s="0" t="inlineStr"/>
       <c r="H717" s="3" t="n"/>
       <c r="I717" s="3" t="n"/>
       <c r="J717" s="3" t="n"/>
@@ -25083,7 +25133,7 @@
       <c r="D718" s="4" t="n"/>
       <c r="E718" s="4" t="n"/>
       <c r="F718" s="3" t="n"/>
-      <c r="G718" t="inlineStr"/>
+      <c r="G718" s="0" t="inlineStr"/>
       <c r="H718" s="3" t="n"/>
       <c r="I718" s="3" t="n"/>
       <c r="J718" s="3" t="n"/>
@@ -25112,7 +25162,7 @@
       <c r="D719" s="4" t="n"/>
       <c r="E719" s="4" t="n"/>
       <c r="F719" s="3" t="n"/>
-      <c r="G719" t="inlineStr"/>
+      <c r="G719" s="0" t="inlineStr"/>
       <c r="H719" s="3" t="n"/>
       <c r="I719" s="3" t="n"/>
       <c r="J719" s="3" t="n"/>
@@ -25141,7 +25191,7 @@
       <c r="D720" s="4" t="n"/>
       <c r="E720" s="4" t="n"/>
       <c r="F720" s="3" t="n"/>
-      <c r="G720" t="inlineStr"/>
+      <c r="G720" s="0" t="inlineStr"/>
       <c r="H720" s="3" t="n"/>
       <c r="I720" s="3" t="n"/>
       <c r="J720" s="3" t="n"/>
@@ -25170,7 +25220,7 @@
       <c r="D721" s="4" t="n"/>
       <c r="E721" s="4" t="n"/>
       <c r="F721" s="3" t="n"/>
-      <c r="G721" t="inlineStr"/>
+      <c r="G721" s="0" t="inlineStr"/>
       <c r="H721" s="3" t="n"/>
       <c r="I721" s="3" t="n"/>
       <c r="J721" s="3" t="n"/>
@@ -25199,7 +25249,7 @@
       <c r="D722" s="4" t="n"/>
       <c r="E722" s="4" t="n"/>
       <c r="F722" s="3" t="n"/>
-      <c r="G722" t="inlineStr"/>
+      <c r="G722" s="0" t="inlineStr"/>
       <c r="H722" s="3" t="n"/>
       <c r="I722" s="3" t="n"/>
       <c r="J722" s="3" t="n"/>
@@ -25228,7 +25278,7 @@
       <c r="D723" s="4" t="n"/>
       <c r="E723" s="4" t="n"/>
       <c r="F723" s="3" t="n"/>
-      <c r="G723" t="inlineStr"/>
+      <c r="G723" s="0" t="inlineStr"/>
       <c r="H723" s="3" t="n"/>
       <c r="I723" s="3" t="n"/>
       <c r="J723" s="3" t="n"/>
@@ -25257,7 +25307,7 @@
       <c r="D724" s="4" t="n"/>
       <c r="E724" s="4" t="n"/>
       <c r="F724" s="3" t="n"/>
-      <c r="G724" t="inlineStr"/>
+      <c r="G724" s="0" t="inlineStr"/>
       <c r="H724" s="3" t="n"/>
       <c r="I724" s="3" t="n"/>
       <c r="J724" s="3" t="n"/>
@@ -25286,7 +25336,7 @@
       <c r="D725" s="4" t="n"/>
       <c r="E725" s="4" t="n"/>
       <c r="F725" s="3" t="n"/>
-      <c r="G725" t="inlineStr"/>
+      <c r="G725" s="0" t="inlineStr"/>
       <c r="H725" s="3" t="n"/>
       <c r="I725" s="3" t="n"/>
       <c r="J725" s="3" t="n"/>
@@ -25315,7 +25365,7 @@
       <c r="D726" s="4" t="n"/>
       <c r="E726" s="4" t="n"/>
       <c r="F726" s="3" t="n"/>
-      <c r="G726" t="inlineStr"/>
+      <c r="G726" s="0" t="inlineStr"/>
       <c r="H726" s="3" t="n"/>
       <c r="I726" s="3" t="n"/>
       <c r="J726" s="3" t="n"/>
@@ -25344,7 +25394,7 @@
       <c r="D727" s="4" t="n"/>
       <c r="E727" s="4" t="n"/>
       <c r="F727" s="3" t="n"/>
-      <c r="G727" t="inlineStr"/>
+      <c r="G727" s="0" t="inlineStr"/>
       <c r="H727" s="3" t="n"/>
       <c r="I727" s="3" t="n"/>
       <c r="J727" s="3" t="n"/>
@@ -25373,7 +25423,7 @@
       <c r="D728" s="4" t="n"/>
       <c r="E728" s="4" t="n"/>
       <c r="F728" s="3" t="n"/>
-      <c r="G728" t="inlineStr"/>
+      <c r="G728" s="0" t="inlineStr"/>
       <c r="H728" s="3" t="n"/>
       <c r="I728" s="3" t="n"/>
       <c r="J728" s="3" t="n"/>
@@ -25402,7 +25452,7 @@
       <c r="D729" s="4" t="n"/>
       <c r="E729" s="4" t="n"/>
       <c r="F729" s="3" t="n"/>
-      <c r="G729" t="inlineStr"/>
+      <c r="G729" s="0" t="inlineStr"/>
       <c r="H729" s="3" t="n"/>
       <c r="I729" s="3" t="n"/>
       <c r="J729" s="3" t="n"/>
@@ -25431,7 +25481,7 @@
       <c r="D730" s="4" t="n"/>
       <c r="E730" s="4" t="n"/>
       <c r="F730" s="3" t="n"/>
-      <c r="G730" t="inlineStr"/>
+      <c r="G730" s="0" t="inlineStr"/>
       <c r="H730" s="3" t="n"/>
       <c r="I730" s="3" t="n"/>
       <c r="J730" s="3" t="n"/>
@@ -25460,7 +25510,7 @@
       <c r="D731" s="4" t="n"/>
       <c r="E731" s="4" t="n"/>
       <c r="F731" s="3" t="n"/>
-      <c r="G731" t="inlineStr"/>
+      <c r="G731" s="0" t="inlineStr"/>
       <c r="H731" s="3" t="n"/>
       <c r="I731" s="3" t="n"/>
       <c r="J731" s="3" t="n"/>
@@ -25489,7 +25539,7 @@
       <c r="D732" s="4" t="n"/>
       <c r="E732" s="4" t="n"/>
       <c r="F732" s="3" t="n"/>
-      <c r="G732" t="inlineStr"/>
+      <c r="G732" s="0" t="inlineStr"/>
       <c r="H732" s="3" t="n"/>
       <c r="I732" s="3" t="n"/>
       <c r="J732" s="3" t="n"/>
@@ -25518,7 +25568,7 @@
       <c r="D733" s="4" t="n"/>
       <c r="E733" s="4" t="n"/>
       <c r="F733" s="3" t="n"/>
-      <c r="G733" t="inlineStr"/>
+      <c r="G733" s="0" t="inlineStr"/>
       <c r="H733" s="3" t="n"/>
       <c r="I733" s="3" t="n"/>
       <c r="J733" s="3" t="n"/>
@@ -25547,7 +25597,7 @@
       <c r="D734" s="4" t="n"/>
       <c r="E734" s="4" t="n"/>
       <c r="F734" s="3" t="n"/>
-      <c r="G734" t="inlineStr"/>
+      <c r="G734" s="0" t="inlineStr"/>
       <c r="H734" s="3" t="n"/>
       <c r="I734" s="3" t="n"/>
       <c r="J734" s="3" t="n"/>
@@ -25576,7 +25626,7 @@
       <c r="D735" s="4" t="n"/>
       <c r="E735" s="4" t="n"/>
       <c r="F735" s="3" t="n"/>
-      <c r="G735" t="inlineStr"/>
+      <c r="G735" s="0" t="inlineStr"/>
       <c r="H735" s="3" t="n"/>
       <c r="I735" s="3" t="n"/>
       <c r="J735" s="3" t="n"/>
@@ -25605,7 +25655,7 @@
       <c r="D736" s="4" t="n"/>
       <c r="E736" s="4" t="n"/>
       <c r="F736" s="3" t="n"/>
-      <c r="G736" t="inlineStr"/>
+      <c r="G736" s="0" t="inlineStr"/>
       <c r="H736" s="3" t="n"/>
       <c r="I736" s="3" t="n"/>
       <c r="J736" s="3" t="n"/>
@@ -25634,7 +25684,7 @@
       <c r="D737" s="4" t="n"/>
       <c r="E737" s="4" t="n"/>
       <c r="F737" s="3" t="n"/>
-      <c r="G737" t="inlineStr"/>
+      <c r="G737" s="0" t="inlineStr"/>
       <c r="H737" s="3" t="n"/>
       <c r="I737" s="3" t="n"/>
       <c r="J737" s="3" t="n"/>
@@ -25663,7 +25713,7 @@
       <c r="D738" s="4" t="n"/>
       <c r="E738" s="4" t="n"/>
       <c r="F738" s="3" t="n"/>
-      <c r="G738" t="inlineStr"/>
+      <c r="G738" s="0" t="inlineStr"/>
       <c r="H738" s="3" t="n"/>
       <c r="I738" s="3" t="n"/>
       <c r="J738" s="3" t="n"/>
@@ -25692,7 +25742,7 @@
       <c r="D739" s="4" t="n"/>
       <c r="E739" s="4" t="n"/>
       <c r="F739" s="3" t="n"/>
-      <c r="G739" t="inlineStr"/>
+      <c r="G739" s="0" t="inlineStr"/>
       <c r="H739" s="3" t="n"/>
       <c r="I739" s="3" t="n"/>
       <c r="J739" s="3" t="n"/>
@@ -25721,7 +25771,7 @@
       <c r="D740" s="4" t="n"/>
       <c r="E740" s="4" t="n"/>
       <c r="F740" s="3" t="n"/>
-      <c r="G740" t="inlineStr"/>
+      <c r="G740" s="0" t="inlineStr"/>
       <c r="H740" s="3" t="n"/>
       <c r="I740" s="3" t="n"/>
       <c r="J740" s="3" t="n"/>
@@ -25750,7 +25800,7 @@
       <c r="D741" s="4" t="n"/>
       <c r="E741" s="4" t="n"/>
       <c r="F741" s="3" t="n"/>
-      <c r="G741" t="inlineStr"/>
+      <c r="G741" s="0" t="inlineStr"/>
       <c r="H741" s="3" t="n"/>
       <c r="I741" s="3" t="n"/>
       <c r="J741" s="3" t="n"/>
@@ -25779,7 +25829,7 @@
       <c r="D742" s="4" t="n"/>
       <c r="E742" s="4" t="n"/>
       <c r="F742" s="3" t="n"/>
-      <c r="G742" t="inlineStr"/>
+      <c r="G742" s="0" t="inlineStr"/>
       <c r="H742" s="3" t="n"/>
       <c r="I742" s="3" t="n"/>
       <c r="J742" s="3" t="n"/>
@@ -25808,7 +25858,7 @@
       <c r="D743" s="4" t="n"/>
       <c r="E743" s="4" t="n"/>
       <c r="F743" s="3" t="n"/>
-      <c r="G743" t="inlineStr"/>
+      <c r="G743" s="0" t="inlineStr"/>
       <c r="H743" s="3" t="n"/>
       <c r="I743" s="3" t="n"/>
       <c r="J743" s="3" t="n"/>
@@ -25837,7 +25887,7 @@
       <c r="D744" s="4" t="n"/>
       <c r="E744" s="4" t="n"/>
       <c r="F744" s="3" t="n"/>
-      <c r="G744" t="inlineStr"/>
+      <c r="G744" s="0" t="inlineStr"/>
       <c r="H744" s="3" t="n"/>
       <c r="I744" s="3" t="n"/>
       <c r="J744" s="3" t="n"/>
@@ -25866,7 +25916,7 @@
       <c r="D745" s="4" t="n"/>
       <c r="E745" s="4" t="n"/>
       <c r="F745" s="3" t="n"/>
-      <c r="G745" t="inlineStr"/>
+      <c r="G745" s="0" t="inlineStr"/>
       <c r="H745" s="3" t="n"/>
       <c r="I745" s="3" t="n"/>
       <c r="J745" s="3" t="n"/>
@@ -25895,7 +25945,7 @@
       <c r="D746" s="4" t="n"/>
       <c r="E746" s="4" t="n"/>
       <c r="F746" s="3" t="n"/>
-      <c r="G746" t="inlineStr"/>
+      <c r="G746" s="0" t="inlineStr"/>
       <c r="H746" s="3" t="n"/>
       <c r="I746" s="3" t="n"/>
       <c r="J746" s="3" t="n"/>
@@ -25924,7 +25974,7 @@
       <c r="D747" s="4" t="n"/>
       <c r="E747" s="4" t="n"/>
       <c r="F747" s="3" t="n"/>
-      <c r="G747" t="inlineStr"/>
+      <c r="G747" s="0" t="inlineStr"/>
       <c r="H747" s="3" t="n"/>
       <c r="I747" s="3" t="n"/>
       <c r="J747" s="3" t="n"/>
@@ -25953,7 +26003,7 @@
       <c r="D748" s="4" t="n"/>
       <c r="E748" s="4" t="n"/>
       <c r="F748" s="3" t="n"/>
-      <c r="G748" t="inlineStr"/>
+      <c r="G748" s="0" t="inlineStr"/>
       <c r="H748" s="3" t="n"/>
       <c r="I748" s="3" t="n"/>
       <c r="J748" s="3" t="n"/>
@@ -25982,7 +26032,7 @@
       <c r="D749" s="4" t="n"/>
       <c r="E749" s="4" t="n"/>
       <c r="F749" s="3" t="n"/>
-      <c r="G749" t="inlineStr"/>
+      <c r="G749" s="0" t="inlineStr"/>
       <c r="H749" s="3" t="n"/>
       <c r="I749" s="3" t="n"/>
       <c r="J749" s="3" t="n"/>
@@ -26011,7 +26061,7 @@
       <c r="D750" s="4" t="n"/>
       <c r="E750" s="4" t="n"/>
       <c r="F750" s="3" t="n"/>
-      <c r="G750" t="inlineStr"/>
+      <c r="G750" s="0" t="inlineStr"/>
       <c r="H750" s="3" t="n"/>
       <c r="I750" s="3" t="n"/>
       <c r="J750" s="3" t="n"/>
@@ -26040,7 +26090,7 @@
       <c r="D751" s="4" t="n"/>
       <c r="E751" s="4" t="n"/>
       <c r="F751" s="3" t="n"/>
-      <c r="G751" t="inlineStr"/>
+      <c r="G751" s="0" t="inlineStr"/>
       <c r="H751" s="3" t="n"/>
       <c r="I751" s="3" t="n"/>
       <c r="J751" s="3" t="n"/>
@@ -26069,7 +26119,7 @@
       <c r="D752" s="4" t="n"/>
       <c r="E752" s="4" t="n"/>
       <c r="F752" s="3" t="n"/>
-      <c r="G752" t="inlineStr"/>
+      <c r="G752" s="0" t="inlineStr"/>
       <c r="H752" s="3" t="n"/>
       <c r="I752" s="3" t="n"/>
       <c r="J752" s="3" t="n"/>
@@ -26098,7 +26148,7 @@
       <c r="D753" s="4" t="n"/>
       <c r="E753" s="4" t="n"/>
       <c r="F753" s="3" t="n"/>
-      <c r="G753" t="inlineStr"/>
+      <c r="G753" s="0" t="inlineStr"/>
       <c r="H753" s="3" t="n"/>
       <c r="I753" s="3" t="n"/>
       <c r="J753" s="3" t="n"/>
@@ -26127,7 +26177,7 @@
       <c r="D754" s="4" t="n"/>
       <c r="E754" s="4" t="n"/>
       <c r="F754" s="3" t="n"/>
-      <c r="G754" t="inlineStr"/>
+      <c r="G754" s="0" t="inlineStr"/>
       <c r="H754" s="3" t="n"/>
       <c r="I754" s="3" t="n"/>
       <c r="J754" s="3" t="n"/>
@@ -26156,7 +26206,7 @@
       <c r="D755" s="4" t="n"/>
       <c r="E755" s="4" t="n"/>
       <c r="F755" s="3" t="n"/>
-      <c r="G755" t="inlineStr"/>
+      <c r="G755" s="0" t="inlineStr"/>
       <c r="H755" s="3" t="n"/>
       <c r="I755" s="3" t="n"/>
       <c r="J755" s="3" t="n"/>
@@ -26185,7 +26235,7 @@
       <c r="D756" s="4" t="n"/>
       <c r="E756" s="4" t="n"/>
       <c r="F756" s="3" t="n"/>
-      <c r="G756" t="inlineStr"/>
+      <c r="G756" s="0" t="inlineStr"/>
       <c r="H756" s="3" t="n"/>
       <c r="I756" s="3" t="n"/>
       <c r="J756" s="3" t="n"/>
@@ -26214,7 +26264,7 @@
       <c r="D757" s="4" t="n"/>
       <c r="E757" s="4" t="n"/>
       <c r="F757" s="3" t="n"/>
-      <c r="G757" t="inlineStr"/>
+      <c r="G757" s="0" t="inlineStr"/>
       <c r="H757" s="3" t="n"/>
       <c r="I757" s="3" t="n"/>
       <c r="J757" s="3" t="n"/>
@@ -26243,7 +26293,7 @@
       <c r="D758" s="4" t="n"/>
       <c r="E758" s="4" t="n"/>
       <c r="F758" s="3" t="n"/>
-      <c r="G758" t="inlineStr"/>
+      <c r="G758" s="0" t="inlineStr"/>
       <c r="H758" s="3" t="n"/>
       <c r="I758" s="3" t="n"/>
       <c r="J758" s="3" t="n"/>
@@ -26272,7 +26322,7 @@
       <c r="D759" s="4" t="n"/>
       <c r="E759" s="4" t="n"/>
       <c r="F759" s="3" t="n"/>
-      <c r="G759" t="inlineStr"/>
+      <c r="G759" s="0" t="inlineStr"/>
       <c r="H759" s="3" t="n"/>
       <c r="I759" s="3" t="n"/>
       <c r="J759" s="3" t="n"/>
@@ -26301,7 +26351,7 @@
       <c r="D760" s="4" t="n"/>
       <c r="E760" s="4" t="n"/>
       <c r="F760" s="3" t="n"/>
-      <c r="G760" t="inlineStr"/>
+      <c r="G760" s="0" t="inlineStr"/>
       <c r="H760" s="3" t="n"/>
       <c r="I760" s="3" t="n"/>
       <c r="J760" s="3" t="n"/>
@@ -26330,7 +26380,7 @@
       <c r="D761" s="4" t="n"/>
       <c r="E761" s="4" t="n"/>
       <c r="F761" s="3" t="n"/>
-      <c r="G761" t="inlineStr"/>
+      <c r="G761" s="0" t="inlineStr"/>
       <c r="H761" s="3" t="n"/>
       <c r="I761" s="3" t="n"/>
       <c r="J761" s="3" t="n"/>
@@ -26359,7 +26409,7 @@
       <c r="D762" s="4" t="n"/>
       <c r="E762" s="4" t="n"/>
       <c r="F762" s="3" t="n"/>
-      <c r="G762" t="inlineStr"/>
+      <c r="G762" s="0" t="inlineStr"/>
       <c r="H762" s="3" t="n"/>
       <c r="I762" s="3" t="n"/>
       <c r="J762" s="3" t="n"/>
@@ -26388,7 +26438,7 @@
       <c r="D763" s="4" t="n"/>
       <c r="E763" s="4" t="n"/>
       <c r="F763" s="3" t="n"/>
-      <c r="G763" t="inlineStr"/>
+      <c r="G763" s="0" t="inlineStr"/>
       <c r="H763" s="3" t="n"/>
       <c r="I763" s="3" t="n"/>
       <c r="J763" s="3" t="n"/>
@@ -26417,7 +26467,7 @@
       <c r="D764" s="4" t="n"/>
       <c r="E764" s="4" t="n"/>
       <c r="F764" s="3" t="n"/>
-      <c r="G764" t="inlineStr"/>
+      <c r="G764" s="0" t="inlineStr"/>
       <c r="H764" s="3" t="n"/>
       <c r="I764" s="3" t="n"/>
       <c r="J764" s="3" t="n"/>
@@ -26446,7 +26496,7 @@
       <c r="D765" s="4" t="n"/>
       <c r="E765" s="4" t="n"/>
       <c r="F765" s="3" t="n"/>
-      <c r="G765" t="inlineStr"/>
+      <c r="G765" s="0" t="inlineStr"/>
       <c r="H765" s="3" t="n"/>
       <c r="I765" s="3" t="n"/>
       <c r="J765" s="3" t="n"/>
@@ -26475,7 +26525,7 @@
       <c r="D766" s="4" t="n"/>
       <c r="E766" s="4" t="n"/>
       <c r="F766" s="3" t="n"/>
-      <c r="G766" t="inlineStr"/>
+      <c r="G766" s="0" t="inlineStr"/>
       <c r="H766" s="3" t="n"/>
       <c r="I766" s="3" t="n"/>
       <c r="J766" s="3" t="n"/>
@@ -26504,7 +26554,7 @@
       <c r="D767" s="4" t="n"/>
       <c r="E767" s="4" t="n"/>
       <c r="F767" s="3" t="n"/>
-      <c r="G767" t="inlineStr"/>
+      <c r="G767" s="0" t="inlineStr"/>
       <c r="H767" s="3" t="n"/>
       <c r="I767" s="3" t="n"/>
       <c r="J767" s="3" t="n"/>
@@ -26533,7 +26583,7 @@
       <c r="D768" s="4" t="n"/>
       <c r="E768" s="4" t="n"/>
       <c r="F768" s="3" t="n"/>
-      <c r="G768" t="inlineStr"/>
+      <c r="G768" s="0" t="inlineStr"/>
       <c r="H768" s="3" t="n"/>
       <c r="I768" s="3" t="n"/>
       <c r="J768" s="3" t="n"/>
@@ -26562,7 +26612,7 @@
       <c r="D769" s="4" t="n"/>
       <c r="E769" s="4" t="n"/>
       <c r="F769" s="3" t="n"/>
-      <c r="G769" t="inlineStr"/>
+      <c r="G769" s="0" t="inlineStr"/>
       <c r="H769" s="3" t="n"/>
       <c r="I769" s="3" t="n"/>
       <c r="J769" s="3" t="n"/>
@@ -26591,7 +26641,7 @@
       <c r="D770" s="4" t="n"/>
       <c r="E770" s="4" t="n"/>
       <c r="F770" s="3" t="n"/>
-      <c r="G770" t="inlineStr"/>
+      <c r="G770" s="0" t="inlineStr"/>
       <c r="H770" s="3" t="n"/>
       <c r="I770" s="3" t="n"/>
       <c r="J770" s="3" t="n"/>
@@ -26620,7 +26670,7 @@
       <c r="D771" s="4" t="n"/>
       <c r="E771" s="4" t="n"/>
       <c r="F771" s="3" t="n"/>
-      <c r="G771" t="inlineStr"/>
+      <c r="G771" s="0" t="inlineStr"/>
       <c r="H771" s="3" t="n"/>
       <c r="I771" s="3" t="n"/>
       <c r="J771" s="3" t="n"/>
@@ -26649,7 +26699,7 @@
       <c r="D772" s="4" t="n"/>
       <c r="E772" s="4" t="n"/>
       <c r="F772" s="3" t="n"/>
-      <c r="G772" t="inlineStr"/>
+      <c r="G772" s="0" t="inlineStr"/>
       <c r="H772" s="3" t="n"/>
       <c r="I772" s="3" t="n"/>
       <c r="J772" s="3" t="n"/>
@@ -26678,7 +26728,7 @@
       <c r="D773" s="4" t="n"/>
       <c r="E773" s="4" t="n"/>
       <c r="F773" s="3" t="n"/>
-      <c r="G773" t="inlineStr"/>
+      <c r="G773" s="0" t="inlineStr"/>
       <c r="H773" s="3" t="n"/>
       <c r="I773" s="3" t="n"/>
       <c r="J773" s="3" t="n"/>
@@ -26707,7 +26757,7 @@
       <c r="D774" s="4" t="n"/>
       <c r="E774" s="4" t="n"/>
       <c r="F774" s="3" t="n"/>
-      <c r="G774" t="inlineStr"/>
+      <c r="G774" s="0" t="inlineStr"/>
       <c r="H774" s="3" t="n"/>
       <c r="I774" s="3" t="n"/>
       <c r="J774" s="3" t="n"/>
@@ -26736,7 +26786,7 @@
       <c r="D775" s="4" t="n"/>
       <c r="E775" s="4" t="n"/>
       <c r="F775" s="3" t="n"/>
-      <c r="G775" t="inlineStr"/>
+      <c r="G775" s="0" t="inlineStr"/>
       <c r="H775" s="3" t="n"/>
       <c r="I775" s="3" t="n"/>
       <c r="J775" s="3" t="n"/>
@@ -26765,7 +26815,7 @@
       <c r="D776" s="4" t="n"/>
       <c r="E776" s="4" t="n"/>
       <c r="F776" s="3" t="n"/>
-      <c r="G776" t="inlineStr"/>
+      <c r="G776" s="0" t="inlineStr"/>
       <c r="H776" s="3" t="n"/>
       <c r="I776" s="3" t="n"/>
       <c r="J776" s="3" t="n"/>
@@ -26794,7 +26844,7 @@
       <c r="D777" s="4" t="n"/>
       <c r="E777" s="4" t="n"/>
       <c r="F777" s="3" t="n"/>
-      <c r="G777" t="inlineStr"/>
+      <c r="G777" s="0" t="inlineStr"/>
       <c r="H777" s="3" t="n"/>
       <c r="I777" s="3" t="n"/>
       <c r="J777" s="3" t="n"/>
@@ -26823,7 +26873,7 @@
       <c r="D778" s="4" t="n"/>
       <c r="E778" s="4" t="n"/>
       <c r="F778" s="3" t="n"/>
-      <c r="G778" t="inlineStr"/>
+      <c r="G778" s="0" t="inlineStr"/>
       <c r="H778" s="3" t="n"/>
       <c r="I778" s="3" t="n"/>
       <c r="J778" s="3" t="n"/>
@@ -26852,7 +26902,7 @@
       <c r="D779" s="4" t="n"/>
       <c r="E779" s="4" t="n"/>
       <c r="F779" s="3" t="n"/>
-      <c r="G779" t="inlineStr"/>
+      <c r="G779" s="0" t="inlineStr"/>
       <c r="H779" s="3" t="n"/>
       <c r="I779" s="3" t="n"/>
       <c r="J779" s="3" t="n"/>
@@ -26881,7 +26931,7 @@
       <c r="D780" s="4" t="n"/>
       <c r="E780" s="4" t="n"/>
       <c r="F780" s="3" t="n"/>
-      <c r="G780" t="inlineStr"/>
+      <c r="G780" s="0" t="inlineStr"/>
       <c r="H780" s="3" t="n"/>
       <c r="I780" s="3" t="n"/>
       <c r="J780" s="3" t="n"/>
@@ -26910,7 +26960,7 @@
       <c r="D781" s="4" t="n"/>
       <c r="E781" s="4" t="n"/>
       <c r="F781" s="3" t="n"/>
-      <c r="G781" t="inlineStr"/>
+      <c r="G781" s="0" t="inlineStr"/>
       <c r="H781" s="3" t="n"/>
       <c r="I781" s="3" t="n"/>
       <c r="J781" s="3" t="n"/>
@@ -26939,7 +26989,7 @@
       <c r="D782" s="4" t="n"/>
       <c r="E782" s="4" t="n"/>
       <c r="F782" s="3" t="n"/>
-      <c r="G782" t="inlineStr"/>
+      <c r="G782" s="0" t="inlineStr"/>
       <c r="H782" s="3" t="n"/>
       <c r="I782" s="3" t="n"/>
       <c r="J782" s="3" t="n"/>
@@ -26968,7 +27018,7 @@
       <c r="D783" s="4" t="n"/>
       <c r="E783" s="4" t="n"/>
       <c r="F783" s="3" t="n"/>
-      <c r="G783" t="inlineStr"/>
+      <c r="G783" s="0" t="inlineStr"/>
       <c r="H783" s="3" t="n"/>
       <c r="I783" s="3" t="n"/>
       <c r="J783" s="3" t="n"/>
@@ -26997,7 +27047,7 @@
       <c r="D784" s="4" t="n"/>
       <c r="E784" s="4" t="n"/>
       <c r="F784" s="3" t="n"/>
-      <c r="G784" t="inlineStr"/>
+      <c r="G784" s="0" t="inlineStr"/>
       <c r="H784" s="3" t="n"/>
       <c r="I784" s="3" t="n"/>
       <c r="J784" s="3" t="n"/>
@@ -27026,7 +27076,7 @@
       <c r="D785" s="4" t="n"/>
       <c r="E785" s="4" t="n"/>
       <c r="F785" s="3" t="n"/>
-      <c r="G785" t="inlineStr"/>
+      <c r="G785" s="0" t="inlineStr"/>
       <c r="H785" s="3" t="n"/>
       <c r="I785" s="3" t="n"/>
       <c r="J785" s="3" t="n"/>
@@ -27055,7 +27105,7 @@
       <c r="D786" s="4" t="n"/>
       <c r="E786" s="4" t="n"/>
       <c r="F786" s="3" t="n"/>
-      <c r="G786" t="inlineStr"/>
+      <c r="G786" s="0" t="inlineStr"/>
       <c r="H786" s="3" t="n"/>
       <c r="I786" s="3" t="n"/>
       <c r="J786" s="3" t="n"/>
@@ -27084,7 +27134,7 @@
       <c r="D787" s="4" t="n"/>
       <c r="E787" s="4" t="n"/>
       <c r="F787" s="3" t="n"/>
-      <c r="G787" t="inlineStr"/>
+      <c r="G787" s="0" t="inlineStr"/>
       <c r="H787" s="3" t="n"/>
       <c r="I787" s="3" t="n"/>
       <c r="J787" s="3" t="n"/>
@@ -27113,7 +27163,7 @@
       <c r="D788" s="4" t="n"/>
       <c r="E788" s="4" t="n"/>
       <c r="F788" s="3" t="n"/>
-      <c r="G788" t="inlineStr"/>
+      <c r="G788" s="0" t="inlineStr"/>
       <c r="H788" s="3" t="n"/>
       <c r="I788" s="3" t="n"/>
       <c r="J788" s="3" t="n"/>
@@ -27142,7 +27192,7 @@
       <c r="D789" s="4" t="n"/>
       <c r="E789" s="4" t="n"/>
       <c r="F789" s="3" t="n"/>
-      <c r="G789" t="inlineStr"/>
+      <c r="G789" s="0" t="inlineStr"/>
       <c r="H789" s="3" t="n"/>
       <c r="I789" s="3" t="n"/>
       <c r="J789" s="3" t="n"/>
@@ -27171,7 +27221,7 @@
       <c r="D790" s="4" t="n"/>
       <c r="E790" s="4" t="n"/>
       <c r="F790" s="3" t="n"/>
-      <c r="G790" t="inlineStr"/>
+      <c r="G790" s="0" t="inlineStr"/>
       <c r="H790" s="3" t="n"/>
       <c r="I790" s="3" t="n"/>
       <c r="J790" s="3" t="n"/>
@@ -27200,7 +27250,7 @@
       <c r="D791" s="4" t="n"/>
       <c r="E791" s="4" t="n"/>
       <c r="F791" s="3" t="n"/>
-      <c r="G791" t="inlineStr"/>
+      <c r="G791" s="0" t="inlineStr"/>
       <c r="H791" s="3" t="n"/>
       <c r="I791" s="3" t="n"/>
       <c r="J791" s="3" t="n"/>
@@ -27229,7 +27279,7 @@
       <c r="D792" s="4" t="n"/>
       <c r="E792" s="4" t="n"/>
       <c r="F792" s="3" t="n"/>
-      <c r="G792" t="inlineStr"/>
+      <c r="G792" s="0" t="inlineStr"/>
       <c r="H792" s="3" t="n"/>
       <c r="I792" s="3" t="n"/>
       <c r="J792" s="3" t="n"/>
@@ -27258,7 +27308,7 @@
       <c r="D793" s="4" t="n"/>
       <c r="E793" s="4" t="n"/>
       <c r="F793" s="3" t="n"/>
-      <c r="G793" t="inlineStr"/>
+      <c r="G793" s="0" t="inlineStr"/>
       <c r="H793" s="3" t="n"/>
       <c r="I793" s="3" t="n"/>
       <c r="J793" s="3" t="n"/>
@@ -27287,7 +27337,7 @@
       <c r="D794" s="4" t="n"/>
       <c r="E794" s="4" t="n"/>
       <c r="F794" s="3" t="n"/>
-      <c r="G794" t="inlineStr"/>
+      <c r="G794" s="0" t="inlineStr"/>
       <c r="H794" s="3" t="n"/>
       <c r="I794" s="3" t="n"/>
       <c r="J794" s="3" t="n"/>
@@ -27316,7 +27366,7 @@
       <c r="D795" s="4" t="n"/>
       <c r="E795" s="4" t="n"/>
       <c r="F795" s="3" t="n"/>
-      <c r="G795" t="inlineStr"/>
+      <c r="G795" s="0" t="inlineStr"/>
       <c r="H795" s="3" t="n"/>
       <c r="I795" s="3" t="n"/>
       <c r="J795" s="3" t="n"/>
@@ -27345,7 +27395,7 @@
       <c r="D796" s="4" t="n"/>
       <c r="E796" s="4" t="n"/>
       <c r="F796" s="3" t="n"/>
-      <c r="G796" t="inlineStr"/>
+      <c r="G796" s="0" t="inlineStr"/>
       <c r="H796" s="3" t="n"/>
       <c r="I796" s="3" t="n"/>
       <c r="J796" s="3" t="n"/>
@@ -27374,7 +27424,7 @@
       <c r="D797" s="4" t="n"/>
       <c r="E797" s="4" t="n"/>
       <c r="F797" s="3" t="n"/>
-      <c r="G797" t="inlineStr"/>
+      <c r="G797" s="0" t="inlineStr"/>
       <c r="H797" s="3" t="n"/>
       <c r="I797" s="3" t="n"/>
       <c r="J797" s="3" t="n"/>
@@ -27403,7 +27453,7 @@
       <c r="D798" s="4" t="n"/>
       <c r="E798" s="4" t="n"/>
       <c r="F798" s="3" t="n"/>
-      <c r="G798" t="inlineStr"/>
+      <c r="G798" s="0" t="inlineStr"/>
       <c r="H798" s="3" t="n"/>
       <c r="I798" s="3" t="n"/>
       <c r="J798" s="3" t="n"/>
@@ -27432,7 +27482,7 @@
       <c r="D799" s="4" t="n"/>
       <c r="E799" s="4" t="n"/>
       <c r="F799" s="3" t="n"/>
-      <c r="G799" t="inlineStr"/>
+      <c r="G799" s="0" t="inlineStr"/>
       <c r="H799" s="3" t="n"/>
       <c r="I799" s="3" t="n"/>
       <c r="J799" s="3" t="n"/>
@@ -27461,7 +27511,7 @@
       <c r="D800" s="4" t="n"/>
       <c r="E800" s="4" t="n"/>
       <c r="F800" s="3" t="n"/>
-      <c r="G800" t="inlineStr"/>
+      <c r="G800" s="0" t="inlineStr"/>
       <c r="H800" s="3" t="n"/>
       <c r="I800" s="3" t="n"/>
       <c r="J800" s="3" t="n"/>
@@ -27490,7 +27540,7 @@
       <c r="D801" s="4" t="n"/>
       <c r="E801" s="4" t="n"/>
       <c r="F801" s="3" t="n"/>
-      <c r="G801" t="inlineStr"/>
+      <c r="G801" s="0" t="inlineStr"/>
       <c r="H801" s="3" t="n"/>
       <c r="I801" s="3" t="n"/>
       <c r="J801" s="3" t="n"/>
@@ -27519,7 +27569,7 @@
       <c r="D802" s="4" t="n"/>
       <c r="E802" s="4" t="n"/>
       <c r="F802" s="3" t="n"/>
-      <c r="G802" t="inlineStr"/>
+      <c r="G802" s="0" t="inlineStr"/>
       <c r="H802" s="3" t="n"/>
       <c r="I802" s="3" t="n"/>
       <c r="J802" s="3" t="n"/>
@@ -27548,7 +27598,7 @@
       <c r="D803" s="4" t="n"/>
       <c r="E803" s="4" t="n"/>
       <c r="F803" s="3" t="n"/>
-      <c r="G803" t="inlineStr"/>
+      <c r="G803" s="0" t="inlineStr"/>
       <c r="H803" s="3" t="n"/>
       <c r="I803" s="3" t="n"/>
       <c r="J803" s="3" t="n"/>
@@ -27577,7 +27627,7 @@
       <c r="D804" s="4" t="n"/>
       <c r="E804" s="4" t="n"/>
       <c r="F804" s="3" t="n"/>
-      <c r="G804" t="inlineStr"/>
+      <c r="G804" s="0" t="inlineStr"/>
       <c r="H804" s="3" t="n"/>
       <c r="I804" s="3" t="n"/>
       <c r="J804" s="3" t="n"/>
@@ -27606,7 +27656,7 @@
       <c r="D805" s="4" t="n"/>
       <c r="E805" s="4" t="n"/>
       <c r="F805" s="3" t="n"/>
-      <c r="G805" t="inlineStr"/>
+      <c r="G805" s="0" t="inlineStr"/>
       <c r="H805" s="3" t="n"/>
       <c r="I805" s="3" t="n"/>
       <c r="J805" s="3" t="n"/>
@@ -27635,7 +27685,7 @@
       <c r="D806" s="4" t="n"/>
       <c r="E806" s="4" t="n"/>
       <c r="F806" s="3" t="n"/>
-      <c r="G806" t="inlineStr"/>
+      <c r="G806" s="0" t="inlineStr"/>
       <c r="H806" s="3" t="n"/>
       <c r="I806" s="3" t="n"/>
       <c r="J806" s="3" t="n"/>
@@ -27664,7 +27714,7 @@
       <c r="D807" s="4" t="n"/>
       <c r="E807" s="4" t="n"/>
       <c r="F807" s="3" t="n"/>
-      <c r="G807" t="inlineStr"/>
+      <c r="G807" s="0" t="inlineStr"/>
       <c r="H807" s="3" t="n"/>
       <c r="I807" s="3" t="n"/>
       <c r="J807" s="3" t="n"/>
@@ -27693,7 +27743,7 @@
       <c r="D808" s="4" t="n"/>
       <c r="E808" s="4" t="n"/>
       <c r="F808" s="3" t="n"/>
-      <c r="G808" t="inlineStr"/>
+      <c r="G808" s="0" t="inlineStr"/>
       <c r="H808" s="3" t="n"/>
       <c r="I808" s="3" t="n"/>
       <c r="J808" s="3" t="n"/>
@@ -27722,7 +27772,7 @@
       <c r="D809" s="4" t="n"/>
       <c r="E809" s="4" t="n"/>
       <c r="F809" s="3" t="n"/>
-      <c r="G809" t="inlineStr"/>
+      <c r="G809" s="0" t="inlineStr"/>
       <c r="H809" s="3" t="n"/>
       <c r="I809" s="3" t="n"/>
       <c r="J809" s="3" t="n"/>
@@ -27751,7 +27801,7 @@
       <c r="D810" s="4" t="n"/>
       <c r="E810" s="4" t="n"/>
       <c r="F810" s="3" t="n"/>
-      <c r="G810" t="inlineStr"/>
+      <c r="G810" s="0" t="inlineStr"/>
       <c r="H810" s="3" t="n"/>
       <c r="I810" s="3" t="n"/>
       <c r="J810" s="3" t="n"/>
@@ -27780,7 +27830,7 @@
       <c r="D811" s="4" t="n"/>
       <c r="E811" s="4" t="n"/>
       <c r="F811" s="3" t="n"/>
-      <c r="G811" t="inlineStr"/>
+      <c r="G811" s="0" t="inlineStr"/>
       <c r="H811" s="3" t="n"/>
       <c r="I811" s="3" t="n"/>
       <c r="J811" s="3" t="n"/>
@@ -27809,7 +27859,7 @@
       <c r="D812" s="4" t="n"/>
       <c r="E812" s="4" t="n"/>
       <c r="F812" s="3" t="n"/>
-      <c r="G812" t="inlineStr"/>
+      <c r="G812" s="0" t="inlineStr"/>
       <c r="H812" s="3" t="n"/>
       <c r="I812" s="3" t="n"/>
       <c r="J812" s="3" t="n"/>
@@ -27838,7 +27888,7 @@
       <c r="D813" s="4" t="n"/>
       <c r="E813" s="4" t="n"/>
       <c r="F813" s="3" t="n"/>
-      <c r="G813" t="inlineStr"/>
+      <c r="G813" s="0" t="inlineStr"/>
       <c r="H813" s="3" t="n"/>
       <c r="I813" s="3" t="n"/>
       <c r="J813" s="3" t="n"/>
@@ -27867,7 +27917,7 @@
       <c r="D814" s="4" t="n"/>
       <c r="E814" s="4" t="n"/>
       <c r="F814" s="3" t="n"/>
-      <c r="G814" t="inlineStr"/>
+      <c r="G814" s="0" t="inlineStr"/>
       <c r="H814" s="3" t="n"/>
       <c r="I814" s="3" t="n"/>
       <c r="J814" s="3" t="n"/>
@@ -27896,7 +27946,7 @@
       <c r="D815" s="4" t="n"/>
       <c r="E815" s="4" t="n"/>
       <c r="F815" s="3" t="n"/>
-      <c r="G815" t="inlineStr"/>
+      <c r="G815" s="0" t="inlineStr"/>
       <c r="H815" s="3" t="n"/>
       <c r="I815" s="3" t="n"/>
       <c r="J815" s="3" t="n"/>
@@ -27925,7 +27975,7 @@
       <c r="D816" s="4" t="n"/>
       <c r="E816" s="4" t="n"/>
       <c r="F816" s="3" t="n"/>
-      <c r="G816" t="inlineStr"/>
+      <c r="G816" s="0" t="inlineStr"/>
       <c r="H816" s="3" t="n"/>
       <c r="I816" s="3" t="n"/>
       <c r="J816" s="3" t="n"/>
@@ -27954,7 +28004,7 @@
       <c r="D817" s="4" t="n"/>
       <c r="E817" s="4" t="n"/>
       <c r="F817" s="3" t="n"/>
-      <c r="G817" t="inlineStr"/>
+      <c r="G817" s="0" t="inlineStr"/>
       <c r="H817" s="3" t="n"/>
       <c r="I817" s="3" t="n"/>
       <c r="J817" s="3" t="n"/>
@@ -27983,7 +28033,7 @@
       <c r="D818" s="4" t="n"/>
       <c r="E818" s="4" t="n"/>
       <c r="F818" s="3" t="n"/>
-      <c r="G818" t="inlineStr"/>
+      <c r="G818" s="0" t="inlineStr"/>
       <c r="H818" s="3" t="n"/>
       <c r="I818" s="3" t="n"/>
       <c r="J818" s="3" t="n"/>
@@ -28012,7 +28062,7 @@
       <c r="D819" s="4" t="n"/>
       <c r="E819" s="4" t="n"/>
       <c r="F819" s="3" t="n"/>
-      <c r="G819" t="inlineStr"/>
+      <c r="G819" s="0" t="inlineStr"/>
       <c r="H819" s="3" t="n"/>
       <c r="I819" s="3" t="n"/>
       <c r="J819" s="3" t="n"/>
@@ -28041,7 +28091,7 @@
       <c r="D820" s="4" t="n"/>
       <c r="E820" s="4" t="n"/>
       <c r="F820" s="3" t="n"/>
-      <c r="G820" t="inlineStr"/>
+      <c r="G820" s="0" t="inlineStr"/>
       <c r="H820" s="3" t="n"/>
       <c r="I820" s="3" t="n"/>
       <c r="J820" s="3" t="n"/>
@@ -28070,7 +28120,7 @@
       <c r="D821" s="4" t="n"/>
       <c r="E821" s="4" t="n"/>
       <c r="F821" s="3" t="n"/>
-      <c r="G821" t="inlineStr"/>
+      <c r="G821" s="0" t="inlineStr"/>
       <c r="H821" s="3" t="n"/>
       <c r="I821" s="3" t="n"/>
       <c r="J821" s="3" t="n"/>
@@ -28099,7 +28149,7 @@
       <c r="D822" s="4" t="n"/>
       <c r="E822" s="4" t="n"/>
       <c r="F822" s="3" t="n"/>
-      <c r="G822" t="inlineStr"/>
+      <c r="G822" s="0" t="inlineStr"/>
       <c r="H822" s="3" t="n"/>
       <c r="I822" s="3" t="n"/>
       <c r="J822" s="3" t="n"/>
@@ -28128,7 +28178,7 @@
       <c r="D823" s="4" t="n"/>
       <c r="E823" s="4" t="n"/>
       <c r="F823" s="3" t="n"/>
-      <c r="G823" t="inlineStr"/>
+      <c r="G823" s="0" t="inlineStr"/>
       <c r="H823" s="3" t="n"/>
       <c r="I823" s="3" t="n"/>
       <c r="J823" s="3" t="n"/>
@@ -28157,7 +28207,7 @@
       <c r="D824" s="4" t="n"/>
       <c r="E824" s="4" t="n"/>
       <c r="F824" s="3" t="n"/>
-      <c r="G824" t="inlineStr"/>
+      <c r="G824" s="0" t="inlineStr"/>
       <c r="H824" s="3" t="n"/>
       <c r="I824" s="3" t="n"/>
       <c r="J824" s="3" t="n"/>
@@ -28186,7 +28236,7 @@
       <c r="D825" s="4" t="n"/>
       <c r="E825" s="4" t="n"/>
       <c r="F825" s="3" t="n"/>
-      <c r="G825" t="inlineStr"/>
+      <c r="G825" s="0" t="inlineStr"/>
       <c r="H825" s="3" t="n"/>
       <c r="I825" s="3" t="n"/>
       <c r="J825" s="3" t="n"/>
@@ -28215,7 +28265,7 @@
       <c r="D826" s="4" t="n"/>
       <c r="E826" s="4" t="n"/>
       <c r="F826" s="3" t="n"/>
-      <c r="G826" t="inlineStr"/>
+      <c r="G826" s="0" t="inlineStr"/>
       <c r="H826" s="3" t="n"/>
       <c r="I826" s="3" t="n"/>
       <c r="J826" s="3" t="n"/>
@@ -28244,7 +28294,7 @@
       <c r="D827" s="4" t="n"/>
       <c r="E827" s="4" t="n"/>
       <c r="F827" s="3" t="n"/>
-      <c r="G827" t="inlineStr"/>
+      <c r="G827" s="0" t="inlineStr"/>
       <c r="H827" s="3" t="n"/>
       <c r="I827" s="3" t="n"/>
       <c r="J827" s="3" t="n"/>
@@ -28273,7 +28323,7 @@
       <c r="D828" s="4" t="n"/>
       <c r="E828" s="4" t="n"/>
       <c r="F828" s="3" t="n"/>
-      <c r="G828" t="inlineStr"/>
+      <c r="G828" s="0" t="inlineStr"/>
       <c r="H828" s="3" t="n"/>
       <c r="I828" s="3" t="n"/>
       <c r="J828" s="3" t="n"/>
@@ -28302,7 +28352,7 @@
       <c r="D829" s="4" t="n"/>
       <c r="E829" s="4" t="n"/>
       <c r="F829" s="3" t="n"/>
-      <c r="G829" t="inlineStr"/>
+      <c r="G829" s="0" t="inlineStr"/>
       <c r="H829" s="3" t="n"/>
       <c r="I829" s="3" t="n"/>
       <c r="J829" s="3" t="n"/>
@@ -28331,7 +28381,7 @@
       <c r="D830" s="4" t="n"/>
       <c r="E830" s="4" t="n"/>
       <c r="F830" s="3" t="n"/>
-      <c r="G830" t="inlineStr"/>
+      <c r="G830" s="0" t="inlineStr"/>
       <c r="H830" s="3" t="n"/>
       <c r="I830" s="3" t="n"/>
       <c r="J830" s="3" t="n"/>
@@ -28360,7 +28410,7 @@
       <c r="D831" s="4" t="n"/>
       <c r="E831" s="4" t="n"/>
       <c r="F831" s="3" t="n"/>
-      <c r="G831" t="inlineStr"/>
+      <c r="G831" s="0" t="inlineStr"/>
       <c r="H831" s="3" t="n"/>
       <c r="I831" s="3" t="n"/>
       <c r="J831" s="3" t="n"/>
@@ -28389,7 +28439,7 @@
       <c r="D832" s="4" t="n"/>
       <c r="E832" s="4" t="n"/>
       <c r="F832" s="3" t="n"/>
-      <c r="G832" t="inlineStr"/>
+      <c r="G832" s="0" t="inlineStr"/>
       <c r="H832" s="3" t="n"/>
       <c r="I832" s="3" t="n"/>
       <c r="J832" s="3" t="n"/>
@@ -28418,7 +28468,7 @@
       <c r="D833" s="4" t="n"/>
       <c r="E833" s="4" t="n"/>
       <c r="F833" s="3" t="n"/>
-      <c r="G833" t="inlineStr"/>
+      <c r="G833" s="0" t="inlineStr"/>
       <c r="H833" s="3" t="n"/>
       <c r="I833" s="3" t="n"/>
       <c r="J833" s="3" t="n"/>
@@ -28447,7 +28497,7 @@
       <c r="D834" s="4" t="n"/>
       <c r="E834" s="4" t="n"/>
       <c r="F834" s="3" t="n"/>
-      <c r="G834" t="inlineStr"/>
+      <c r="G834" s="0" t="inlineStr"/>
       <c r="H834" s="3" t="n"/>
       <c r="I834" s="3" t="n"/>
       <c r="J834" s="3" t="n"/>
@@ -28476,7 +28526,7 @@
       <c r="D835" s="4" t="n"/>
       <c r="E835" s="4" t="n"/>
       <c r="F835" s="3" t="n"/>
-      <c r="G835" t="inlineStr"/>
+      <c r="G835" s="0" t="inlineStr"/>
       <c r="H835" s="3" t="n"/>
       <c r="I835" s="3" t="n"/>
       <c r="J835" s="3" t="n"/>
@@ -28505,7 +28555,7 @@
       <c r="D836" s="4" t="n"/>
       <c r="E836" s="4" t="n"/>
       <c r="F836" s="3" t="n"/>
-      <c r="G836" t="inlineStr"/>
+      <c r="G836" s="0" t="inlineStr"/>
       <c r="H836" s="3" t="n"/>
       <c r="I836" s="3" t="n"/>
       <c r="J836" s="3" t="n"/>
@@ -28534,7 +28584,7 @@
       <c r="D837" s="4" t="n"/>
       <c r="E837" s="4" t="n"/>
       <c r="F837" s="3" t="n"/>
-      <c r="G837" t="inlineStr"/>
+      <c r="G837" s="0" t="inlineStr"/>
       <c r="H837" s="3" t="n"/>
       <c r="I837" s="3" t="n"/>
       <c r="J837" s="3" t="n"/>
@@ -28563,7 +28613,7 @@
       <c r="D838" s="4" t="n"/>
       <c r="E838" s="4" t="n"/>
       <c r="F838" s="3" t="n"/>
-      <c r="G838" t="inlineStr"/>
+      <c r="G838" s="0" t="inlineStr"/>
       <c r="H838" s="3" t="n"/>
       <c r="I838" s="3" t="n"/>
       <c r="J838" s="3" t="n"/>
@@ -28592,7 +28642,7 @@
       <c r="D839" s="4" t="n"/>
       <c r="E839" s="4" t="n"/>
       <c r="F839" s="3" t="n"/>
-      <c r="G839" t="inlineStr"/>
+      <c r="G839" s="0" t="inlineStr"/>
       <c r="H839" s="3" t="n"/>
       <c r="I839" s="3" t="n"/>
       <c r="J839" s="3" t="n"/>
@@ -28621,7 +28671,7 @@
       <c r="D840" s="4" t="n"/>
       <c r="E840" s="4" t="n"/>
       <c r="F840" s="3" t="n"/>
-      <c r="G840" t="inlineStr"/>
+      <c r="G840" s="0" t="inlineStr"/>
       <c r="H840" s="3" t="n"/>
       <c r="I840" s="3" t="n"/>
       <c r="J840" s="3" t="n"/>
@@ -28650,7 +28700,7 @@
       <c r="D841" s="4" t="n"/>
       <c r="E841" s="4" t="n"/>
       <c r="F841" s="3" t="n"/>
-      <c r="G841" t="inlineStr"/>
+      <c r="G841" s="0" t="inlineStr"/>
       <c r="H841" s="3" t="n"/>
       <c r="I841" s="3" t="n"/>
       <c r="J841" s="3" t="n"/>
@@ -28679,7 +28729,7 @@
       <c r="D842" s="4" t="n"/>
       <c r="E842" s="4" t="n"/>
       <c r="F842" s="3" t="n"/>
-      <c r="G842" t="inlineStr"/>
+      <c r="G842" s="0" t="inlineStr"/>
       <c r="H842" s="3" t="n"/>
       <c r="I842" s="3" t="n"/>
       <c r="J842" s="3" t="n"/>
@@ -28708,7 +28758,7 @@
       <c r="D843" s="4" t="n"/>
       <c r="E843" s="4" t="n"/>
       <c r="F843" s="3" t="n"/>
-      <c r="G843" t="inlineStr"/>
+      <c r="G843" s="0" t="inlineStr"/>
       <c r="H843" s="3" t="n"/>
       <c r="I843" s="3" t="n"/>
       <c r="J843" s="3" t="n"/>
@@ -28737,7 +28787,7 @@
       <c r="D844" s="4" t="n"/>
       <c r="E844" s="4" t="n"/>
       <c r="F844" s="3" t="n"/>
-      <c r="G844" t="inlineStr"/>
+      <c r="G844" s="0" t="inlineStr"/>
       <c r="H844" s="3" t="n"/>
       <c r="I844" s="3" t="n"/>
       <c r="J844" s="3" t="n"/>
@@ -28766,7 +28816,7 @@
       <c r="D845" s="4" t="n"/>
       <c r="E845" s="4" t="n"/>
       <c r="F845" s="3" t="n"/>
-      <c r="G845" t="inlineStr"/>
+      <c r="G845" s="0" t="inlineStr"/>
       <c r="H845" s="3" t="n"/>
       <c r="I845" s="3" t="n"/>
       <c r="J845" s="3" t="n"/>
@@ -28795,7 +28845,7 @@
       <c r="D846" s="4" t="n"/>
       <c r="E846" s="4" t="n"/>
       <c r="F846" s="3" t="n"/>
-      <c r="G846" t="inlineStr"/>
+      <c r="G846" s="0" t="inlineStr"/>
       <c r="H846" s="3" t="n"/>
       <c r="I846" s="3" t="n"/>
       <c r="J846" s="3" t="n"/>
@@ -28824,7 +28874,7 @@
       <c r="D847" s="4" t="n"/>
       <c r="E847" s="4" t="n"/>
       <c r="F847" s="3" t="n"/>
-      <c r="G847" t="inlineStr"/>
+      <c r="G847" s="0" t="inlineStr"/>
       <c r="H847" s="3" t="n"/>
       <c r="I847" s="3" t="n"/>
       <c r="J847" s="3" t="n"/>
@@ -28853,7 +28903,7 @@
       <c r="D848" s="4" t="n"/>
       <c r="E848" s="4" t="n"/>
       <c r="F848" s="3" t="n"/>
-      <c r="G848" t="inlineStr"/>
+      <c r="G848" s="0" t="inlineStr"/>
       <c r="H848" s="3" t="n"/>
       <c r="I848" s="3" t="n"/>
       <c r="J848" s="3" t="n"/>
@@ -28882,7 +28932,7 @@
       <c r="D849" s="4" t="n"/>
       <c r="E849" s="4" t="n"/>
       <c r="F849" s="3" t="n"/>
-      <c r="G849" t="inlineStr"/>
+      <c r="G849" s="0" t="inlineStr"/>
       <c r="H849" s="3" t="n"/>
       <c r="I849" s="3" t="n"/>
       <c r="J849" s="3" t="n"/>
@@ -28911,7 +28961,7 @@
       <c r="D850" s="4" t="n"/>
       <c r="E850" s="4" t="n"/>
       <c r="F850" s="3" t="n"/>
-      <c r="G850" t="inlineStr"/>
+      <c r="G850" s="0" t="inlineStr"/>
       <c r="H850" s="3" t="n"/>
       <c r="I850" s="3" t="n"/>
       <c r="J850" s="3" t="n"/>
@@ -28940,7 +28990,7 @@
       <c r="D851" s="4" t="n"/>
       <c r="E851" s="4" t="n"/>
       <c r="F851" s="3" t="n"/>
-      <c r="G851" t="inlineStr"/>
+      <c r="G851" s="0" t="inlineStr"/>
       <c r="H851" s="3" t="n"/>
       <c r="I851" s="3" t="n"/>
       <c r="J851" s="3" t="n"/>
@@ -28969,7 +29019,7 @@
       <c r="D852" s="4" t="n"/>
       <c r="E852" s="4" t="n"/>
       <c r="F852" s="3" t="n"/>
-      <c r="G852" t="inlineStr"/>
+      <c r="G852" s="0" t="inlineStr"/>
       <c r="H852" s="3" t="n"/>
       <c r="I852" s="3" t="n"/>
       <c r="J852" s="3" t="n"/>
@@ -28998,7 +29048,7 @@
       <c r="D853" s="4" t="n"/>
       <c r="E853" s="4" t="n"/>
       <c r="F853" s="3" t="n"/>
-      <c r="G853" t="inlineStr"/>
+      <c r="G853" s="0" t="inlineStr"/>
       <c r="H853" s="3" t="n"/>
       <c r="I853" s="3" t="n"/>
       <c r="J853" s="3" t="n"/>
@@ -29027,7 +29077,7 @@
       <c r="D854" s="4" t="n"/>
       <c r="E854" s="4" t="n"/>
       <c r="F854" s="3" t="n"/>
-      <c r="G854" t="inlineStr"/>
+      <c r="G854" s="0" t="inlineStr"/>
       <c r="H854" s="3" t="n"/>
       <c r="I854" s="3" t="n"/>
       <c r="J854" s="3" t="n"/>
@@ -29056,7 +29106,7 @@
       <c r="D855" s="4" t="n"/>
       <c r="E855" s="4" t="n"/>
       <c r="F855" s="3" t="n"/>
-      <c r="G855" t="inlineStr"/>
+      <c r="G855" s="0" t="inlineStr"/>
       <c r="H855" s="3" t="n"/>
       <c r="I855" s="3" t="n"/>
       <c r="J855" s="3" t="n"/>
@@ -29085,7 +29135,7 @@
       <c r="D856" s="4" t="n"/>
       <c r="E856" s="4" t="n"/>
       <c r="F856" s="3" t="n"/>
-      <c r="G856" t="inlineStr"/>
+      <c r="G856" s="0" t="inlineStr"/>
       <c r="H856" s="3" t="n"/>
       <c r="I856" s="3" t="n"/>
       <c r="J856" s="3" t="n"/>
@@ -29114,7 +29164,7 @@
       <c r="D857" s="4" t="n"/>
       <c r="E857" s="4" t="n"/>
       <c r="F857" s="3" t="n"/>
-      <c r="G857" t="inlineStr"/>
+      <c r="G857" s="0" t="inlineStr"/>
       <c r="H857" s="3" t="n"/>
       <c r="I857" s="3" t="n"/>
       <c r="J857" s="3" t="n"/>
@@ -29143,7 +29193,7 @@
       <c r="D858" s="4" t="n"/>
       <c r="E858" s="4" t="n"/>
       <c r="F858" s="3" t="n"/>
-      <c r="G858" t="inlineStr"/>
+      <c r="G858" s="0" t="inlineStr"/>
       <c r="H858" s="3" t="n"/>
       <c r="I858" s="3" t="n"/>
       <c r="J858" s="3" t="n"/>
@@ -29172,7 +29222,7 @@
       <c r="D859" s="4" t="n"/>
       <c r="E859" s="4" t="n"/>
       <c r="F859" s="3" t="n"/>
-      <c r="G859" t="inlineStr"/>
+      <c r="G859" s="0" t="inlineStr"/>
       <c r="H859" s="3" t="n"/>
       <c r="I859" s="3" t="n"/>
       <c r="J859" s="3" t="n"/>
@@ -29201,7 +29251,7 @@
       <c r="D860" s="4" t="n"/>
       <c r="E860" s="4" t="n"/>
       <c r="F860" s="3" t="n"/>
-      <c r="G860" t="inlineStr"/>
+      <c r="G860" s="0" t="inlineStr"/>
       <c r="H860" s="3" t="n"/>
       <c r="I860" s="3" t="n"/>
       <c r="J860" s="3" t="n"/>
@@ -29230,7 +29280,7 @@
       <c r="D861" s="4" t="n"/>
       <c r="E861" s="4" t="n"/>
       <c r="F861" s="3" t="n"/>
-      <c r="G861" t="inlineStr"/>
+      <c r="G861" s="0" t="inlineStr"/>
       <c r="H861" s="3" t="n"/>
       <c r="I861" s="3" t="n"/>
       <c r="J861" s="3" t="n"/>
@@ -29259,7 +29309,7 @@
       <c r="D862" s="4" t="n"/>
       <c r="E862" s="4" t="n"/>
       <c r="F862" s="3" t="n"/>
-      <c r="G862" t="inlineStr"/>
+      <c r="G862" s="0" t="inlineStr"/>
       <c r="H862" s="3" t="n"/>
       <c r="I862" s="3" t="n"/>
       <c r="J862" s="3" t="n"/>
@@ -29288,7 +29338,7 @@
       <c r="D863" s="4" t="n"/>
       <c r="E863" s="4" t="n"/>
       <c r="F863" s="3" t="n"/>
-      <c r="G863" t="inlineStr"/>
+      <c r="G863" s="0" t="inlineStr"/>
       <c r="H863" s="3" t="n"/>
       <c r="I863" s="3" t="n"/>
       <c r="J863" s="3" t="n"/>
@@ -29317,7 +29367,7 @@
       <c r="D864" s="4" t="n"/>
       <c r="E864" s="4" t="n"/>
       <c r="F864" s="3" t="n"/>
-      <c r="G864" t="inlineStr"/>
+      <c r="G864" s="0" t="inlineStr"/>
       <c r="H864" s="3" t="n"/>
       <c r="I864" s="3" t="n"/>
       <c r="J864" s="3" t="n"/>
@@ -29346,7 +29396,7 @@
       <c r="D865" s="4" t="n"/>
       <c r="E865" s="4" t="n"/>
       <c r="F865" s="3" t="n"/>
-      <c r="G865" t="inlineStr"/>
+      <c r="G865" s="0" t="inlineStr"/>
       <c r="H865" s="3" t="n"/>
       <c r="I865" s="3" t="n"/>
       <c r="J865" s="3" t="n"/>
@@ -29375,7 +29425,7 @@
       <c r="D866" s="4" t="n"/>
       <c r="E866" s="4" t="n"/>
       <c r="F866" s="3" t="n"/>
-      <c r="G866" t="inlineStr"/>
+      <c r="G866" s="0" t="inlineStr"/>
       <c r="H866" s="3" t="n"/>
       <c r="I866" s="3" t="n"/>
       <c r="J866" s="3" t="n"/>
@@ -29404,7 +29454,7 @@
       <c r="D867" s="4" t="n"/>
       <c r="E867" s="4" t="n"/>
       <c r="F867" s="3" t="n"/>
-      <c r="G867" t="inlineStr"/>
+      <c r="G867" s="0" t="inlineStr"/>
       <c r="H867" s="3" t="n"/>
       <c r="I867" s="3" t="n"/>
       <c r="J867" s="3" t="n"/>
@@ -29433,7 +29483,7 @@
       <c r="D868" s="4" t="n"/>
       <c r="E868" s="4" t="n"/>
       <c r="F868" s="3" t="n"/>
-      <c r="G868" t="inlineStr"/>
+      <c r="G868" s="0" t="inlineStr"/>
       <c r="H868" s="3" t="n"/>
       <c r="I868" s="3" t="n"/>
       <c r="J868" s="3" t="n"/>
@@ -29462,7 +29512,7 @@
       <c r="D869" s="4" t="n"/>
       <c r="E869" s="4" t="n"/>
       <c r="F869" s="3" t="n"/>
-      <c r="G869" t="inlineStr"/>
+      <c r="G869" s="0" t="inlineStr"/>
       <c r="H869" s="3" t="n"/>
       <c r="I869" s="3" t="n"/>
       <c r="J869" s="3" t="n"/>
@@ -29491,7 +29541,7 @@
       <c r="D870" s="4" t="n"/>
       <c r="E870" s="4" t="n"/>
       <c r="F870" s="3" t="n"/>
-      <c r="G870" t="inlineStr"/>
+      <c r="G870" s="0" t="inlineStr"/>
       <c r="H870" s="3" t="n"/>
       <c r="I870" s="3" t="n"/>
       <c r="J870" s="3" t="n"/>
@@ -29520,7 +29570,7 @@
       <c r="D871" s="4" t="n"/>
       <c r="E871" s="4" t="n"/>
       <c r="F871" s="3" t="n"/>
-      <c r="G871" t="inlineStr"/>
+      <c r="G871" s="0" t="inlineStr"/>
       <c r="H871" s="3" t="n"/>
       <c r="I871" s="3" t="n"/>
       <c r="J871" s="3" t="n"/>
@@ -29549,7 +29599,7 @@
       <c r="D872" s="4" t="n"/>
       <c r="E872" s="4" t="n"/>
       <c r="F872" s="3" t="n"/>
-      <c r="G872" t="inlineStr"/>
+      <c r="G872" s="0" t="inlineStr"/>
       <c r="H872" s="3" t="n"/>
       <c r="I872" s="3" t="n"/>
       <c r="J872" s="3" t="n"/>
@@ -29578,7 +29628,7 @@
       <c r="D873" s="4" t="n"/>
       <c r="E873" s="4" t="n"/>
       <c r="F873" s="3" t="n"/>
-      <c r="G873" t="inlineStr"/>
+      <c r="G873" s="0" t="inlineStr"/>
       <c r="H873" s="3" t="n"/>
       <c r="I873" s="3" t="n"/>
       <c r="J873" s="3" t="n"/>
@@ -29607,7 +29657,7 @@
       <c r="D874" s="4" t="n"/>
       <c r="E874" s="4" t="n"/>
       <c r="F874" s="3" t="n"/>
-      <c r="G874" t="inlineStr"/>
+      <c r="G874" s="0" t="inlineStr"/>
       <c r="H874" s="3" t="n"/>
       <c r="I874" s="3" t="n"/>
       <c r="J874" s="3" t="n"/>
@@ -29636,7 +29686,7 @@
       <c r="D875" s="4" t="n"/>
       <c r="E875" s="4" t="n"/>
       <c r="F875" s="3" t="n"/>
-      <c r="G875" t="inlineStr"/>
+      <c r="G875" s="0" t="inlineStr"/>
       <c r="H875" s="3" t="n"/>
       <c r="I875" s="3" t="n"/>
       <c r="J875" s="3" t="n"/>
@@ -29665,7 +29715,7 @@
       <c r="D876" s="4" t="n"/>
       <c r="E876" s="4" t="n"/>
       <c r="F876" s="3" t="n"/>
-      <c r="G876" t="inlineStr"/>
+      <c r="G876" s="0" t="inlineStr"/>
       <c r="H876" s="3" t="n"/>
       <c r="I876" s="3" t="n"/>
       <c r="J876" s="3" t="n"/>
@@ -29694,7 +29744,7 @@
       <c r="D877" s="4" t="n"/>
       <c r="E877" s="4" t="n"/>
       <c r="F877" s="3" t="n"/>
-      <c r="G877" t="inlineStr"/>
+      <c r="G877" s="0" t="inlineStr"/>
       <c r="H877" s="3" t="n"/>
       <c r="I877" s="3" t="n"/>
       <c r="J877" s="3" t="n"/>
@@ -29723,7 +29773,7 @@
       <c r="D878" s="4" t="n"/>
       <c r="E878" s="4" t="n"/>
       <c r="F878" s="3" t="n"/>
-      <c r="G878" t="inlineStr"/>
+      <c r="G878" s="0" t="inlineStr"/>
       <c r="H878" s="3" t="n"/>
       <c r="I878" s="3" t="n"/>
       <c r="J878" s="3" t="n"/>
@@ -29752,7 +29802,7 @@
       <c r="D879" s="4" t="n"/>
       <c r="E879" s="4" t="n"/>
       <c r="F879" s="3" t="n"/>
-      <c r="G879" t="inlineStr"/>
+      <c r="G879" s="0" t="inlineStr"/>
       <c r="H879" s="3" t="n"/>
       <c r="I879" s="3" t="n"/>
       <c r="J879" s="3" t="n"/>
@@ -29781,7 +29831,7 @@
       <c r="D880" s="4" t="n"/>
       <c r="E880" s="4" t="n"/>
       <c r="F880" s="3" t="n"/>
-      <c r="G880" t="inlineStr"/>
+      <c r="G880" s="0" t="inlineStr"/>
       <c r="H880" s="3" t="n"/>
       <c r="I880" s="3" t="n"/>
       <c r="J880" s="3" t="n"/>
@@ -29810,7 +29860,7 @@
       <c r="D881" s="4" t="n"/>
       <c r="E881" s="4" t="n"/>
       <c r="F881" s="3" t="n"/>
-      <c r="G881" t="inlineStr"/>
+      <c r="G881" s="0" t="inlineStr"/>
       <c r="H881" s="3" t="n"/>
       <c r="I881" s="3" t="n"/>
       <c r="J881" s="3" t="n"/>
@@ -29839,7 +29889,7 @@
       <c r="D882" s="4" t="n"/>
       <c r="E882" s="4" t="n"/>
       <c r="F882" s="3" t="n"/>
-      <c r="G882" t="inlineStr"/>
+      <c r="G882" s="0" t="inlineStr"/>
       <c r="H882" s="3" t="n"/>
       <c r="I882" s="3" t="n"/>
       <c r="J882" s="3" t="n"/>
@@ -29868,7 +29918,7 @@
       <c r="D883" s="4" t="n"/>
       <c r="E883" s="4" t="n"/>
       <c r="F883" s="3" t="n"/>
-      <c r="G883" t="inlineStr"/>
+      <c r="G883" s="0" t="inlineStr"/>
       <c r="H883" s="3" t="n"/>
       <c r="I883" s="3" t="n"/>
       <c r="J883" s="3" t="n"/>
@@ -29897,7 +29947,7 @@
       <c r="D884" s="4" t="n"/>
       <c r="E884" s="4" t="n"/>
       <c r="F884" s="3" t="n"/>
-      <c r="G884" t="inlineStr"/>
+      <c r="G884" s="0" t="inlineStr"/>
       <c r="H884" s="3" t="n"/>
       <c r="I884" s="3" t="n"/>
       <c r="J884" s="3" t="n"/>
@@ -29926,7 +29976,7 @@
       <c r="D885" s="4" t="n"/>
       <c r="E885" s="4" t="n"/>
       <c r="F885" s="3" t="n"/>
-      <c r="G885" t="inlineStr"/>
+      <c r="G885" s="0" t="inlineStr"/>
       <c r="H885" s="3" t="n"/>
       <c r="I885" s="3" t="n"/>
       <c r="J885" s="3" t="n"/>
@@ -29955,7 +30005,7 @@
       <c r="D886" s="4" t="n"/>
       <c r="E886" s="4" t="n"/>
       <c r="F886" s="3" t="n"/>
-      <c r="G886" t="inlineStr"/>
+      <c r="G886" s="0" t="inlineStr"/>
       <c r="H886" s="3" t="n"/>
       <c r="I886" s="3" t="n"/>
       <c r="J886" s="3" t="n"/>
@@ -29984,7 +30034,7 @@
       <c r="D887" s="4" t="n"/>
       <c r="E887" s="4" t="n"/>
       <c r="F887" s="3" t="n"/>
-      <c r="G887" t="inlineStr"/>
+      <c r="G887" s="0" t="inlineStr"/>
       <c r="H887" s="3" t="n"/>
       <c r="I887" s="3" t="n"/>
       <c r="J887" s="3" t="n"/>
@@ -30013,7 +30063,7 @@
       <c r="D888" s="4" t="n"/>
       <c r="E888" s="4" t="n"/>
       <c r="F888" s="3" t="n"/>
-      <c r="G888" t="inlineStr"/>
+      <c r="G888" s="0" t="inlineStr"/>
       <c r="H888" s="3" t="n"/>
       <c r="I888" s="3" t="n"/>
       <c r="J888" s="3" t="n"/>
@@ -30042,7 +30092,7 @@
       <c r="D889" s="4" t="n"/>
       <c r="E889" s="4" t="n"/>
       <c r="F889" s="3" t="n"/>
-      <c r="G889" t="inlineStr"/>
+      <c r="G889" s="0" t="inlineStr"/>
       <c r="H889" s="3" t="n"/>
       <c r="I889" s="3" t="n"/>
       <c r="J889" s="3" t="n"/>
@@ -30071,7 +30121,7 @@
       <c r="D890" s="4" t="n"/>
       <c r="E890" s="4" t="n"/>
       <c r="F890" s="3" t="n"/>
-      <c r="G890" t="inlineStr"/>
+      <c r="G890" s="0" t="inlineStr"/>
       <c r="H890" s="3" t="n"/>
       <c r="I890" s="3" t="n"/>
       <c r="J890" s="3" t="n"/>
@@ -30100,7 +30150,7 @@
       <c r="D891" s="4" t="n"/>
       <c r="E891" s="4" t="n"/>
       <c r="F891" s="3" t="n"/>
-      <c r="G891" t="inlineStr"/>
+      <c r="G891" s="0" t="inlineStr"/>
       <c r="H891" s="3" t="n"/>
       <c r="I891" s="3" t="n"/>
       <c r="J891" s="3" t="n"/>
@@ -30129,7 +30179,7 @@
       <c r="D892" s="4" t="n"/>
       <c r="E892" s="4" t="n"/>
       <c r="F892" s="3" t="n"/>
-      <c r="G892" t="inlineStr"/>
+      <c r="G892" s="0" t="inlineStr"/>
       <c r="H892" s="3" t="n"/>
       <c r="I892" s="3" t="n"/>
       <c r="J892" s="3" t="n"/>
@@ -30158,7 +30208,7 @@
       <c r="D893" s="4" t="n"/>
       <c r="E893" s="4" t="n"/>
       <c r="F893" s="3" t="n"/>
-      <c r="G893" t="inlineStr"/>
+      <c r="G893" s="0" t="inlineStr"/>
       <c r="H893" s="3" t="n"/>
       <c r="I893" s="3" t="n"/>
       <c r="J893" s="3" t="n"/>
@@ -30187,7 +30237,7 @@
       <c r="D894" s="4" t="n"/>
       <c r="E894" s="4" t="n"/>
       <c r="F894" s="3" t="n"/>
-      <c r="G894" t="inlineStr"/>
+      <c r="G894" s="0" t="inlineStr"/>
       <c r="H894" s="3" t="n"/>
       <c r="I894" s="3" t="n"/>
       <c r="J894" s="3" t="n"/>
@@ -30216,7 +30266,7 @@
       <c r="D895" s="4" t="n"/>
       <c r="E895" s="4" t="n"/>
       <c r="F895" s="3" t="n"/>
-      <c r="G895" t="inlineStr"/>
+      <c r="G895" s="0" t="inlineStr"/>
       <c r="H895" s="3" t="n"/>
       <c r="I895" s="3" t="n"/>
       <c r="J895" s="3" t="n"/>
@@ -30245,7 +30295,7 @@
       <c r="D896" s="4" t="n"/>
       <c r="E896" s="4" t="n"/>
       <c r="F896" s="3" t="n"/>
-      <c r="G896" t="inlineStr"/>
+      <c r="G896" s="0" t="inlineStr"/>
       <c r="H896" s="3" t="n"/>
       <c r="I896" s="3" t="n"/>
       <c r="J896" s="3" t="n"/>
@@ -30274,7 +30324,7 @@
       <c r="D897" s="4" t="n"/>
       <c r="E897" s="4" t="n"/>
       <c r="F897" s="3" t="n"/>
-      <c r="G897" t="inlineStr"/>
+      <c r="G897" s="0" t="inlineStr"/>
       <c r="H897" s="3" t="n"/>
       <c r="I897" s="3" t="n"/>
       <c r="J897" s="3" t="n"/>
@@ -30303,7 +30353,7 @@
       <c r="D898" s="4" t="n"/>
       <c r="E898" s="4" t="n"/>
       <c r="F898" s="3" t="n"/>
-      <c r="G898" t="inlineStr"/>
+      <c r="G898" s="0" t="inlineStr"/>
       <c r="H898" s="3" t="n"/>
       <c r="I898" s="3" t="n"/>
       <c r="J898" s="3" t="n"/>
@@ -30332,7 +30382,7 @@
       <c r="D899" s="4" t="n"/>
       <c r="E899" s="4" t="n"/>
       <c r="F899" s="3" t="n"/>
-      <c r="G899" t="inlineStr"/>
+      <c r="G899" s="0" t="inlineStr"/>
       <c r="H899" s="3" t="n"/>
       <c r="I899" s="3" t="n"/>
       <c r="J899" s="3" t="n"/>
@@ -30361,7 +30411,7 @@
       <c r="D900" s="4" t="n"/>
       <c r="E900" s="4" t="n"/>
       <c r="F900" s="3" t="n"/>
-      <c r="G900" t="inlineStr"/>
+      <c r="G900" s="0" t="inlineStr"/>
       <c r="H900" s="3" t="n"/>
       <c r="I900" s="3" t="n"/>
       <c r="J900" s="3" t="n"/>
@@ -30390,7 +30440,7 @@
       <c r="D901" s="4" t="n"/>
       <c r="E901" s="4" t="n"/>
       <c r="F901" s="3" t="n"/>
-      <c r="G901" t="inlineStr"/>
+      <c r="G901" s="0" t="inlineStr"/>
       <c r="H901" s="3" t="n"/>
       <c r="I901" s="3" t="n"/>
       <c r="J901" s="3" t="n"/>
@@ -30419,7 +30469,7 @@
       <c r="D902" s="4" t="n"/>
       <c r="E902" s="4" t="n"/>
       <c r="F902" s="3" t="n"/>
-      <c r="G902" t="inlineStr"/>
+      <c r="G902" s="0" t="inlineStr"/>
       <c r="H902" s="3" t="n"/>
       <c r="I902" s="3" t="n"/>
       <c r="J902" s="3" t="n"/>
@@ -30448,7 +30498,7 @@
       <c r="D903" s="4" t="n"/>
       <c r="E903" s="4" t="n"/>
       <c r="F903" s="3" t="n"/>
-      <c r="G903" t="inlineStr"/>
+      <c r="G903" s="0" t="inlineStr"/>
       <c r="H903" s="3" t="n"/>
       <c r="I903" s="3" t="n"/>
       <c r="J903" s="3" t="n"/>
@@ -30477,7 +30527,7 @@
       <c r="D904" s="4" t="n"/>
       <c r="E904" s="4" t="n"/>
       <c r="F904" s="3" t="n"/>
-      <c r="G904" t="inlineStr"/>
+      <c r="G904" s="0" t="inlineStr"/>
       <c r="H904" s="3" t="n"/>
       <c r="I904" s="3" t="n"/>
       <c r="J904" s="3" t="n"/>
@@ -30506,7 +30556,7 @@
       <c r="D905" s="4" t="n"/>
       <c r="E905" s="4" t="n"/>
       <c r="F905" s="3" t="n"/>
-      <c r="G905" t="inlineStr"/>
+      <c r="G905" s="0" t="inlineStr"/>
       <c r="H905" s="3" t="n"/>
       <c r="I905" s="3" t="n"/>
       <c r="J905" s="3" t="n"/>
@@ -30535,7 +30585,7 @@
       <c r="D906" s="4" t="n"/>
       <c r="E906" s="4" t="n"/>
       <c r="F906" s="3" t="n"/>
-      <c r="G906" t="inlineStr"/>
+      <c r="G906" s="0" t="inlineStr"/>
       <c r="H906" s="3" t="n"/>
       <c r="I906" s="3" t="n"/>
       <c r="J906" s="3" t="n"/>
@@ -30564,7 +30614,7 @@
       <c r="D907" s="4" t="n"/>
       <c r="E907" s="4" t="n"/>
       <c r="F907" s="3" t="n"/>
-      <c r="G907" t="inlineStr"/>
+      <c r="G907" s="0" t="inlineStr"/>
       <c r="H907" s="3" t="n"/>
       <c r="I907" s="3" t="n"/>
       <c r="J907" s="3" t="n"/>
@@ -30593,7 +30643,7 @@
       <c r="D908" s="4" t="n"/>
       <c r="E908" s="4" t="n"/>
       <c r="F908" s="3" t="n"/>
-      <c r="G908" t="inlineStr"/>
+      <c r="G908" s="0" t="inlineStr"/>
       <c r="H908" s="3" t="n"/>
       <c r="I908" s="3" t="n"/>
       <c r="J908" s="3" t="n"/>
@@ -30622,7 +30672,7 @@
       <c r="D909" s="4" t="n"/>
       <c r="E909" s="4" t="n"/>
       <c r="F909" s="3" t="n"/>
-      <c r="G909" t="inlineStr"/>
+      <c r="G909" s="0" t="inlineStr"/>
       <c r="H909" s="3" t="n"/>
       <c r="I909" s="3" t="n"/>
       <c r="J909" s="3" t="n"/>
@@ -30651,7 +30701,7 @@
       <c r="D910" s="4" t="n"/>
       <c r="E910" s="4" t="n"/>
       <c r="F910" s="3" t="n"/>
-      <c r="G910" t="inlineStr"/>
+      <c r="G910" s="0" t="inlineStr"/>
       <c r="H910" s="3" t="n"/>
       <c r="I910" s="3" t="n"/>
       <c r="J910" s="3" t="n"/>
@@ -30680,7 +30730,7 @@
       <c r="D911" s="4" t="n"/>
       <c r="E911" s="4" t="n"/>
       <c r="F911" s="3" t="n"/>
-      <c r="G911" t="inlineStr"/>
+      <c r="G911" s="0" t="inlineStr"/>
       <c r="H911" s="3" t="n"/>
       <c r="I911" s="3" t="n"/>
       <c r="J911" s="3" t="n"/>
@@ -30709,7 +30759,7 @@
       <c r="D912" s="4" t="n"/>
       <c r="E912" s="4" t="n"/>
       <c r="F912" s="3" t="n"/>
-      <c r="G912" t="inlineStr"/>
+      <c r="G912" s="0" t="inlineStr"/>
       <c r="H912" s="3" t="n"/>
       <c r="I912" s="3" t="n"/>
       <c r="J912" s="3" t="n"/>
@@ -30738,7 +30788,7 @@
       <c r="D913" s="4" t="n"/>
       <c r="E913" s="4" t="n"/>
       <c r="F913" s="3" t="n"/>
-      <c r="G913" t="inlineStr"/>
+      <c r="G913" s="0" t="inlineStr"/>
       <c r="H913" s="3" t="n"/>
       <c r="I913" s="3" t="n"/>
       <c r="J913" s="3" t="n"/>
@@ -30767,7 +30817,7 @@
       <c r="D914" s="4" t="n"/>
       <c r="E914" s="4" t="n"/>
       <c r="F914" s="3" t="n"/>
-      <c r="G914" t="inlineStr"/>
+      <c r="G914" s="0" t="inlineStr"/>
       <c r="H914" s="3" t="n"/>
       <c r="I914" s="3" t="n"/>
       <c r="J914" s="3" t="n"/>
@@ -30796,7 +30846,7 @@
       <c r="D915" s="4" t="n"/>
       <c r="E915" s="4" t="n"/>
       <c r="F915" s="3" t="n"/>
-      <c r="G915" t="inlineStr"/>
+      <c r="G915" s="0" t="inlineStr"/>
       <c r="H915" s="3" t="n"/>
       <c r="I915" s="3" t="n"/>
       <c r="J915" s="3" t="n"/>
@@ -30825,7 +30875,7 @@
       <c r="D916" s="4" t="n"/>
       <c r="E916" s="4" t="n"/>
       <c r="F916" s="3" t="n"/>
-      <c r="G916" t="inlineStr"/>
+      <c r="G916" s="0" t="inlineStr"/>
       <c r="H916" s="3" t="n"/>
       <c r="I916" s="3" t="n"/>
       <c r="J916" s="3" t="n"/>
@@ -30854,7 +30904,7 @@
       <c r="D917" s="4" t="n"/>
       <c r="E917" s="4" t="n"/>
       <c r="F917" s="3" t="n"/>
-      <c r="G917" t="inlineStr"/>
+      <c r="G917" s="0" t="inlineStr"/>
       <c r="H917" s="3" t="n"/>
       <c r="I917" s="3" t="n"/>
       <c r="J917" s="3" t="n"/>
@@ -30883,7 +30933,7 @@
       <c r="D918" s="4" t="n"/>
       <c r="E918" s="4" t="n"/>
       <c r="F918" s="3" t="n"/>
-      <c r="G918" t="inlineStr"/>
+      <c r="G918" s="0" t="inlineStr"/>
       <c r="H918" s="3" t="n"/>
       <c r="I918" s="3" t="n"/>
       <c r="J918" s="3" t="n"/>
@@ -30912,7 +30962,7 @@
       <c r="D919" s="4" t="n"/>
       <c r="E919" s="4" t="n"/>
       <c r="F919" s="3" t="n"/>
-      <c r="G919" t="inlineStr"/>
+      <c r="G919" s="0" t="inlineStr"/>
       <c r="H919" s="3" t="n"/>
       <c r="I919" s="3" t="n"/>
       <c r="J919" s="3" t="n"/>
@@ -30941,7 +30991,7 @@
       <c r="D920" s="4" t="n"/>
       <c r="E920" s="4" t="n"/>
       <c r="F920" s="3" t="n"/>
-      <c r="G920" t="inlineStr"/>
+      <c r="G920" s="0" t="inlineStr"/>
       <c r="H920" s="3" t="n"/>
       <c r="I920" s="3" t="n"/>
       <c r="J920" s="3" t="n"/>
@@ -30970,7 +31020,7 @@
       <c r="D921" s="4" t="n"/>
       <c r="E921" s="4" t="n"/>
       <c r="F921" s="3" t="n"/>
-      <c r="G921" t="inlineStr"/>
+      <c r="G921" s="0" t="inlineStr"/>
       <c r="H921" s="3" t="n"/>
       <c r="I921" s="3" t="n"/>
       <c r="J921" s="3" t="n"/>
@@ -30999,7 +31049,7 @@
       <c r="D922" s="4" t="n"/>
       <c r="E922" s="4" t="n"/>
       <c r="F922" s="3" t="n"/>
-      <c r="G922" t="inlineStr"/>
+      <c r="G922" s="0" t="inlineStr"/>
       <c r="H922" s="3" t="n"/>
       <c r="I922" s="3" t="n"/>
       <c r="J922" s="3" t="n"/>
@@ -31028,7 +31078,7 @@
       <c r="D923" s="4" t="n"/>
       <c r="E923" s="4" t="n"/>
       <c r="F923" s="3" t="n"/>
-      <c r="G923" t="inlineStr"/>
+      <c r="G923" s="0" t="inlineStr"/>
       <c r="H923" s="3" t="n"/>
       <c r="I923" s="3" t="n"/>
       <c r="J923" s="3" t="n"/>
@@ -31057,7 +31107,7 @@
       <c r="D924" s="4" t="n"/>
       <c r="E924" s="4" t="n"/>
       <c r="F924" s="3" t="n"/>
-      <c r="G924" t="inlineStr"/>
+      <c r="G924" s="0" t="inlineStr"/>
       <c r="H924" s="3" t="n"/>
       <c r="I924" s="3" t="n"/>
       <c r="J924" s="3" t="n"/>
@@ -31086,7 +31136,7 @@
       <c r="D925" s="4" t="n"/>
       <c r="E925" s="4" t="n"/>
       <c r="F925" s="3" t="n"/>
-      <c r="G925" t="inlineStr"/>
+      <c r="G925" s="0" t="inlineStr"/>
       <c r="H925" s="3" t="n"/>
       <c r="I925" s="3" t="n"/>
       <c r="J925" s="3" t="n"/>
@@ -31115,7 +31165,7 @@
       <c r="D926" s="4" t="n"/>
       <c r="E926" s="4" t="n"/>
       <c r="F926" s="3" t="n"/>
-      <c r="G926" t="inlineStr"/>
+      <c r="G926" s="0" t="inlineStr"/>
       <c r="H926" s="3" t="n"/>
       <c r="I926" s="3" t="n"/>
       <c r="J926" s="3" t="n"/>
@@ -31144,7 +31194,7 @@
       <c r="D927" s="4" t="n"/>
       <c r="E927" s="4" t="n"/>
       <c r="F927" s="3" t="n"/>
-      <c r="G927" t="inlineStr"/>
+      <c r="G927" s="0" t="inlineStr"/>
       <c r="H927" s="3" t="n"/>
       <c r="I927" s="3" t="n"/>
       <c r="J927" s="3" t="n"/>
@@ -31173,7 +31223,7 @@
       <c r="D928" s="4" t="n"/>
       <c r="E928" s="4" t="n"/>
       <c r="F928" s="3" t="n"/>
-      <c r="G928" t="inlineStr"/>
+      <c r="G928" s="0" t="inlineStr"/>
       <c r="H928" s="3" t="n"/>
       <c r="I928" s="3" t="n"/>
       <c r="J928" s="3" t="n"/>
@@ -31202,7 +31252,7 @@
       <c r="D929" s="4" t="n"/>
       <c r="E929" s="4" t="n"/>
       <c r="F929" s="3" t="n"/>
-      <c r="G929" t="inlineStr"/>
+      <c r="G929" s="0" t="inlineStr"/>
       <c r="H929" s="3" t="n"/>
       <c r="I929" s="3" t="n"/>
       <c r="J929" s="3" t="n"/>
@@ -31231,7 +31281,7 @@
       <c r="D930" s="4" t="n"/>
       <c r="E930" s="4" t="n"/>
       <c r="F930" s="3" t="n"/>
-      <c r="G930" t="inlineStr"/>
+      <c r="G930" s="0" t="inlineStr"/>
       <c r="H930" s="3" t="n"/>
       <c r="I930" s="3" t="n"/>
       <c r="J930" s="3" t="n"/>
@@ -31260,7 +31310,7 @@
       <c r="D931" s="4" t="n"/>
       <c r="E931" s="4" t="n"/>
       <c r="F931" s="3" t="n"/>
-      <c r="G931" t="inlineStr"/>
+      <c r="G931" s="0" t="inlineStr"/>
       <c r="H931" s="3" t="n"/>
       <c r="I931" s="3" t="n"/>
       <c r="J931" s="3" t="n"/>
@@ -31289,7 +31339,7 @@
       <c r="D932" s="4" t="n"/>
       <c r="E932" s="4" t="n"/>
       <c r="F932" s="3" t="n"/>
-      <c r="G932" t="inlineStr"/>
+      <c r="G932" s="0" t="inlineStr"/>
       <c r="H932" s="3" t="n"/>
       <c r="I932" s="3" t="n"/>
       <c r="J932" s="3" t="n"/>
@@ -31318,7 +31368,7 @@
       <c r="D933" s="4" t="n"/>
       <c r="E933" s="4" t="n"/>
       <c r="F933" s="3" t="n"/>
-      <c r="G933" t="inlineStr"/>
+      <c r="G933" s="0" t="inlineStr"/>
       <c r="H933" s="3" t="n"/>
       <c r="I933" s="3" t="n"/>
       <c r="J933" s="3" t="n"/>
@@ -31347,7 +31397,7 @@
       <c r="D934" s="4" t="n"/>
       <c r="E934" s="4" t="n"/>
       <c r="F934" s="3" t="n"/>
-      <c r="G934" t="inlineStr"/>
+      <c r="G934" s="0" t="inlineStr"/>
       <c r="H934" s="3" t="n"/>
       <c r="I934" s="3" t="n"/>
       <c r="J934" s="3" t="n"/>
@@ -31376,7 +31426,7 @@
       <c r="D935" s="4" t="n"/>
       <c r="E935" s="4" t="n"/>
       <c r="F935" s="3" t="n"/>
-      <c r="G935" t="inlineStr"/>
+      <c r="G935" s="0" t="inlineStr"/>
       <c r="H935" s="3" t="n"/>
       <c r="I935" s="3" t="n"/>
       <c r="J935" s="3" t="n"/>
@@ -31405,7 +31455,7 @@
       <c r="D936" s="4" t="n"/>
       <c r="E936" s="4" t="n"/>
       <c r="F936" s="3" t="n"/>
-      <c r="G936" t="inlineStr"/>
+      <c r="G936" s="0" t="inlineStr"/>
       <c r="H936" s="3" t="n"/>
       <c r="I936" s="3" t="n"/>
       <c r="J936" s="3" t="n"/>
@@ -31434,7 +31484,7 @@
       <c r="D937" s="4" t="n"/>
       <c r="E937" s="4" t="n"/>
       <c r="F937" s="3" t="n"/>
-      <c r="G937" t="inlineStr"/>
+      <c r="G937" s="0" t="inlineStr"/>
       <c r="H937" s="3" t="n"/>
       <c r="I937" s="3" t="n"/>
       <c r="J937" s="3" t="n"/>
@@ -31463,7 +31513,7 @@
       <c r="D938" s="4" t="n"/>
       <c r="E938" s="4" t="n"/>
       <c r="F938" s="3" t="n"/>
-      <c r="G938" t="inlineStr"/>
+      <c r="G938" s="0" t="inlineStr"/>
       <c r="H938" s="3" t="n"/>
       <c r="I938" s="3" t="n"/>
       <c r="J938" s="3" t="n"/>
@@ -31492,7 +31542,7 @@
       <c r="D939" s="4" t="n"/>
       <c r="E939" s="4" t="n"/>
       <c r="F939" s="3" t="n"/>
-      <c r="G939" t="inlineStr"/>
+      <c r="G939" s="0" t="inlineStr"/>
       <c r="H939" s="3" t="n"/>
       <c r="I939" s="3" t="n"/>
       <c r="J939" s="3" t="n"/>
@@ -31521,7 +31571,7 @@
       <c r="D940" s="4" t="n"/>
       <c r="E940" s="4" t="n"/>
       <c r="F940" s="3" t="n"/>
-      <c r="G940" t="inlineStr"/>
+      <c r="G940" s="0" t="inlineStr"/>
       <c r="H940" s="3" t="n"/>
       <c r="I940" s="3" t="n"/>
       <c r="J940" s="3" t="n"/>
@@ -31550,7 +31600,7 @@
       <c r="D941" s="4" t="n"/>
       <c r="E941" s="4" t="n"/>
       <c r="F941" s="3" t="n"/>
-      <c r="G941" t="inlineStr"/>
+      <c r="G941" s="0" t="inlineStr"/>
       <c r="H941" s="3" t="n"/>
       <c r="I941" s="3" t="n"/>
       <c r="J941" s="3" t="n"/>
@@ -31579,7 +31629,7 @@
       <c r="D942" s="4" t="n"/>
       <c r="E942" s="4" t="n"/>
       <c r="F942" s="3" t="n"/>
-      <c r="G942" t="inlineStr"/>
+      <c r="G942" s="0" t="inlineStr"/>
       <c r="H942" s="3" t="n"/>
       <c r="I942" s="3" t="n"/>
       <c r="J942" s="3" t="n"/>
@@ -31608,7 +31658,7 @@
       <c r="D943" s="4" t="n"/>
       <c r="E943" s="4" t="n"/>
       <c r="F943" s="3" t="n"/>
-      <c r="G943" t="inlineStr"/>
+      <c r="G943" s="0" t="inlineStr"/>
       <c r="H943" s="3" t="n"/>
       <c r="I943" s="3" t="n"/>
       <c r="J943" s="3" t="n"/>
@@ -31637,7 +31687,7 @@
       <c r="D944" s="4" t="n"/>
       <c r="E944" s="4" t="n"/>
       <c r="F944" s="3" t="n"/>
-      <c r="G944" t="inlineStr"/>
+      <c r="G944" s="0" t="inlineStr"/>
       <c r="H944" s="3" t="n"/>
       <c r="I944" s="3" t="n"/>
       <c r="J944" s="3" t="n"/>
@@ -31666,7 +31716,7 @@
       <c r="D945" s="4" t="n"/>
       <c r="E945" s="4" t="n"/>
       <c r="F945" s="3" t="n"/>
-      <c r="G945" t="inlineStr"/>
+      <c r="G945" s="0" t="inlineStr"/>
       <c r="H945" s="3" t="n"/>
       <c r="I945" s="3" t="n"/>
       <c r="J945" s="3" t="n"/>
@@ -31695,7 +31745,7 @@
       <c r="D946" s="4" t="n"/>
       <c r="E946" s="4" t="n"/>
       <c r="F946" s="3" t="n"/>
-      <c r="G946" t="inlineStr"/>
+      <c r="G946" s="0" t="inlineStr"/>
       <c r="H946" s="3" t="n"/>
       <c r="I946" s="3" t="n"/>
       <c r="J946" s="3" t="n"/>
@@ -31724,7 +31774,7 @@
       <c r="D947" s="4" t="n"/>
       <c r="E947" s="4" t="n"/>
       <c r="F947" s="3" t="n"/>
-      <c r="G947" t="inlineStr"/>
+      <c r="G947" s="0" t="inlineStr"/>
       <c r="H947" s="3" t="n"/>
       <c r="I947" s="3" t="n"/>
       <c r="J947" s="3" t="n"/>
@@ -31753,7 +31803,7 @@
       <c r="D948" s="4" t="n"/>
       <c r="E948" s="4" t="n"/>
       <c r="F948" s="3" t="n"/>
-      <c r="G948" t="inlineStr"/>
+      <c r="G948" s="0" t="inlineStr"/>
       <c r="H948" s="3" t="n"/>
       <c r="I948" s="3" t="n"/>
       <c r="J948" s="3" t="n"/>
@@ -31782,7 +31832,7 @@
       <c r="D949" s="4" t="n"/>
       <c r="E949" s="4" t="n"/>
       <c r="F949" s="3" t="n"/>
-      <c r="G949" t="inlineStr"/>
+      <c r="G949" s="0" t="inlineStr"/>
       <c r="H949" s="3" t="n"/>
       <c r="I949" s="3" t="n"/>
       <c r="J949" s="3" t="n"/>
@@ -31811,7 +31861,7 @@
       <c r="D950" s="4" t="n"/>
       <c r="E950" s="4" t="n"/>
       <c r="F950" s="3" t="n"/>
-      <c r="G950" t="inlineStr"/>
+      <c r="G950" s="0" t="inlineStr"/>
       <c r="H950" s="3" t="n"/>
       <c r="I950" s="3" t="n"/>
       <c r="J950" s="3" t="n"/>
@@ -31840,7 +31890,7 @@
       <c r="D951" s="4" t="n"/>
       <c r="E951" s="4" t="n"/>
       <c r="F951" s="3" t="n"/>
-      <c r="G951" t="inlineStr"/>
+      <c r="G951" s="0" t="inlineStr"/>
       <c r="H951" s="3" t="n"/>
       <c r="I951" s="3" t="n"/>
       <c r="J951" s="3" t="n"/>
@@ -31869,7 +31919,7 @@
       <c r="D952" s="4" t="n"/>
       <c r="E952" s="4" t="n"/>
       <c r="F952" s="3" t="n"/>
-      <c r="G952" t="inlineStr"/>
+      <c r="G952" s="0" t="inlineStr"/>
       <c r="H952" s="3" t="n"/>
       <c r="I952" s="3" t="n"/>
       <c r="J952" s="3" t="n"/>
@@ -31898,7 +31948,7 @@
       <c r="D953" s="4" t="n"/>
       <c r="E953" s="4" t="n"/>
       <c r="F953" s="3" t="n"/>
-      <c r="G953" t="inlineStr"/>
+      <c r="G953" s="0" t="inlineStr"/>
       <c r="H953" s="3" t="n"/>
       <c r="I953" s="3" t="n"/>
       <c r="J953" s="3" t="n"/>
@@ -31927,7 +31977,7 @@
       <c r="D954" s="4" t="n"/>
       <c r="E954" s="4" t="n"/>
       <c r="F954" s="3" t="n"/>
-      <c r="G954" t="inlineStr"/>
+      <c r="G954" s="0" t="inlineStr"/>
       <c r="H954" s="3" t="n"/>
       <c r="I954" s="3" t="n"/>
       <c r="J954" s="3" t="n"/>
@@ -31956,7 +32006,7 @@
       <c r="D955" s="4" t="n"/>
       <c r="E955" s="4" t="n"/>
       <c r="F955" s="3" t="n"/>
-      <c r="G955" t="inlineStr"/>
+      <c r="G955" s="0" t="inlineStr"/>
       <c r="H955" s="3" t="n"/>
       <c r="I955" s="3" t="n"/>
       <c r="J955" s="3" t="n"/>
@@ -31985,7 +32035,7 @@
       <c r="D956" s="4" t="n"/>
       <c r="E956" s="4" t="n"/>
       <c r="F956" s="3" t="n"/>
-      <c r="G956" t="inlineStr"/>
+      <c r="G956" s="0" t="inlineStr"/>
       <c r="H956" s="3" t="n"/>
       <c r="I956" s="3" t="n"/>
       <c r="J956" s="3" t="n"/>
@@ -32014,7 +32064,7 @@
       <c r="D957" s="4" t="n"/>
       <c r="E957" s="4" t="n"/>
       <c r="F957" s="3" t="n"/>
-      <c r="G957" t="inlineStr"/>
+      <c r="G957" s="0" t="inlineStr"/>
       <c r="H957" s="3" t="n"/>
       <c r="I957" s="3" t="n"/>
       <c r="J957" s="3" t="n"/>
@@ -32043,7 +32093,7 @@
       <c r="D958" s="4" t="n"/>
       <c r="E958" s="4" t="n"/>
       <c r="F958" s="3" t="n"/>
-      <c r="G958" t="inlineStr"/>
+      <c r="G958" s="0" t="inlineStr"/>
       <c r="H958" s="3" t="n"/>
       <c r="I958" s="3" t="n"/>
       <c r="J958" s="3" t="n"/>
@@ -32072,7 +32122,7 @@
       <c r="D959" s="4" t="n"/>
       <c r="E959" s="4" t="n"/>
       <c r="F959" s="3" t="n"/>
-      <c r="G959" t="inlineStr"/>
+      <c r="G959" s="0" t="inlineStr"/>
       <c r="H959" s="3" t="n"/>
       <c r="I959" s="3" t="n"/>
       <c r="J959" s="3" t="n"/>
@@ -32101,7 +32151,7 @@
       <c r="D960" s="4" t="n"/>
       <c r="E960" s="4" t="n"/>
       <c r="F960" s="3" t="n"/>
-      <c r="G960" t="inlineStr"/>
+      <c r="G960" s="0" t="inlineStr"/>
       <c r="H960" s="3" t="n"/>
       <c r="I960" s="3" t="n"/>
       <c r="J960" s="3" t="n"/>
@@ -32130,7 +32180,7 @@
       <c r="D961" s="4" t="n"/>
       <c r="E961" s="4" t="n"/>
       <c r="F961" s="3" t="n"/>
-      <c r="G961" t="inlineStr"/>
+      <c r="G961" s="0" t="inlineStr"/>
       <c r="H961" s="3" t="n"/>
       <c r="I961" s="3" t="n"/>
       <c r="J961" s="3" t="n"/>
@@ -32159,7 +32209,7 @@
       <c r="D962" s="4" t="n"/>
       <c r="E962" s="4" t="n"/>
       <c r="F962" s="3" t="n"/>
-      <c r="G962" t="inlineStr"/>
+      <c r="G962" s="0" t="inlineStr"/>
       <c r="H962" s="3" t="n"/>
       <c r="I962" s="3" t="n"/>
       <c r="J962" s="3" t="n"/>
@@ -32188,7 +32238,7 @@
       <c r="D963" s="4" t="n"/>
       <c r="E963" s="4" t="n"/>
       <c r="F963" s="3" t="n"/>
-      <c r="G963" t="inlineStr"/>
+      <c r="G963" s="0" t="inlineStr"/>
       <c r="H963" s="3" t="n"/>
       <c r="I963" s="3" t="n"/>
       <c r="J963" s="3" t="n"/>
@@ -32217,7 +32267,7 @@
       <c r="D964" s="4" t="n"/>
       <c r="E964" s="4" t="n"/>
       <c r="F964" s="3" t="n"/>
-      <c r="G964" t="inlineStr"/>
+      <c r="G964" s="0" t="inlineStr"/>
       <c r="H964" s="3" t="n"/>
       <c r="I964" s="3" t="n"/>
       <c r="J964" s="3" t="n"/>
@@ -32246,7 +32296,7 @@
       <c r="D965" s="4" t="n"/>
       <c r="E965" s="4" t="n"/>
       <c r="F965" s="3" t="n"/>
-      <c r="G965" t="inlineStr"/>
+      <c r="G965" s="0" t="inlineStr"/>
       <c r="H965" s="3" t="n"/>
       <c r="I965" s="3" t="n"/>
       <c r="J965" s="3" t="n"/>
@@ -32275,7 +32325,7 @@
       <c r="D966" s="4" t="n"/>
       <c r="E966" s="4" t="n"/>
       <c r="F966" s="3" t="n"/>
-      <c r="G966" t="inlineStr"/>
+      <c r="G966" s="0" t="inlineStr"/>
       <c r="H966" s="3" t="n"/>
       <c r="I966" s="3" t="n"/>
       <c r="J966" s="3" t="n"/>
@@ -32304,7 +32354,7 @@
       <c r="D967" s="4" t="n"/>
       <c r="E967" s="4" t="n"/>
       <c r="F967" s="3" t="n"/>
-      <c r="G967" t="inlineStr"/>
+      <c r="G967" s="0" t="inlineStr"/>
       <c r="H967" s="3" t="n"/>
       <c r="I967" s="3" t="n"/>
       <c r="J967" s="3" t="n"/>
@@ -32333,7 +32383,7 @@
       <c r="D968" s="4" t="n"/>
       <c r="E968" s="4" t="n"/>
       <c r="F968" s="3" t="n"/>
-      <c r="G968" t="inlineStr"/>
+      <c r="G968" s="0" t="inlineStr"/>
       <c r="H968" s="3" t="n"/>
       <c r="I968" s="3" t="n"/>
       <c r="J968" s="3" t="n"/>
@@ -32362,7 +32412,7 @@
       <c r="D969" s="4" t="n"/>
       <c r="E969" s="4" t="n"/>
       <c r="F969" s="3" t="n"/>
-      <c r="G969" t="inlineStr"/>
+      <c r="G969" s="0" t="inlineStr"/>
       <c r="H969" s="3" t="n"/>
       <c r="I969" s="3" t="n"/>
       <c r="J969" s="3" t="n"/>
@@ -32391,7 +32441,7 @@
       <c r="D970" s="4" t="n"/>
       <c r="E970" s="4" t="n"/>
       <c r="F970" s="3" t="n"/>
-      <c r="G970" t="inlineStr"/>
+      <c r="G970" s="0" t="inlineStr"/>
       <c r="H970" s="3" t="n"/>
       <c r="I970" s="3" t="n"/>
       <c r="J970" s="3" t="n"/>
@@ -32420,7 +32470,7 @@
       <c r="D971" s="4" t="n"/>
       <c r="E971" s="4" t="n"/>
       <c r="F971" s="3" t="n"/>
-      <c r="G971" t="inlineStr"/>
+      <c r="G971" s="0" t="inlineStr"/>
       <c r="H971" s="3" t="n"/>
       <c r="I971" s="3" t="n"/>
       <c r="J971" s="3" t="n"/>
@@ -32449,7 +32499,7 @@
       <c r="D972" s="4" t="n"/>
       <c r="E972" s="4" t="n"/>
       <c r="F972" s="3" t="n"/>
-      <c r="G972" t="inlineStr"/>
+      <c r="G972" s="0" t="inlineStr"/>
       <c r="H972" s="3" t="n"/>
       <c r="I972" s="3" t="n"/>
       <c r="J972" s="3" t="n"/>
@@ -32478,7 +32528,7 @@
       <c r="D973" s="4" t="n"/>
       <c r="E973" s="4" t="n"/>
       <c r="F973" s="3" t="n"/>
-      <c r="G973" t="inlineStr"/>
+      <c r="G973" s="0" t="inlineStr"/>
       <c r="H973" s="3" t="n"/>
       <c r="I973" s="3" t="n"/>
       <c r="J973" s="3" t="n"/>
@@ -32507,7 +32557,7 @@
       <c r="D974" s="4" t="n"/>
       <c r="E974" s="4" t="n"/>
       <c r="F974" s="3" t="n"/>
-      <c r="G974" t="inlineStr"/>
+      <c r="G974" s="0" t="inlineStr"/>
       <c r="H974" s="3" t="n"/>
       <c r="I974" s="3" t="n"/>
       <c r="J974" s="3" t="n"/>
@@ -32536,7 +32586,7 @@
       <c r="D975" s="4" t="n"/>
       <c r="E975" s="4" t="n"/>
       <c r="F975" s="3" t="n"/>
-      <c r="G975" t="inlineStr"/>
+      <c r="G975" s="0" t="inlineStr"/>
       <c r="H975" s="3" t="n"/>
       <c r="I975" s="3" t="n"/>
       <c r="J975" s="3" t="n"/>
@@ -32565,7 +32615,7 @@
       <c r="D976" s="4" t="n"/>
       <c r="E976" s="4" t="n"/>
       <c r="F976" s="3" t="n"/>
-      <c r="G976" t="inlineStr"/>
+      <c r="G976" s="0" t="inlineStr"/>
       <c r="H976" s="3" t="n"/>
       <c r="I976" s="3" t="n"/>
       <c r="J976" s="3" t="n"/>
@@ -32594,7 +32644,7 @@
       <c r="D977" s="4" t="n"/>
       <c r="E977" s="4" t="n"/>
       <c r="F977" s="3" t="n"/>
-      <c r="G977" t="inlineStr"/>
+      <c r="G977" s="0" t="inlineStr"/>
       <c r="H977" s="3" t="n"/>
       <c r="I977" s="3" t="n"/>
       <c r="J977" s="3" t="n"/>
@@ -32623,7 +32673,7 @@
       <c r="D978" s="4" t="n"/>
       <c r="E978" s="4" t="n"/>
       <c r="F978" s="3" t="n"/>
-      <c r="G978" t="inlineStr"/>
+      <c r="G978" s="0" t="inlineStr"/>
       <c r="H978" s="3" t="n"/>
       <c r="I978" s="3" t="n"/>
       <c r="J978" s="3" t="n"/>
@@ -32652,7 +32702,7 @@
       <c r="D979" s="4" t="n"/>
       <c r="E979" s="4" t="n"/>
       <c r="F979" s="3" t="n"/>
-      <c r="G979" t="inlineStr"/>
+      <c r="G979" s="0" t="inlineStr"/>
       <c r="H979" s="3" t="n"/>
       <c r="I979" s="3" t="n"/>
       <c r="J979" s="3" t="n"/>
@@ -32681,7 +32731,7 @@
       <c r="D980" s="4" t="n"/>
       <c r="E980" s="4" t="n"/>
       <c r="F980" s="3" t="n"/>
-      <c r="G980" t="inlineStr"/>
+      <c r="G980" s="0" t="inlineStr"/>
       <c r="H980" s="3" t="n"/>
       <c r="I980" s="3" t="n"/>
       <c r="J980" s="3" t="n"/>
@@ -32710,7 +32760,7 @@
       <c r="D981" s="4" t="n"/>
       <c r="E981" s="4" t="n"/>
       <c r="F981" s="3" t="n"/>
-      <c r="G981" t="inlineStr"/>
+      <c r="G981" s="0" t="inlineStr"/>
       <c r="H981" s="3" t="n"/>
       <c r="I981" s="3" t="n"/>
       <c r="J981" s="3" t="n"/>
@@ -32739,7 +32789,7 @@
       <c r="D982" s="4" t="n"/>
       <c r="E982" s="4" t="n"/>
       <c r="F982" s="3" t="n"/>
-      <c r="G982" t="inlineStr"/>
+      <c r="G982" s="0" t="inlineStr"/>
       <c r="H982" s="3" t="n"/>
       <c r="I982" s="3" t="n"/>
       <c r="J982" s="3" t="n"/>
@@ -32768,7 +32818,7 @@
       <c r="D983" s="4" t="n"/>
       <c r="E983" s="4" t="n"/>
       <c r="F983" s="3" t="n"/>
-      <c r="G983" t="inlineStr"/>
+      <c r="G983" s="0" t="inlineStr"/>
       <c r="H983" s="3" t="n"/>
       <c r="I983" s="3" t="n"/>
       <c r="J983" s="3" t="n"/>
@@ -32797,7 +32847,7 @@
       <c r="D984" s="4" t="n"/>
       <c r="E984" s="4" t="n"/>
       <c r="F984" s="3" t="n"/>
-      <c r="G984" t="inlineStr"/>
+      <c r="G984" s="0" t="inlineStr"/>
       <c r="H984" s="3" t="n"/>
       <c r="I984" s="3" t="n"/>
       <c r="J984" s="3" t="n"/>
@@ -32826,7 +32876,7 @@
       <c r="D985" s="4" t="n"/>
       <c r="E985" s="4" t="n"/>
       <c r="F985" s="3" t="n"/>
-      <c r="G985" t="inlineStr"/>
+      <c r="G985" s="0" t="inlineStr"/>
       <c r="H985" s="3" t="n"/>
       <c r="I985" s="3" t="n"/>
       <c r="J985" s="3" t="n"/>
@@ -32855,7 +32905,7 @@
       <c r="D986" s="4" t="n"/>
       <c r="E986" s="4" t="n"/>
       <c r="F986" s="3" t="n"/>
-      <c r="G986" t="inlineStr"/>
+      <c r="G986" s="0" t="inlineStr"/>
       <c r="H986" s="3" t="n"/>
       <c r="I986" s="3" t="n"/>
       <c r="J986" s="3" t="n"/>
@@ -32884,7 +32934,7 @@
       <c r="D987" s="4" t="n"/>
       <c r="E987" s="4" t="n"/>
       <c r="F987" s="3" t="n"/>
-      <c r="G987" t="inlineStr"/>
+      <c r="G987" s="0" t="inlineStr"/>
       <c r="H987" s="3" t="n"/>
       <c r="I987" s="3" t="n"/>
       <c r="J987" s="3" t="n"/>
@@ -32913,7 +32963,7 @@
       <c r="D988" s="4" t="n"/>
       <c r="E988" s="4" t="n"/>
       <c r="F988" s="3" t="n"/>
-      <c r="G988" t="inlineStr"/>
+      <c r="G988" s="0" t="inlineStr"/>
       <c r="H988" s="3" t="n"/>
       <c r="I988" s="3" t="n"/>
       <c r="J988" s="3" t="n"/>
@@ -32942,7 +32992,7 @@
       <c r="D989" s="4" t="n"/>
       <c r="E989" s="4" t="n"/>
       <c r="F989" s="3" t="n"/>
-      <c r="G989" t="inlineStr"/>
+      <c r="G989" s="0" t="inlineStr"/>
       <c r="H989" s="3" t="n"/>
       <c r="I989" s="3" t="n"/>
       <c r="J989" s="3" t="n"/>
@@ -32971,7 +33021,7 @@
       <c r="D990" s="4" t="n"/>
       <c r="E990" s="4" t="n"/>
       <c r="F990" s="3" t="n"/>
-      <c r="G990" t="inlineStr"/>
+      <c r="G990" s="0" t="inlineStr"/>
       <c r="H990" s="3" t="n"/>
       <c r="I990" s="3" t="n"/>
       <c r="J990" s="3" t="n"/>
@@ -33000,7 +33050,7 @@
       <c r="D991" s="4" t="n"/>
       <c r="E991" s="4" t="n"/>
       <c r="F991" s="3" t="n"/>
-      <c r="G991" t="inlineStr"/>
+      <c r="G991" s="0" t="inlineStr"/>
       <c r="H991" s="3" t="n"/>
       <c r="I991" s="3" t="n"/>
       <c r="J991" s="3" t="n"/>
@@ -33029,7 +33079,7 @@
       <c r="D992" s="4" t="n"/>
       <c r="E992" s="4" t="n"/>
       <c r="F992" s="3" t="n"/>
-      <c r="G992" t="inlineStr"/>
+      <c r="G992" s="0" t="inlineStr"/>
       <c r="H992" s="3" t="n"/>
       <c r="I992" s="3" t="n"/>
       <c r="J992" s="3" t="n"/>
@@ -33058,7 +33108,7 @@
       <c r="D993" s="4" t="n"/>
       <c r="E993" s="4" t="n"/>
       <c r="F993" s="3" t="n"/>
-      <c r="G993" t="inlineStr"/>
+      <c r="G993" s="0" t="inlineStr"/>
       <c r="H993" s="3" t="n"/>
       <c r="I993" s="3" t="n"/>
       <c r="J993" s="3" t="n"/>
@@ -33087,7 +33137,7 @@
       <c r="D994" s="4" t="n"/>
       <c r="E994" s="4" t="n"/>
       <c r="F994" s="3" t="n"/>
-      <c r="G994" t="inlineStr"/>
+      <c r="G994" s="0" t="inlineStr"/>
       <c r="H994" s="3" t="n"/>
       <c r="I994" s="3" t="n"/>
       <c r="J994" s="3" t="n"/>
@@ -33116,7 +33166,7 @@
       <c r="D995" s="4" t="n"/>
       <c r="E995" s="4" t="n"/>
       <c r="F995" s="3" t="n"/>
-      <c r="G995" t="inlineStr"/>
+      <c r="G995" s="0" t="inlineStr"/>
       <c r="H995" s="3" t="n"/>
       <c r="I995" s="3" t="n"/>
       <c r="J995" s="3" t="n"/>
@@ -33145,7 +33195,7 @@
       <c r="D996" s="4" t="n"/>
       <c r="E996" s="4" t="n"/>
       <c r="F996" s="3" t="n"/>
-      <c r="G996" t="inlineStr"/>
+      <c r="G996" s="0" t="inlineStr"/>
       <c r="H996" s="3" t="n"/>
       <c r="I996" s="3" t="n"/>
       <c r="J996" s="3" t="n"/>
@@ -33174,7 +33224,7 @@
       <c r="D997" s="4" t="n"/>
       <c r="E997" s="4" t="n"/>
       <c r="F997" s="3" t="n"/>
-      <c r="G997" t="inlineStr"/>
+      <c r="G997" s="0" t="inlineStr"/>
       <c r="H997" s="3" t="n"/>
       <c r="I997" s="3" t="n"/>
       <c r="J997" s="3" t="n"/>
@@ -33203,7 +33253,7 @@
       <c r="D998" s="4" t="n"/>
       <c r="E998" s="4" t="n"/>
       <c r="F998" s="3" t="n"/>
-      <c r="G998" t="inlineStr"/>
+      <c r="G998" s="0" t="inlineStr"/>
       <c r="H998" s="3" t="n"/>
       <c r="I998" s="3" t="n"/>
       <c r="J998" s="3" t="n"/>
@@ -33232,7 +33282,7 @@
       <c r="D999" s="4" t="n"/>
       <c r="E999" s="4" t="n"/>
       <c r="F999" s="3" t="n"/>
-      <c r="G999" t="inlineStr"/>
+      <c r="G999" s="0" t="inlineStr"/>
       <c r="H999" s="3" t="n"/>
       <c r="I999" s="3" t="n"/>
       <c r="J999" s="3" t="n"/>
@@ -33261,7 +33311,7 @@
       <c r="D1000" s="4" t="n"/>
       <c r="E1000" s="4" t="n"/>
       <c r="F1000" s="3" t="n"/>
-      <c r="G1000" t="inlineStr"/>
+      <c r="G1000" s="0" t="inlineStr"/>
       <c r="H1000" s="3" t="n"/>
       <c r="I1000" s="3" t="n"/>
       <c r="J1000" s="3" t="n"/>
@@ -33287,4 +33337,459 @@
   <autoFilter ref="A1:G1000"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="5" min="1" max="1"/>
+    <col width="35" customWidth="1" style="5" min="2" max="2"/>
+    <col width="40" customWidth="1" style="5" min="3" max="3"/>
+    <col width="18" customWidth="1" style="5" min="4" max="4"/>
+    <col width="60" customWidth="1" style="5" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>(731) 571-5337</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Holly Bobo</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr"/>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Victim</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>Holly cell phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>(731) 571-9634</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Karen Bobo</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr"/>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Victim Family</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>(731) 571-6498</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Dana Bobo</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr"/>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Victim Family</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>(731) 571-4016</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Clint Bobo</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr"/>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Victim Family</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Brother; witnessed abduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>(731) 571-3498</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Natalie Bobo</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr"/>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Victim Family</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Cousin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>(731) 733-3992</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Drew Scott</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr"/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Victim/Witness</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Holly boyfriend; hunting Bath Springs on 4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>(731) 733-0139</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Kassie Barnes</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Neighbor</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Confirmed from KML data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>(731) 733-0071</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>James Barnes</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr"/>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Neighbor</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Heard screaming 7:40 AM; SMS with Clark 7:04 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>(731) 549-0408</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Keith Clark</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>2325 Haney School Rd, Decaturville</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Witness</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>IR #28; Barnes friend; working on truck at Barnes house on 4/13; 1,157 call records</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>(731) 798-0089</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Larry Hamm</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>1040 Frizzell Rd, Lexington</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Witness</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>IR #95; saw suspicious white van w/ Seagrams graphics 10:30-10:45 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>(731) 549-0599</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Jonathan Dodd</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Scotts Hill</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Person of Interest</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>Polygraph (IR #59); FBI lead (IR #90); 4-wheeler theft attempt (IR #270)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>(731) 220-0597</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Becky Conrad (Jerrel Conrad)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>3585 Hwy 192, Holladay</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>No Significance</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Zero call records; passing ping</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>(901) 827-8777</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>SHARED: Zach/Dylan Adams, Dennis Benjamin</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Defendant</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Memphis area code; shared/burner phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>(770) 653-4095</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>SHARED: Zach Adams, Dennis Benjamin</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Defendant</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta area code; shared device</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>(731) 549-1804</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Jason Autry</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Defendant</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Co-defendant; testified for prosecution</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>(731) 549-0670</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Dylan Adams</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>Defendant</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>Zach brother</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>(731) 549-0446</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Shane Austin</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Defendant</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>Remains found ~3 mi from home</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>